--- a/data/OP2/case18_2_2/case18_operational_data.xlsx
+++ b/data/OP2/case18_2_2/case18_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case18_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case18_2_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B93344F-939B-1A40-A0CE-E2F4E31A6CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AAAF63-517C-F14D-8EFF-9CE7D97BFA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -458,7 +458,8 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="C2" s="1">
-        <v>0.12</v>
+        <f>F2*3</f>
+        <v>0.36</v>
       </c>
       <c r="D2" s="2">
         <f>$B2/SUM($B$2:$B$1048576)</f>
@@ -476,14 +477,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B16" si="0">E3*3</f>
+        <f t="shared" ref="B3:B31" si="0">E3*3</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="C3" s="1">
-        <v>0.25</v>
+        <f t="shared" ref="C3:C31" si="1">F3*3</f>
+        <v>0.75</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D31" si="1">$B3/SUM($B$2:$B$1048576)</f>
+        <f t="shared" ref="D3:D31" si="2">$B3/SUM($B$2:$B$1048576)</f>
         <v>1.7241379310344827E-2</v>
       </c>
       <c r="E3" s="1">
@@ -502,10 +504,11 @@
         <v>4.5</v>
       </c>
       <c r="C4" s="1">
-        <v>0.93</v>
+        <f t="shared" si="1"/>
+        <v>2.79</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.4655172413793094E-2</v>
       </c>
       <c r="E4" s="1">
@@ -524,10 +527,11 @@
         <v>9</v>
       </c>
       <c r="C5" s="1">
-        <v>2.2599999999999998</v>
+        <f t="shared" si="1"/>
+        <v>6.7799999999999994</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.12931034482758619</v>
       </c>
       <c r="E5" s="1">
@@ -546,10 +550,11 @@
         <v>2.4000000000000004</v>
       </c>
       <c r="C6" s="1">
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>1.5</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="E6" s="1">
@@ -568,10 +573,11 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="C7" s="1">
-        <v>0.12</v>
+        <f t="shared" si="1"/>
+        <v>0.36</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.6206896551724137E-3</v>
       </c>
       <c r="E7" s="1">
@@ -590,10 +596,11 @@
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>0.62</v>
+        <f t="shared" si="1"/>
+        <v>1.8599999999999999</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3103448275862065E-2</v>
       </c>
       <c r="E8" s="1">
@@ -612,10 +619,11 @@
         <v>1.5</v>
       </c>
       <c r="C9" s="1">
-        <v>0.31</v>
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.1551724137931032E-2</v>
       </c>
       <c r="E9" s="1">
@@ -634,10 +642,11 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>0.62</v>
+        <f t="shared" si="1"/>
+        <v>1.8599999999999999</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3103448275862065E-2</v>
       </c>
       <c r="E10" s="1">
@@ -656,10 +665,11 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="C11" s="1">
-        <v>0.19</v>
+        <f t="shared" si="1"/>
+        <v>0.57000000000000006</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2931034482758617E-2</v>
       </c>
       <c r="E11" s="1">
@@ -678,10 +688,11 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="C12" s="1">
-        <v>0.12</v>
+        <f t="shared" si="1"/>
+        <v>0.36</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.6206896551724137E-3</v>
       </c>
       <c r="E12" s="1">
@@ -700,10 +711,11 @@
         <v>2.4000000000000004</v>
       </c>
       <c r="C13" s="1">
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>1.5</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="E13" s="1">
@@ -722,10 +734,11 @@
         <v>1.5</v>
       </c>
       <c r="C14" s="1">
-        <v>0.31</v>
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.1551724137931032E-2</v>
       </c>
       <c r="E14" s="1">
@@ -744,10 +757,11 @@
         <v>3</v>
       </c>
       <c r="C15" s="1">
-        <v>0.62</v>
+        <f t="shared" si="1"/>
+        <v>1.8599999999999999</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.3103448275862065E-2</v>
       </c>
       <c r="E15" s="1">
@@ -766,10 +780,11 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="C16" s="1">
-        <v>0.12</v>
+        <f t="shared" si="1"/>
+        <v>0.36</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.6206896551724137E-3</v>
       </c>
       <c r="E16" s="1">
@@ -784,11 +799,12 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <f>E17*3</f>
+        <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="C17" s="1">
-        <v>0.12</v>
+        <f t="shared" si="1"/>
+        <v>0.36</v>
       </c>
       <c r="D17" s="2">
         <f>$B17/SUM($B$2:$B$1048576)</f>
@@ -806,14 +822,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" ref="B18:B31" si="2">E18*3</f>
+        <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="C18" s="1">
-        <v>0.25</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7241379310344827E-2</v>
       </c>
       <c r="E18" s="1">
@@ -828,14 +845,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="1"/>
+        <v>2.79</v>
+      </c>
+      <c r="D19" s="2">
         <f t="shared" si="2"/>
-        <v>4.5</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0.93</v>
-      </c>
-      <c r="D19" s="2">
-        <f t="shared" si="1"/>
         <v>6.4655172413793094E-2</v>
       </c>
       <c r="E19" s="1">
@@ -850,14 +868,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" si="1"/>
+        <v>6.7799999999999994</v>
+      </c>
+      <c r="D20" s="2">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="C20" s="1">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="D20" s="2">
-        <f t="shared" si="1"/>
         <v>0.12931034482758619</v>
       </c>
       <c r="E20" s="1">
@@ -872,14 +891,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="D21" s="2">
         <f t="shared" si="2"/>
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="D21" s="2">
-        <f t="shared" si="1"/>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="E21" s="1">
@@ -894,14 +914,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="1"/>
+        <v>0.36</v>
+      </c>
+      <c r="D22" s="2">
         <f t="shared" si="2"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="1"/>
         <v>8.6206896551724137E-3</v>
       </c>
       <c r="E22" s="1">
@@ -916,14 +937,15 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="1"/>
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="D23" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="1"/>
         <v>4.3103448275862065E-2</v>
       </c>
       <c r="E23" s="1">
@@ -938,14 +960,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="D24" s="2">
         <f t="shared" si="2"/>
-        <v>1.5</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.31</v>
-      </c>
-      <c r="D24" s="2">
-        <f t="shared" si="1"/>
         <v>2.1551724137931032E-2</v>
       </c>
       <c r="E24" s="1">
@@ -960,14 +983,15 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="1"/>
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="D25" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="D25" s="2">
-        <f t="shared" si="1"/>
         <v>4.3103448275862065E-2</v>
       </c>
       <c r="E25" s="1">
@@ -982,14 +1006,15 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
+        <f t="shared" si="0"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" si="1"/>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="D26" s="2">
         <f t="shared" si="2"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="D26" s="2">
-        <f t="shared" si="1"/>
         <v>1.2931034482758617E-2</v>
       </c>
       <c r="E26" s="1">
@@ -1004,14 +1029,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" si="1"/>
+        <v>0.36</v>
+      </c>
+      <c r="D27" s="2">
         <f t="shared" si="2"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="D27" s="2">
-        <f t="shared" si="1"/>
         <v>8.6206896551724137E-3</v>
       </c>
       <c r="E27" s="1">
@@ -1026,14 +1052,15 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="2">
         <f t="shared" si="2"/>
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="D28" s="2">
-        <f t="shared" si="1"/>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="E28" s="1">
@@ -1048,14 +1075,15 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="D29" s="2">
         <f t="shared" si="2"/>
-        <v>1.5</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0.31</v>
-      </c>
-      <c r="D29" s="2">
-        <f t="shared" si="1"/>
         <v>2.1551724137931032E-2</v>
       </c>
       <c r="E29" s="1">
@@ -1070,14 +1098,15 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" si="1"/>
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="D30" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="D30" s="2">
-        <f t="shared" si="1"/>
         <v>4.3103448275862065E-2</v>
       </c>
       <c r="E30" s="1">
@@ -1092,14 +1121,15 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" si="1"/>
+        <v>0.36</v>
+      </c>
+      <c r="D31" s="2">
         <f t="shared" si="2"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="D31" s="2">
-        <f t="shared" si="1"/>
         <v>8.6206896551724137E-3</v>
       </c>
       <c r="E31" s="1">

--- a/data/OP2/case18_2_2/case18_operational_data.xlsx
+++ b/data/OP2/case18_2_2/case18_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case18_2_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AAAF63-517C-F14D-8EFF-9CE7D97BFA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404D3E4C-C787-B847-9D9C-5268F187CB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="680" windowWidth="50080" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -454,12 +454,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*3</f>
-        <v>0.60000000000000009</v>
+        <f>E2*2</f>
+        <v>0.4</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*3</f>
-        <v>0.36</v>
+        <f>F2*-1.5</f>
+        <v>-0.18</v>
       </c>
       <c r="D2" s="2">
         <f>$B2/SUM($B$2:$B$1048576)</f>
@@ -477,12 +477,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B31" si="0">E3*3</f>
-        <v>1.2000000000000002</v>
+        <f t="shared" ref="B3:B31" si="0">E3*2</f>
+        <v>0.8</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C31" si="1">F3*3</f>
-        <v>0.75</v>
+        <f t="shared" ref="C3:C31" si="1">F3*-1.5</f>
+        <v>-0.375</v>
       </c>
       <c r="D3" s="2">
         <f t="shared" ref="D3:D31" si="2">$B3/SUM($B$2:$B$1048576)</f>
@@ -501,15 +501,15 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>2.79</v>
+        <v>-1.395</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="2"/>
-        <v>6.4655172413793094E-2</v>
+        <v>6.4655172413793108E-2</v>
       </c>
       <c r="E4" s="1">
         <v>1.5</v>
@@ -524,15 +524,15 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>6.7799999999999994</v>
+        <v>-3.3899999999999997</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="2"/>
-        <v>0.12931034482758619</v>
+        <v>0.12931034482758622</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -547,11 +547,11 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>-0.75</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="2"/>
@@ -570,11 +570,11 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>0.36</v>
+        <v>-0.18</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="2"/>
@@ -593,15 +593,15 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>1.8599999999999999</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="2"/>
-        <v>4.3103448275862065E-2</v>
+        <v>4.3103448275862072E-2</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -616,15 +616,15 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>0.92999999999999994</v>
+        <v>-0.46499999999999997</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="2"/>
-        <v>2.1551724137931032E-2</v>
+        <v>2.1551724137931036E-2</v>
       </c>
       <c r="E9" s="1">
         <v>0.5</v>
@@ -639,15 +639,15 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>1.8599999999999999</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="2"/>
-        <v>4.3103448275862065E-2</v>
+        <v>4.3103448275862072E-2</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -662,15 +662,15 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.6</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>0.57000000000000006</v>
+        <v>-0.28500000000000003</v>
       </c>
       <c r="D11" s="2">
         <f t="shared" si="2"/>
-        <v>1.2931034482758617E-2</v>
+        <v>1.2931034482758621E-2</v>
       </c>
       <c r="E11" s="1">
         <v>0.3</v>
@@ -685,11 +685,11 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>0.36</v>
+        <v>-0.18</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" si="2"/>
@@ -708,11 +708,11 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>-0.75</v>
       </c>
       <c r="D13" s="2">
         <f t="shared" si="2"/>
@@ -731,15 +731,15 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>0.92999999999999994</v>
+        <v>-0.46499999999999997</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="2"/>
-        <v>2.1551724137931032E-2</v>
+        <v>2.1551724137931036E-2</v>
       </c>
       <c r="E14" s="1">
         <v>0.5</v>
@@ -754,15 +754,15 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>1.8599999999999999</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="2"/>
-        <v>4.3103448275862065E-2</v>
+        <v>4.3103448275862072E-2</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -777,11 +777,11 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>0.36</v>
+        <v>-0.18</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" si="2"/>
@@ -800,11 +800,11 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>0.36</v>
+        <v>-0.18</v>
       </c>
       <c r="D17" s="2">
         <f>$B17/SUM($B$2:$B$1048576)</f>
@@ -823,11 +823,11 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>1.2000000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>-0.375</v>
       </c>
       <c r="D18" s="2">
         <f t="shared" si="2"/>
@@ -846,15 +846,15 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>2.79</v>
+        <v>-1.395</v>
       </c>
       <c r="D19" s="2">
         <f t="shared" si="2"/>
-        <v>6.4655172413793094E-2</v>
+        <v>6.4655172413793108E-2</v>
       </c>
       <c r="E19" s="1">
         <v>1.5</v>
@@ -869,15 +869,15 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>6.7799999999999994</v>
+        <v>-3.3899999999999997</v>
       </c>
       <c r="D20" s="2">
         <f t="shared" si="2"/>
-        <v>0.12931034482758619</v>
+        <v>0.12931034482758622</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -892,11 +892,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>-0.75</v>
       </c>
       <c r="D21" s="2">
         <f t="shared" si="2"/>
@@ -915,11 +915,11 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>0.36</v>
+        <v>-0.18</v>
       </c>
       <c r="D22" s="2">
         <f t="shared" si="2"/>
@@ -938,15 +938,15 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>1.8599999999999999</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="D23" s="2">
         <f t="shared" si="2"/>
-        <v>4.3103448275862065E-2</v>
+        <v>4.3103448275862072E-2</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -961,15 +961,15 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
-        <v>0.92999999999999994</v>
+        <v>-0.46499999999999997</v>
       </c>
       <c r="D24" s="2">
         <f t="shared" si="2"/>
-        <v>2.1551724137931032E-2</v>
+        <v>2.1551724137931036E-2</v>
       </c>
       <c r="E24" s="1">
         <v>0.5</v>
@@ -984,15 +984,15 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
-        <v>1.8599999999999999</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="D25" s="2">
         <f t="shared" si="2"/>
-        <v>4.3103448275862065E-2</v>
+        <v>4.3103448275862072E-2</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -1007,15 +1007,15 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.6</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>0.57000000000000006</v>
+        <v>-0.28500000000000003</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="2"/>
-        <v>1.2931034482758617E-2</v>
+        <v>1.2931034482758621E-2</v>
       </c>
       <c r="E26" s="1">
         <v>0.3</v>
@@ -1030,11 +1030,11 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>0.36</v>
+        <v>-0.18</v>
       </c>
       <c r="D27" s="2">
         <f t="shared" si="2"/>
@@ -1053,11 +1053,11 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>-0.75</v>
       </c>
       <c r="D28" s="2">
         <f t="shared" si="2"/>
@@ -1076,15 +1076,15 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>0.92999999999999994</v>
+        <v>-0.46499999999999997</v>
       </c>
       <c r="D29" s="2">
         <f t="shared" si="2"/>
-        <v>2.1551724137931032E-2</v>
+        <v>2.1551724137931036E-2</v>
       </c>
       <c r="E29" s="1">
         <v>0.5</v>
@@ -1099,15 +1099,15 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="1"/>
-        <v>1.8599999999999999</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" si="2"/>
-        <v>4.3103448275862065E-2</v>
+        <v>4.3103448275862072E-2</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -1122,11 +1122,11 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>0.36</v>
+        <v>-0.18</v>
       </c>
       <c r="D31" s="2">
         <f t="shared" si="2"/>

--- a/data/OP2/case18_2_2/case18_operational_data.xlsx
+++ b/data/OP2/case18_2_2/case18_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case18_2_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404D3E4C-C787-B847-9D9C-5268F187CB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A2B29F-59F8-1548-9AAC-03CADE5D0251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="680" windowWidth="50080" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -71023,76 +71023,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>3.7692400000000004</v>
+        <v>1.8846200000000002</v>
       </c>
       <c r="E2" s="1">
-        <v>3.8949733333333341</v>
+        <v>1.947486666666667</v>
       </c>
       <c r="F2" s="1">
-        <v>3.4877199999999995</v>
+        <v>1.7438599999999997</v>
       </c>
       <c r="G2" s="1">
-        <v>3.3058666666666663</v>
+        <v>1.6529333333333331</v>
       </c>
       <c r="H2" s="1">
-        <v>2.7084800000000002</v>
+        <v>1.3542400000000001</v>
       </c>
       <c r="I2" s="1">
-        <v>2.2987733333333336</v>
+        <v>1.1493866666666668</v>
       </c>
       <c r="J2" s="1">
-        <v>2.8112133333333333</v>
+        <v>1.4056066666666667</v>
       </c>
       <c r="K2" s="1">
-        <v>0.48821333333333333</v>
+        <v>0.24410666666666667</v>
       </c>
       <c r="L2" s="1">
-        <v>0.42933333333333334</v>
+        <v>0.21466666666666667</v>
       </c>
       <c r="M2" s="1">
-        <v>0.6259066666666665</v>
+        <v>0.31295333333333325</v>
       </c>
       <c r="N2" s="1">
-        <v>0.3686133333333334</v>
+        <v>0.1843066666666667</v>
       </c>
       <c r="O2" s="1">
-        <v>0.46061333333333332</v>
+        <v>0.23030666666666666</v>
       </c>
       <c r="P2" s="1">
-        <v>0.73385333333333358</v>
+        <v>0.36692666666666679</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.3520933333333334</v>
+        <v>0.67604666666666668</v>
       </c>
       <c r="R2" s="1">
-        <v>1.4425599999999996</v>
+        <v>0.72127999999999981</v>
       </c>
       <c r="S2" s="1">
-        <v>1.4186399999999999</v>
+        <v>0.70931999999999995</v>
       </c>
       <c r="T2" s="1">
-        <v>0.79579999999999995</v>
+        <v>0.39789999999999998</v>
       </c>
       <c r="U2" s="1">
-        <v>1.6210399999999998</v>
+        <v>0.81051999999999991</v>
       </c>
       <c r="V2" s="1">
-        <v>0.95128000000000001</v>
+        <v>0.47564000000000001</v>
       </c>
       <c r="W2" s="1">
-        <v>0.66883999999999988</v>
+        <v>0.33441999999999994</v>
       </c>
       <c r="X2" s="1">
-        <v>1.0156800000000001</v>
+        <v>0.50784000000000007</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.62774666666666668</v>
+        <v>0.31387333333333334</v>
       </c>
       <c r="Z2" s="1">
-        <v>2.8651866666666668</v>
+        <v>1.4325933333333334</v>
       </c>
       <c r="AA2" s="1">
-        <v>3.4539866666666668</v>
+        <v>1.7269933333333334</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -71106,76 +71106,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-8.51</v>
+        <v>-4.2549999999999999</v>
       </c>
       <c r="E3" s="1">
-        <v>-9.1000266666666665</v>
+        <v>-4.5500133333333332</v>
       </c>
       <c r="F3" s="1">
-        <v>-10.234693333333334</v>
+        <v>-5.1173466666666672</v>
       </c>
       <c r="G3" s="1">
-        <v>-11.040306666666666</v>
+        <v>-5.520153333333333</v>
       </c>
       <c r="H3" s="1">
-        <v>-11.800533333333334</v>
+        <v>-5.900266666666667</v>
       </c>
       <c r="I3" s="1">
-        <v>-12.878466666666668</v>
+        <v>-6.439233333333334</v>
       </c>
       <c r="J3" s="1">
-        <v>-12.28844</v>
+        <v>-6.1442199999999998</v>
       </c>
       <c r="K3" s="1">
-        <v>-13.784482666666664</v>
+        <v>-6.8922413333333319</v>
       </c>
       <c r="L3" s="1">
-        <v>-12.502309333333329</v>
+        <v>-6.2511546666666646</v>
       </c>
       <c r="M3" s="1">
-        <v>-18.363843999999997</v>
+        <v>-9.1819219999999984</v>
       </c>
       <c r="N3" s="1">
-        <v>-18.175642666666668</v>
+        <v>-9.0878213333333342</v>
       </c>
       <c r="O3" s="1">
-        <v>-16.615322666666668</v>
+        <v>-8.3076613333333338</v>
       </c>
       <c r="P3" s="1">
-        <v>-15.927162666666666</v>
+        <v>-7.963581333333333</v>
       </c>
       <c r="Q3" s="1">
-        <v>-15.377401333333333</v>
+        <v>-7.6887006666666666</v>
       </c>
       <c r="R3" s="1">
-        <v>-14.494354666666668</v>
+        <v>-7.247177333333334</v>
       </c>
       <c r="S3" s="1">
-        <v>-13.189917333333332</v>
+        <v>-6.594958666666666</v>
       </c>
       <c r="T3" s="1">
-        <v>-12.333336000000001</v>
+        <v>-6.1666680000000005</v>
       </c>
       <c r="U3" s="1">
-        <v>-11.037117333333335</v>
+        <v>-5.5185586666666673</v>
       </c>
       <c r="V3" s="1">
-        <v>-7.0055853333333324</v>
+        <v>-3.5027926666666662</v>
       </c>
       <c r="W3" s="1">
-        <v>-7.8403013333333318</v>
+        <v>-3.9201506666666659</v>
       </c>
       <c r="X3" s="1">
-        <v>-8.2875439999999987</v>
+        <v>-4.1437719999999993</v>
       </c>
       <c r="Y3" s="1">
-        <v>-8.8974733333333322</v>
+        <v>-4.4487366666666661</v>
       </c>
       <c r="Z3" s="1">
-        <v>-7.0689733333333331</v>
+        <v>-3.5344866666666666</v>
       </c>
       <c r="AA3" s="1">
-        <v>-7.511493333333334</v>
+        <v>-3.755746666666667</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -71189,76 +71189,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>8.1983959999999989</v>
+        <v>4.0991979999999995</v>
       </c>
       <c r="E4" s="1">
-        <v>8.7709119999999974</v>
+        <v>4.3854559999999987</v>
       </c>
       <c r="F4" s="1">
-        <v>9.8342173333333331</v>
+        <v>4.9171086666666666</v>
       </c>
       <c r="G4" s="1">
-        <v>10.581870666666669</v>
+        <v>5.2909353333333344</v>
       </c>
       <c r="H4" s="1">
-        <v>11.263406666666663</v>
+        <v>5.6317033333333315</v>
       </c>
       <c r="I4" s="1">
-        <v>12.298866666666667</v>
+        <v>6.1494333333333335</v>
       </c>
       <c r="J4" s="1">
-        <v>11.725399999999999</v>
+        <v>5.8626999999999994</v>
       </c>
       <c r="K4" s="1">
-        <v>13.232022666666666</v>
+        <v>6.6160113333333328</v>
       </c>
       <c r="L4" s="1">
-        <v>12.120356000000001</v>
+        <v>6.0601780000000005</v>
       </c>
       <c r="M4" s="1">
-        <v>13.830237333333331</v>
+        <v>6.9151186666666655</v>
       </c>
       <c r="N4" s="1">
-        <v>13.939134666666666</v>
+        <v>6.969567333333333</v>
       </c>
       <c r="O4" s="1">
-        <v>13.048390666666664</v>
+        <v>6.5241953333333322</v>
       </c>
       <c r="P4" s="1">
-        <v>12.608600000000001</v>
+        <v>6.3043000000000005</v>
       </c>
       <c r="Q4" s="1">
-        <v>12.284514666666666</v>
+        <v>6.1422573333333332</v>
       </c>
       <c r="R4" s="1">
-        <v>11.512512000000001</v>
+        <v>5.7562560000000005</v>
       </c>
       <c r="S4" s="1">
-        <v>10.481468000000001</v>
+        <v>5.2407340000000007</v>
       </c>
       <c r="T4" s="1">
-        <v>9.7642973333333298</v>
+        <v>4.8821486666666649</v>
       </c>
       <c r="U4" s="1">
-        <v>8.7268746666666654</v>
+        <v>4.3634373333333327</v>
       </c>
       <c r="V4" s="1">
-        <v>6.8305093333333327</v>
+        <v>3.4152546666666663</v>
       </c>
       <c r="W4" s="1">
-        <v>7.645322666666666</v>
+        <v>3.822661333333333</v>
       </c>
       <c r="X4" s="1">
-        <v>8.1240293333333344</v>
+        <v>4.0620146666666672</v>
       </c>
       <c r="Y4" s="1">
-        <v>8.7511626666666675</v>
+        <v>4.3755813333333338</v>
       </c>
       <c r="Z4" s="1">
-        <v>6.8095333333333334</v>
+        <v>3.4047666666666667</v>
       </c>
       <c r="AA4" s="1">
-        <v>7.2410133333333349</v>
+        <v>3.6205066666666674</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -71272,76 +71272,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>3.7315476000000012</v>
+        <v>1.8657738000000006</v>
       </c>
       <c r="E5" s="1">
-        <v>3.8949733333333341</v>
+        <v>1.947486666666667</v>
       </c>
       <c r="F5" s="1">
-        <v>3.6272287999999997</v>
+        <v>1.8136143999999998</v>
       </c>
       <c r="G5" s="1">
-        <v>3.3719839999999994</v>
+        <v>1.6859919999999997</v>
       </c>
       <c r="H5" s="1">
-        <v>2.6543104</v>
+        <v>1.3271552</v>
       </c>
       <c r="I5" s="1">
-        <v>2.2068224000000005</v>
+        <v>1.1034112000000003</v>
       </c>
       <c r="J5" s="1">
-        <v>2.8393254666666667</v>
+        <v>1.4196627333333334</v>
       </c>
       <c r="K5" s="1">
-        <v>0.4784490666666667</v>
+        <v>0.23922453333333335</v>
       </c>
       <c r="L5" s="1">
-        <v>0.44650666666666677</v>
+        <v>0.22325333333333339</v>
       </c>
       <c r="M5" s="1">
-        <v>0.65720199999999995</v>
+        <v>0.32860099999999998</v>
       </c>
       <c r="N5" s="1">
-        <v>0.36124106666666672</v>
+        <v>0.18062053333333336</v>
       </c>
       <c r="O5" s="1">
-        <v>0.46521946666666664</v>
+        <v>0.23260973333333332</v>
       </c>
       <c r="P5" s="1">
-        <v>0.73385333333333358</v>
+        <v>0.36692666666666679</v>
       </c>
       <c r="Q5" s="1">
-        <v>1.4196980000000001</v>
+        <v>0.70984900000000006</v>
       </c>
       <c r="R5" s="1">
-        <v>1.4425599999999996</v>
+        <v>0.72127999999999981</v>
       </c>
       <c r="S5" s="1">
-        <v>1.4470127999999998</v>
+        <v>0.72350639999999988</v>
       </c>
       <c r="T5" s="1">
-        <v>0.75600999999999996</v>
+        <v>0.37800499999999998</v>
       </c>
       <c r="U5" s="1">
-        <v>1.7020919999999995</v>
+        <v>0.85104599999999975</v>
       </c>
       <c r="V5" s="1">
-        <v>0.9607928</v>
+        <v>0.4803964</v>
       </c>
       <c r="W5" s="1">
-        <v>0.68890519999999977</v>
+        <v>0.34445259999999989</v>
       </c>
       <c r="X5" s="1">
-        <v>1.0258368000000002</v>
+        <v>0.51291840000000011</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.59635933333333335</v>
+        <v>0.29817966666666668</v>
       </c>
       <c r="Z5" s="1">
-        <v>2.9224904000000005</v>
+        <v>1.4612452000000002</v>
       </c>
       <c r="AA5" s="1">
-        <v>3.4539866666666668</v>
+        <v>1.7269933333333334</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -71355,76 +71355,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-8.51</v>
+        <v>-4.2549999999999999</v>
       </c>
       <c r="E6" s="1">
-        <v>-9.0090263999999998</v>
+        <v>-4.5045131999999999</v>
       </c>
       <c r="F6" s="1">
-        <v>-10.234693333333334</v>
+        <v>-5.1173466666666672</v>
       </c>
       <c r="G6" s="1">
-        <v>-10.488291333333333</v>
+        <v>-5.2441456666666664</v>
       </c>
       <c r="H6" s="1">
-        <v>-11.446517333333333</v>
+        <v>-5.7232586666666663</v>
       </c>
       <c r="I6" s="1">
-        <v>-12.363328000000001</v>
+        <v>-6.1816640000000005</v>
       </c>
       <c r="J6" s="1">
-        <v>-12.4113244</v>
+        <v>-6.2056621999999999</v>
       </c>
       <c r="K6" s="1">
-        <v>-13.784482666666664</v>
+        <v>-6.8922413333333319</v>
       </c>
       <c r="L6" s="1">
-        <v>-12.502309333333329</v>
+        <v>-6.2511546666666646</v>
       </c>
       <c r="M6" s="1">
-        <v>-18.180205559999997</v>
+        <v>-9.0901027799999987</v>
       </c>
       <c r="N6" s="1">
-        <v>-18.539155520000005</v>
+        <v>-9.2695777600000024</v>
       </c>
       <c r="O6" s="1">
-        <v>-16.283016213333333</v>
+        <v>-8.1415081066666666</v>
       </c>
       <c r="P6" s="1">
-        <v>-16.564249173333334</v>
+        <v>-8.2821245866666668</v>
       </c>
       <c r="Q6" s="1">
-        <v>-15.223627319999999</v>
+        <v>-7.6118136599999993</v>
       </c>
       <c r="R6" s="1">
-        <v>-15.074128853333336</v>
+        <v>-7.5370644266666682</v>
       </c>
       <c r="S6" s="1">
-        <v>-13.189917333333332</v>
+        <v>-6.594958666666666</v>
       </c>
       <c r="T6" s="1">
-        <v>-12.086669280000001</v>
+        <v>-6.0433346400000003</v>
       </c>
       <c r="U6" s="1">
-        <v>-10.59563264</v>
+        <v>-5.2978163199999999</v>
       </c>
       <c r="V6" s="1">
-        <v>-7.0055853333333324</v>
+        <v>-3.5027926666666662</v>
       </c>
       <c r="W6" s="1">
-        <v>-7.7618983199999976</v>
+        <v>-3.8809491599999988</v>
       </c>
       <c r="X6" s="1">
-        <v>-8.1217931199999978</v>
+        <v>-4.0608965599999989</v>
       </c>
       <c r="Y6" s="1">
-        <v>-8.6305491333333322</v>
+        <v>-4.3152745666666661</v>
       </c>
       <c r="Z6" s="1">
-        <v>-7.3517322666666667</v>
+        <v>-3.6758661333333333</v>
       </c>
       <c r="AA6" s="1">
-        <v>-7.2110336000000004</v>
+        <v>-3.6055168000000002</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -71438,76 +71438,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>7.788476199999999</v>
+        <v>3.8942380999999995</v>
       </c>
       <c r="E7" s="1">
-        <v>9.0340393599999977</v>
+        <v>4.5170196799999989</v>
       </c>
       <c r="F7" s="1">
-        <v>9.4408486399999987</v>
+        <v>4.7204243199999993</v>
       </c>
       <c r="G7" s="1">
-        <v>10.052777133333334</v>
+        <v>5.0263885666666672</v>
       </c>
       <c r="H7" s="1">
-        <v>10.925504466666665</v>
+        <v>5.4627522333333323</v>
       </c>
       <c r="I7" s="1">
-        <v>12.667832666666669</v>
+        <v>6.3339163333333346</v>
       </c>
       <c r="J7" s="1">
-        <v>11.256383999999999</v>
+        <v>5.6281919999999994</v>
       </c>
       <c r="K7" s="1">
-        <v>12.702741760000002</v>
+        <v>6.3513708800000011</v>
       </c>
       <c r="L7" s="1">
-        <v>12.241559560000001</v>
+        <v>6.1207797800000003</v>
       </c>
       <c r="M7" s="1">
-        <v>13.415330213333332</v>
+        <v>6.7076651066666662</v>
       </c>
       <c r="N7" s="1">
-        <v>13.939134666666666</v>
+        <v>6.969567333333333</v>
       </c>
       <c r="O7" s="1">
-        <v>13.309358479999998</v>
+        <v>6.6546792399999992</v>
       </c>
       <c r="P7" s="1">
-        <v>12.104256000000001</v>
+        <v>6.0521280000000006</v>
       </c>
       <c r="Q7" s="1">
-        <v>12.530204959999997</v>
+        <v>6.2651024799999986</v>
       </c>
       <c r="R7" s="1">
-        <v>12.088137600000003</v>
+        <v>6.0440688000000016</v>
       </c>
       <c r="S7" s="1">
-        <v>10.795912040000003</v>
+        <v>5.3979560200000014</v>
       </c>
       <c r="T7" s="1">
-        <v>9.4713684133333302</v>
+        <v>4.7356842066666651</v>
       </c>
       <c r="U7" s="1">
-        <v>9.0759496533333319</v>
+        <v>4.537974826666666</v>
       </c>
       <c r="V7" s="1">
-        <v>7.1720347999999987</v>
+        <v>3.5860173999999994</v>
       </c>
       <c r="W7" s="1">
-        <v>7.645322666666666</v>
+        <v>3.822661333333333</v>
       </c>
       <c r="X7" s="1">
-        <v>7.7178278666666671</v>
+        <v>3.8589139333333335</v>
       </c>
       <c r="Y7" s="1">
-        <v>9.1887208000000005</v>
+        <v>4.5943604000000002</v>
       </c>
       <c r="Z7" s="1">
-        <v>6.7414379999999987</v>
+        <v>3.3707189999999994</v>
       </c>
       <c r="AA7" s="1">
-        <v>7.2410133333333349</v>
+        <v>3.6205066666666674</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -71521,76 +71521,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>3.6569166480000006</v>
+        <v>1.8284583240000003</v>
       </c>
       <c r="E8" s="1">
-        <v>3.9728727999999998</v>
+        <v>1.9864363999999999</v>
       </c>
       <c r="F8" s="1">
-        <v>3.6635010879999999</v>
+        <v>1.8317505439999999</v>
       </c>
       <c r="G8" s="1">
-        <v>3.2371046399999996</v>
+        <v>1.6185523199999998</v>
       </c>
       <c r="H8" s="1">
-        <v>2.5215948799999999</v>
+        <v>1.2607974399999999</v>
       </c>
       <c r="I8" s="1">
-        <v>2.2288906240000004</v>
+        <v>1.1144453120000002</v>
       </c>
       <c r="J8" s="1">
-        <v>2.8109322120000004</v>
+        <v>1.4054661060000002</v>
       </c>
       <c r="K8" s="1">
-        <v>0.49758702933333332</v>
+        <v>0.24879351466666666</v>
       </c>
       <c r="L8" s="1">
-        <v>0.44650666666666677</v>
+        <v>0.22325333333333339</v>
       </c>
       <c r="M8" s="1">
-        <v>0.62434190000000001</v>
+        <v>0.31217095</v>
       </c>
       <c r="N8" s="1">
-        <v>0.36485347733333334</v>
+        <v>0.18242673866666667</v>
       </c>
       <c r="O8" s="1">
-        <v>0.46521946666666664</v>
+        <v>0.23260973333333332</v>
       </c>
       <c r="P8" s="1">
-        <v>0.72651480000000024</v>
+        <v>0.36325740000000012</v>
       </c>
       <c r="Q8" s="1">
-        <v>1.3487131000000001</v>
+        <v>0.67435655000000005</v>
       </c>
       <c r="R8" s="1">
-        <v>1.3992831999999999</v>
+        <v>0.69964159999999997</v>
       </c>
       <c r="S8" s="1">
-        <v>1.4036024159999998</v>
+        <v>0.7018012079999999</v>
       </c>
       <c r="T8" s="1">
-        <v>0.75600999999999996</v>
+        <v>0.37800499999999998</v>
       </c>
       <c r="U8" s="1">
-        <v>1.6510292399999995</v>
+        <v>0.82551461999999975</v>
       </c>
       <c r="V8" s="1">
-        <v>0.94157694399999992</v>
+        <v>0.47078847199999996</v>
       </c>
       <c r="W8" s="1">
-        <v>0.72335045999999981</v>
+        <v>0.3616752299999999</v>
       </c>
       <c r="X8" s="1">
-        <v>1.0258368000000002</v>
+        <v>0.51291840000000011</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.62021370666666664</v>
+        <v>0.31010685333333332</v>
       </c>
       <c r="Z8" s="1">
-        <v>2.8640405920000003</v>
+        <v>1.4320202960000001</v>
       </c>
       <c r="AA8" s="1">
-        <v>3.3158271999999998</v>
+        <v>1.6579135999999999</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -71604,76 +71604,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-8.0845000000000002</v>
+        <v>-4.0422500000000001</v>
       </c>
       <c r="E9" s="1">
-        <v>-9.0090263999999998</v>
+        <v>-4.5045131999999999</v>
       </c>
       <c r="F9" s="1">
-        <v>-9.7229586666666687</v>
+        <v>-4.8614793333333344</v>
       </c>
       <c r="G9" s="1">
-        <v>-10.488291333333333</v>
+        <v>-5.2441456666666664</v>
       </c>
       <c r="H9" s="1">
-        <v>-11.904378026666668</v>
+        <v>-5.9521890133333342</v>
       </c>
       <c r="I9" s="1">
-        <v>-12.116061440000001</v>
+        <v>-6.0580307200000005</v>
       </c>
       <c r="J9" s="1">
-        <v>-12.783664132</v>
+        <v>-6.3918320660000001</v>
       </c>
       <c r="K9" s="1">
-        <v>-13.508793013333332</v>
+        <v>-6.7543965066666658</v>
       </c>
       <c r="L9" s="1">
-        <v>-13.127424799999995</v>
+        <v>-6.5637123999999973</v>
       </c>
       <c r="M9" s="1">
-        <v>-18.362007615599996</v>
+        <v>-9.181003807799998</v>
       </c>
       <c r="N9" s="1">
-        <v>-17.982980854400004</v>
+        <v>-8.9914904272000022</v>
       </c>
       <c r="O9" s="1">
-        <v>-16.771506699733333</v>
+        <v>-8.3857533498666665</v>
       </c>
       <c r="P9" s="1">
-        <v>-16.398606681600004</v>
+        <v>-8.199303340800002</v>
       </c>
       <c r="Q9" s="1">
-        <v>-15.984808685999999</v>
+        <v>-7.9924043429999996</v>
       </c>
       <c r="R9" s="1">
-        <v>-14.923387564800002</v>
+        <v>-7.4616937824000011</v>
       </c>
       <c r="S9" s="1">
-        <v>-13.189917333333332</v>
+        <v>-6.594958666666666</v>
       </c>
       <c r="T9" s="1">
-        <v>-11.965802587200001</v>
+        <v>-5.9829012936000003</v>
       </c>
       <c r="U9" s="1">
-        <v>-11.019457945600001</v>
+        <v>-5.5097289728000005</v>
       </c>
       <c r="V9" s="1">
-        <v>-7.2157528933333337</v>
+        <v>-3.6078764466666668</v>
       </c>
       <c r="W9" s="1">
-        <v>-7.6842793367999969</v>
+        <v>-3.8421396683999984</v>
       </c>
       <c r="X9" s="1">
-        <v>-8.1217931199999978</v>
+        <v>-4.0608965599999989</v>
       </c>
       <c r="Y9" s="1">
-        <v>-8.1990216766666659</v>
+        <v>-4.099510838333333</v>
       </c>
       <c r="Z9" s="1">
-        <v>-7.2782149439999992</v>
+        <v>-3.6391074719999996</v>
       </c>
       <c r="AA9" s="1">
-        <v>-7.5715852799999999</v>
+        <v>-3.7857926399999999</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -71687,76 +71687,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>7.9442457239999991</v>
+        <v>3.9721228619999995</v>
       </c>
       <c r="E10" s="1">
-        <v>8.5823373919999977</v>
+        <v>4.2911686959999988</v>
       </c>
       <c r="F10" s="1">
-        <v>9.4408486399999987</v>
+        <v>4.7204243199999993</v>
       </c>
       <c r="G10" s="1">
-        <v>9.7511938193333343</v>
+        <v>4.8755969096666671</v>
       </c>
       <c r="H10" s="1">
-        <v>10.379229243333329</v>
+        <v>5.1896146216666645</v>
       </c>
       <c r="I10" s="1">
-        <v>12.034441033333335</v>
+        <v>6.0172205166666677</v>
       </c>
       <c r="J10" s="1">
-        <v>10.693564799999997</v>
+        <v>5.3467823999999986</v>
       </c>
       <c r="K10" s="1">
-        <v>12.067604672000002</v>
+        <v>6.0338023360000008</v>
       </c>
       <c r="L10" s="1">
-        <v>11.996728368800001</v>
+        <v>5.9983641844000006</v>
       </c>
       <c r="M10" s="1">
-        <v>13.683636817600002</v>
+        <v>6.8418184088000009</v>
       </c>
       <c r="N10" s="1">
-        <v>14.21791736</v>
+        <v>7.1089586799999998</v>
       </c>
       <c r="O10" s="1">
-        <v>12.643890556000001</v>
+        <v>6.3219452780000003</v>
       </c>
       <c r="P10" s="1">
-        <v>12.588426240000002</v>
+        <v>6.2942131200000011</v>
       </c>
       <c r="Q10" s="1">
-        <v>12.655507009599999</v>
+        <v>6.3277535047999995</v>
       </c>
       <c r="R10" s="1">
-        <v>12.329900352000003</v>
+        <v>6.1649501760000014</v>
       </c>
       <c r="S10" s="1">
-        <v>10.364075558400001</v>
+        <v>5.1820377792000007</v>
       </c>
       <c r="T10" s="1">
-        <v>9.8502231498666628</v>
+        <v>4.9251115749333314</v>
       </c>
       <c r="U10" s="1">
-        <v>8.7129116671999984</v>
+        <v>4.3564558335999992</v>
       </c>
       <c r="V10" s="1">
-        <v>7.5306365399999988</v>
+        <v>3.7653182699999994</v>
       </c>
       <c r="W10" s="1">
-        <v>7.7217758933333336</v>
+        <v>3.8608879466666668</v>
       </c>
       <c r="X10" s="1">
-        <v>8.0265409813333335</v>
+        <v>4.0132704906666667</v>
       </c>
       <c r="Y10" s="1">
-        <v>9.4643824240000018</v>
+        <v>4.7321912120000009</v>
       </c>
       <c r="Z10" s="1">
-        <v>6.8088523799999985</v>
+        <v>3.4044261899999992</v>
       </c>
       <c r="AA10" s="1">
-        <v>7.6030640000000025</v>
+        <v>3.8015320000000012</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -71770,76 +71770,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>3.5807780000000005</v>
+        <v>1.7903890000000002</v>
       </c>
       <c r="E11" s="1">
-        <v>3.7002246666666667</v>
+        <v>1.8501123333333334</v>
       </c>
       <c r="F11" s="1">
-        <v>3.3133339999999998</v>
+        <v>1.6566669999999999</v>
       </c>
       <c r="G11" s="1">
-        <v>3.1405733333333323</v>
+        <v>1.5702866666666662</v>
       </c>
       <c r="H11" s="1">
-        <v>2.5730559999999998</v>
+        <v>1.2865279999999999</v>
       </c>
       <c r="I11" s="1">
-        <v>2.1838346666666668</v>
+        <v>1.0919173333333334</v>
       </c>
       <c r="J11" s="1">
-        <v>2.6706526666666668</v>
+        <v>1.3353263333333334</v>
       </c>
       <c r="K11" s="1">
-        <v>0.46380266666666664</v>
+        <v>0.23190133333333332</v>
       </c>
       <c r="L11" s="1">
-        <v>0.40786666666666666</v>
+        <v>0.20393333333333333</v>
       </c>
       <c r="M11" s="1">
-        <v>0.59461133333333316</v>
+        <v>0.29730566666666658</v>
       </c>
       <c r="N11" s="1">
-        <v>0.3501826666666667</v>
+        <v>0.17509133333333335</v>
       </c>
       <c r="O11" s="1">
-        <v>0.43758266666666662</v>
+        <v>0.21879133333333331</v>
       </c>
       <c r="P11" s="1">
-        <v>0.69716066666666687</v>
+        <v>0.34858033333333344</v>
       </c>
       <c r="Q11" s="1">
-        <v>1.2844886666666666</v>
+        <v>0.64224433333333331</v>
       </c>
       <c r="R11" s="1">
-        <v>1.3704319999999999</v>
+        <v>0.68521599999999994</v>
       </c>
       <c r="S11" s="1">
-        <v>1.3477079999999997</v>
+        <v>0.67385399999999984</v>
       </c>
       <c r="T11" s="1">
-        <v>0.75600999999999996</v>
+        <v>0.37800499999999998</v>
       </c>
       <c r="U11" s="1">
-        <v>1.5399879999999995</v>
+        <v>0.76999399999999973</v>
       </c>
       <c r="V11" s="1">
-        <v>0.90371599999999985</v>
+        <v>0.45185799999999993</v>
       </c>
       <c r="W11" s="1">
-        <v>0.6353979999999998</v>
+        <v>0.3176989999999999</v>
       </c>
       <c r="X11" s="1">
-        <v>0.96489599999999998</v>
+        <v>0.48244799999999999</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.59635933333333335</v>
+        <v>0.29817966666666668</v>
       </c>
       <c r="Z11" s="1">
-        <v>2.7219273333333334</v>
+        <v>1.3609636666666667</v>
       </c>
       <c r="AA11" s="1">
-        <v>3.2812873333333332</v>
+        <v>1.6406436666666666</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -71853,76 +71853,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-8.4078800000000005</v>
+        <v>-4.2039400000000002</v>
       </c>
       <c r="E12" s="1">
-        <v>-9.0090263999999998</v>
+        <v>-4.5045131999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>-9.2368107333333338</v>
+        <v>-4.6184053666666669</v>
       </c>
       <c r="G12" s="1">
-        <v>-10.488291333333333</v>
+        <v>-5.2441456666666664</v>
       </c>
       <c r="H12" s="1">
-        <v>-11.7853342464</v>
+        <v>-5.8926671231999999</v>
       </c>
       <c r="I12" s="1">
-        <v>-12.600703897599999</v>
+        <v>-6.3003519487999995</v>
       </c>
       <c r="J12" s="1">
-        <v>-12.400154208040002</v>
+        <v>-6.2000771040200009</v>
       </c>
       <c r="K12" s="1">
-        <v>-13.373705083199996</v>
+        <v>-6.6868525415999978</v>
       </c>
       <c r="L12" s="1">
-        <v>-13.389973295999996</v>
+        <v>-6.6949866479999978</v>
       </c>
       <c r="M12" s="1">
-        <v>-17.627527310975996</v>
+        <v>-8.8137636554879979</v>
       </c>
       <c r="N12" s="1">
-        <v>-18.162810662944008</v>
+        <v>-9.0814053314720038</v>
       </c>
       <c r="O12" s="1">
-        <v>-17.274651900725335</v>
+        <v>-8.6373259503626674</v>
       </c>
       <c r="P12" s="1">
-        <v>-15.906648481151999</v>
+        <v>-7.9533242405759994</v>
       </c>
       <c r="Q12" s="1">
-        <v>-15.185568251699998</v>
+        <v>-7.5927841258499988</v>
       </c>
       <c r="R12" s="1">
-        <v>-14.774153689152003</v>
+        <v>-7.3870768445760016</v>
       </c>
       <c r="S12" s="1">
-        <v>-13.189917333333332</v>
+        <v>-6.594958666666666</v>
       </c>
       <c r="T12" s="1">
-        <v>-12.444434690688</v>
+        <v>-6.2222173453440002</v>
       </c>
       <c r="U12" s="1">
-        <v>-10.799068786687998</v>
+        <v>-5.3995343933439992</v>
       </c>
       <c r="V12" s="1">
-        <v>-6.9271227776000002</v>
+        <v>-3.4635613888000001</v>
       </c>
       <c r="W12" s="1">
-        <v>-7.7611221301679976</v>
+        <v>-3.8805610650839988</v>
       </c>
       <c r="X12" s="1">
-        <v>-8.5278827759999984</v>
+        <v>-4.2639413879999992</v>
       </c>
       <c r="Y12" s="1">
-        <v>-8.1990216766666659</v>
+        <v>-4.099510838333333</v>
       </c>
       <c r="Z12" s="1">
-        <v>-7.05986849568</v>
+        <v>-3.52993424784</v>
       </c>
       <c r="AA12" s="1">
-        <v>-7.4201535743999996</v>
+        <v>-3.7100767871999998</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -71936,76 +71936,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>7.5470334377999997</v>
+        <v>3.7735167188999998</v>
       </c>
       <c r="E13" s="1">
-        <v>8.3248672702400004</v>
+        <v>4.1624336351200002</v>
       </c>
       <c r="F13" s="1">
-        <v>9.5352571263999977</v>
+        <v>4.7676285631999988</v>
       </c>
       <c r="G13" s="1">
-        <v>9.5561699429466689</v>
+        <v>4.7780849714733344</v>
       </c>
       <c r="H13" s="1">
-        <v>10.275436950899996</v>
+        <v>5.137718475449998</v>
       </c>
       <c r="I13" s="1">
-        <v>12.154785443666668</v>
+        <v>6.0773927218333341</v>
       </c>
       <c r="J13" s="1">
-        <v>10.693564799999997</v>
+        <v>5.3467823999999986</v>
       </c>
       <c r="K13" s="1">
-        <v>12.18828071872</v>
+        <v>6.0941403593599999</v>
       </c>
       <c r="L13" s="1">
-        <v>11.996728368800001</v>
+        <v>5.9983641844000006</v>
       </c>
       <c r="M13" s="1">
-        <v>14.094145922128002</v>
+        <v>7.0470729610640008</v>
       </c>
       <c r="N13" s="1">
-        <v>13.507021492</v>
+        <v>6.7535107459999999</v>
       </c>
       <c r="O13" s="1">
-        <v>12.011696028199999</v>
+        <v>6.0058480140999997</v>
       </c>
       <c r="P13" s="1">
-        <v>12.966079027200001</v>
+        <v>6.4830395136000005</v>
       </c>
       <c r="Q13" s="1">
-        <v>12.528951939503999</v>
+        <v>6.2644759697519996</v>
       </c>
       <c r="R13" s="1">
-        <v>12.083302344960003</v>
+        <v>6.0416511724800017</v>
       </c>
       <c r="S13" s="1">
-        <v>9.8458717804800013</v>
+        <v>4.9229358902400007</v>
       </c>
       <c r="T13" s="1">
-        <v>10.342734307359997</v>
+        <v>5.1713671536799986</v>
       </c>
       <c r="U13" s="1">
-        <v>9.0614281338879987</v>
+        <v>4.5307140669439994</v>
       </c>
       <c r="V13" s="1">
-        <v>7.6059429053999992</v>
+        <v>3.8029714526999996</v>
       </c>
       <c r="W13" s="1">
-        <v>7.9534291701333339</v>
+        <v>3.976714585066667</v>
       </c>
       <c r="X13" s="1">
-        <v>7.9462755715200011</v>
+        <v>3.9731377857600005</v>
       </c>
       <c r="Y13" s="1">
-        <v>9.842957720960003</v>
+        <v>4.9214788604800015</v>
       </c>
       <c r="Z13" s="1">
-        <v>6.8088523799999985</v>
+        <v>3.4044261899999992</v>
       </c>
       <c r="AA13" s="1">
-        <v>7.7551252800000023</v>
+        <v>3.8775626400000012</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -72019,76 +72019,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>3.7240091200000003</v>
+        <v>1.8620045600000001</v>
       </c>
       <c r="E14" s="1">
-        <v>3.7372269133333336</v>
+        <v>1.8686134566666668</v>
       </c>
       <c r="F14" s="1">
-        <v>3.3133339999999998</v>
+        <v>1.6566669999999999</v>
       </c>
       <c r="G14" s="1">
-        <v>3.2033847999999985</v>
+        <v>1.6016923999999992</v>
       </c>
       <c r="H14" s="1">
-        <v>2.5987865599999997</v>
+        <v>1.2993932799999999</v>
       </c>
       <c r="I14" s="1">
-        <v>2.1183196266666666</v>
+        <v>1.0591598133333333</v>
       </c>
       <c r="J14" s="1">
-        <v>2.7774787733333333</v>
+        <v>1.3887393866666666</v>
       </c>
       <c r="K14" s="1">
-        <v>0.45916464000000001</v>
+        <v>0.22958232000000001</v>
       </c>
       <c r="L14" s="1">
-        <v>0.42010266666666674</v>
+        <v>0.21005133333333337</v>
       </c>
       <c r="M14" s="1">
-        <v>0.58866521999999988</v>
+        <v>0.29433260999999994</v>
       </c>
       <c r="N14" s="1">
-        <v>0.36068814666666665</v>
+        <v>0.18034407333333333</v>
       </c>
       <c r="O14" s="1">
-        <v>0.41570353333333326</v>
+        <v>0.20785176666666663</v>
       </c>
       <c r="P14" s="1">
-        <v>0.69716066666666687</v>
+        <v>0.34858033333333344</v>
       </c>
       <c r="Q14" s="1">
-        <v>1.3230233266666667</v>
+        <v>0.66151166333333333</v>
       </c>
       <c r="R14" s="1">
-        <v>1.3430233599999999</v>
+        <v>0.67151167999999994</v>
       </c>
       <c r="S14" s="1">
-        <v>1.3746621599999995</v>
+        <v>0.68733107999999976</v>
       </c>
       <c r="T14" s="1">
-        <v>0.7257695999999999</v>
+        <v>0.36288479999999995</v>
       </c>
       <c r="U14" s="1">
-        <v>1.4783884799999996</v>
+        <v>0.73919423999999978</v>
       </c>
       <c r="V14" s="1">
-        <v>0.8675673599999999</v>
+        <v>0.43378367999999995</v>
       </c>
       <c r="W14" s="1">
-        <v>0.66716789999999981</v>
+        <v>0.33358394999999991</v>
       </c>
       <c r="X14" s="1">
-        <v>0.93594912000000008</v>
+        <v>0.46797456000000004</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.61425011333333324</v>
+        <v>0.30712505666666662</v>
       </c>
       <c r="Z14" s="1">
-        <v>2.7491466066666668</v>
+        <v>1.3745733033333334</v>
       </c>
       <c r="AA14" s="1">
-        <v>3.2156615866666667</v>
+        <v>1.6078307933333333</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -72102,76 +72102,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-8.4919588000000008</v>
+        <v>-4.2459794000000004</v>
       </c>
       <c r="E15" s="1">
-        <v>-8.8288458720000005</v>
+        <v>-4.4144229360000002</v>
       </c>
       <c r="F15" s="1">
-        <v>-8.8673383040000004</v>
+        <v>-4.4336691520000002</v>
       </c>
       <c r="G15" s="1">
-        <v>-10.068759679999998</v>
+        <v>-5.0343798399999988</v>
       </c>
       <c r="H15" s="1">
-        <v>-12.256747616256002</v>
+        <v>-6.1283738081280008</v>
       </c>
       <c r="I15" s="1">
-        <v>-12.348689819647999</v>
+        <v>-6.1743449098239997</v>
       </c>
       <c r="J15" s="1">
-        <v>-12.1521511238792</v>
+        <v>-6.0760755619396001</v>
       </c>
       <c r="K15" s="1">
-        <v>-12.838756879871994</v>
+        <v>-6.419378439935997</v>
       </c>
       <c r="L15" s="1">
-        <v>-13.523873028959997</v>
+        <v>-6.7619365144799986</v>
       </c>
       <c r="M15" s="1">
-        <v>-17.451252037866237</v>
+        <v>-8.7256260189331183</v>
       </c>
       <c r="N15" s="1">
-        <v>-18.889323089461765</v>
+        <v>-9.4446615447308826</v>
       </c>
       <c r="O15" s="1">
-        <v>-16.929158862710832</v>
+        <v>-8.4645794313554159</v>
       </c>
       <c r="P15" s="1">
-        <v>-15.747581996340481</v>
+        <v>-7.8737909981702403</v>
       </c>
       <c r="Q15" s="1">
-        <v>-14.578145521631996</v>
+        <v>-7.2890727608159978</v>
       </c>
       <c r="R15" s="1">
-        <v>-14.478670615368962</v>
+        <v>-7.2393353076844811</v>
       </c>
       <c r="S15" s="1">
-        <v>-12.530421466666665</v>
+        <v>-6.2652107333333324</v>
       </c>
       <c r="T15" s="1">
-        <v>-12.444434690688</v>
+        <v>-6.2222173453440002</v>
       </c>
       <c r="U15" s="1">
-        <v>-10.691078098821118</v>
+        <v>-5.3455390494105588</v>
       </c>
       <c r="V15" s="1">
-        <v>-6.9271227776000002</v>
+        <v>-3.4635613888000001</v>
       </c>
       <c r="W15" s="1">
-        <v>-7.9163445727713579</v>
+        <v>-3.958172286385679</v>
       </c>
       <c r="X15" s="1">
-        <v>-8.6131616037599983</v>
+        <v>-4.3065808018799991</v>
       </c>
       <c r="Y15" s="1">
-        <v>-8.2810118934333321</v>
+        <v>-4.1405059467166661</v>
       </c>
       <c r="Z15" s="1">
-        <v>-6.7774737558527995</v>
+        <v>-3.3887368779263998</v>
       </c>
       <c r="AA15" s="1">
-        <v>-7.7169597173759996</v>
+        <v>-3.8584798586879998</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -72185,76 +72185,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>7.1696817659099992</v>
+        <v>3.5848408829549996</v>
       </c>
       <c r="E16" s="1">
-        <v>7.9918725794303995</v>
+        <v>3.9959362897151998</v>
       </c>
       <c r="F16" s="1">
-        <v>10.012019982719998</v>
+        <v>5.0060099913599991</v>
       </c>
       <c r="G16" s="1">
-        <v>9.1739231452287999</v>
+        <v>4.5869615726144</v>
       </c>
       <c r="H16" s="1">
-        <v>10.789208798444996</v>
+        <v>5.3946043992224979</v>
       </c>
       <c r="I16" s="1">
-        <v>11.668594025920001</v>
+        <v>5.8342970129600005</v>
       </c>
       <c r="J16" s="1">
-        <v>10.800500447999999</v>
+        <v>5.4002502239999997</v>
       </c>
       <c r="K16" s="1">
-        <v>12.18828071872</v>
+        <v>6.0941403593599999</v>
       </c>
       <c r="L16" s="1">
-        <v>11.396891950360002</v>
+        <v>5.6984459751800012</v>
       </c>
       <c r="M16" s="1">
-        <v>14.376028840570562</v>
+        <v>7.1880144202852811</v>
       </c>
       <c r="N16" s="1">
-        <v>13.23688106216</v>
+        <v>6.6184405310800001</v>
       </c>
       <c r="O16" s="1">
-        <v>12.492163869327998</v>
+        <v>6.2460819346639989</v>
       </c>
       <c r="P16" s="1">
-        <v>12.447435866112</v>
+        <v>6.2237179330560002</v>
       </c>
       <c r="Q16" s="1">
-        <v>12.904820497689117</v>
+        <v>6.4524102488445587</v>
       </c>
       <c r="R16" s="1">
-        <v>12.324968391859203</v>
+        <v>6.1624841959296015</v>
       </c>
       <c r="S16" s="1">
-        <v>9.9443304982848009</v>
+        <v>4.9721652491424004</v>
       </c>
       <c r="T16" s="1">
-        <v>10.549588993507196</v>
+        <v>5.2747944967535982</v>
       </c>
       <c r="U16" s="1">
-        <v>8.8801995712102393</v>
+        <v>4.4400997856051196</v>
       </c>
       <c r="V16" s="1">
-        <v>7.6820023344539985</v>
+        <v>3.8410011672269992</v>
       </c>
       <c r="W16" s="1">
-        <v>7.9534291701333339</v>
+        <v>3.976714585066667</v>
       </c>
       <c r="X16" s="1">
-        <v>8.2641265943807998</v>
+        <v>4.1320632971903999</v>
       </c>
       <c r="Y16" s="1">
-        <v>10.039816875379204</v>
+        <v>5.0199084376896019</v>
       </c>
       <c r="Z16" s="1">
-        <v>6.8769409037999987</v>
+        <v>3.4384704518999993</v>
       </c>
       <c r="AA16" s="1">
-        <v>7.4449202688000033</v>
+        <v>3.7224601344000017</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -72268,76 +72268,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>3.5378086640000004</v>
+        <v>1.7689043320000002</v>
       </c>
       <c r="E17" s="1">
-        <v>3.886715989866667</v>
+        <v>1.9433579949333335</v>
       </c>
       <c r="F17" s="1">
-        <v>3.2802006599999998</v>
+        <v>1.6401003299999999</v>
       </c>
       <c r="G17" s="1">
-        <v>3.3635540399999986</v>
+        <v>1.6817770199999993</v>
       </c>
       <c r="H17" s="1">
-        <v>2.6247744255999996</v>
+        <v>1.3123872127999998</v>
       </c>
       <c r="I17" s="1">
-        <v>2.0971364304000004</v>
+        <v>1.0485682152000002</v>
       </c>
       <c r="J17" s="1">
-        <v>2.6941544101333328</v>
+        <v>1.3470772050666664</v>
       </c>
       <c r="K17" s="1">
-        <v>0.4637562864</v>
+        <v>0.2318781432</v>
       </c>
       <c r="L17" s="1">
-        <v>0.42010266666666674</v>
+        <v>0.21005133333333337</v>
       </c>
       <c r="M17" s="1">
-        <v>0.57100526339999991</v>
+        <v>0.28550263169999995</v>
       </c>
       <c r="N17" s="1">
-        <v>0.3570812652</v>
+        <v>0.1785406326</v>
       </c>
       <c r="O17" s="1">
-        <v>0.41154649799999993</v>
+        <v>0.20577324899999996</v>
       </c>
       <c r="P17" s="1">
-        <v>0.69716066666666687</v>
+        <v>0.34858033333333344</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.3362535599333334</v>
+        <v>0.6681267799666667</v>
       </c>
       <c r="R17" s="1">
-        <v>1.4101745279999998</v>
+        <v>0.70508726399999988</v>
       </c>
       <c r="S17" s="1">
-        <v>1.3059290519999993</v>
+        <v>0.65296452599999966</v>
       </c>
       <c r="T17" s="1">
-        <v>0.70399651199999991</v>
+        <v>0.35199825599999995</v>
       </c>
       <c r="U17" s="1">
-        <v>1.4636045951999996</v>
+        <v>0.73180229759999982</v>
       </c>
       <c r="V17" s="1">
-        <v>0.88491870719999977</v>
+        <v>0.44245935359999988</v>
       </c>
       <c r="W17" s="1">
-        <v>0.66716789999999981</v>
+        <v>0.33358394999999991</v>
       </c>
       <c r="X17" s="1">
-        <v>0.91723013760000016</v>
+        <v>0.45861506880000008</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.61425011333333324</v>
+        <v>0.30712505666666662</v>
       </c>
       <c r="Z17" s="1">
-        <v>2.6391807424000002</v>
+        <v>1.3195903712000001</v>
       </c>
       <c r="AA17" s="1">
-        <v>3.151348354933333</v>
+        <v>1.5756741774666665</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -72351,76 +72351,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-8.4070392120000026</v>
+        <v>-4.2035196060000013</v>
       </c>
       <c r="E18" s="1">
-        <v>-9.181999706880001</v>
+        <v>-4.5909998534400005</v>
       </c>
       <c r="F18" s="1">
-        <v>-8.4239713888000001</v>
+        <v>-4.2119856944</v>
       </c>
       <c r="G18" s="1">
-        <v>-10.169447276799998</v>
+        <v>-5.084723638399999</v>
       </c>
       <c r="H18" s="1">
-        <v>-12.62445004474368</v>
+        <v>-6.3122250223718401</v>
       </c>
       <c r="I18" s="1">
-        <v>-12.472176717844476</v>
+        <v>-6.2360883589222382</v>
       </c>
       <c r="J18" s="1">
-        <v>-11.666065078924033</v>
+        <v>-5.8330325394620166</v>
       </c>
       <c r="K18" s="1">
-        <v>-13.095532017469433</v>
+        <v>-6.5477660087347163</v>
       </c>
       <c r="L18" s="1">
-        <v>-13.659111759249598</v>
+        <v>-6.8295558796247988</v>
       </c>
       <c r="M18" s="1">
-        <v>-16.753201956351589</v>
+        <v>-8.3766009781757944</v>
       </c>
       <c r="N18" s="1">
-        <v>-19.267109551251</v>
+        <v>-9.6335547756255</v>
       </c>
       <c r="O18" s="1">
-        <v>-16.759867274083721</v>
+        <v>-8.3799336370418605</v>
       </c>
       <c r="P18" s="1">
-        <v>-16.220009456230695</v>
+        <v>-8.1100047281153476</v>
       </c>
       <c r="Q18" s="1">
-        <v>-15.015489887280955</v>
+        <v>-7.5077449436404775</v>
       </c>
       <c r="R18" s="1">
-        <v>-15.202604146137411</v>
+        <v>-7.6013020730687053</v>
       </c>
       <c r="S18" s="1">
-        <v>-13.031638325333331</v>
+        <v>-6.5158191626666655</v>
       </c>
       <c r="T18" s="1">
-        <v>-12.07110164996736</v>
+        <v>-6.0355508249836802</v>
       </c>
       <c r="U18" s="1">
-        <v>-11.011810441785753</v>
+        <v>-5.5059052208928767</v>
       </c>
       <c r="V18" s="1">
-        <v>-6.5807666387200001</v>
+        <v>-3.2903833193600001</v>
       </c>
       <c r="W18" s="1">
-        <v>-7.7580176813159305</v>
+        <v>-3.8790088406579653</v>
       </c>
       <c r="X18" s="1">
-        <v>-8.5270299877223987</v>
+        <v>-4.2635149938611994</v>
       </c>
       <c r="Y18" s="1">
-        <v>-8.0325815366303335</v>
+        <v>-4.0162907683151667</v>
       </c>
       <c r="Z18" s="1">
-        <v>-6.6419242807357435</v>
+        <v>-3.3209621403678717</v>
       </c>
       <c r="AA18" s="1">
-        <v>-7.7169597173759996</v>
+        <v>-3.8584798586879998</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -72434,76 +72434,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>6.8111976776144987</v>
+        <v>3.4055988388072493</v>
       </c>
       <c r="E19" s="1">
-        <v>8.1517100310190074</v>
+        <v>4.0758550155095037</v>
       </c>
       <c r="F19" s="1">
-        <v>10.412500782028799</v>
+        <v>5.2062503910143993</v>
       </c>
       <c r="G19" s="1">
-        <v>9.6326193024902409</v>
+        <v>4.8163096512451204</v>
       </c>
       <c r="H19" s="1">
-        <v>11.220777150382794</v>
+        <v>5.6103885751913971</v>
       </c>
       <c r="I19" s="1">
-        <v>11.318536205142401</v>
+        <v>5.6592681025712004</v>
       </c>
       <c r="J19" s="1">
-        <v>11.340525470399998</v>
+        <v>5.6702627351999988</v>
       </c>
       <c r="K19" s="1">
-        <v>12.797694754656</v>
+        <v>6.3988473773279999</v>
       </c>
       <c r="L19" s="1">
-        <v>11.054985191849203</v>
+        <v>5.5274925959246017</v>
       </c>
       <c r="M19" s="1">
-        <v>14.376028840570562</v>
+        <v>7.1880144202852811</v>
       </c>
       <c r="N19" s="1">
-        <v>13.3692498727816</v>
+        <v>6.6846249363907999</v>
       </c>
       <c r="O19" s="1">
-        <v>12.242320591941441</v>
+        <v>6.1211602959707205</v>
       </c>
       <c r="P19" s="1">
-        <v>13.0698076594176</v>
+        <v>6.5349038297088002</v>
       </c>
       <c r="Q19" s="1">
-        <v>12.517675882758446</v>
+        <v>6.2588379413792232</v>
       </c>
       <c r="R19" s="1">
-        <v>11.708719972266245</v>
+        <v>5.8543599861331224</v>
       </c>
       <c r="S19" s="1">
-        <v>9.8448871933019539</v>
+        <v>4.922443596650977</v>
       </c>
       <c r="T19" s="1">
-        <v>10.549588993507196</v>
+        <v>5.2747944967535982</v>
       </c>
       <c r="U19" s="1">
-        <v>9.057803562634442</v>
+        <v>4.528901781317221</v>
       </c>
       <c r="V19" s="1">
-        <v>7.9892824278321584</v>
+        <v>3.9946412139160792</v>
       </c>
       <c r="W19" s="1">
-        <v>8.192032045237335</v>
+        <v>4.0960160226186675</v>
       </c>
       <c r="X19" s="1">
-        <v>8.2641265943807998</v>
+        <v>4.1320632971903999</v>
       </c>
       <c r="Y19" s="1">
-        <v>9.8390205378716189</v>
+        <v>4.9195102689358094</v>
       </c>
       <c r="Z19" s="1">
-        <v>6.6018632676479987</v>
+        <v>3.3009316338239993</v>
       </c>
       <c r="AA19" s="1">
-        <v>7.221572660736002</v>
+        <v>3.610786330368001</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -72517,76 +72517,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>3.9388558000000011</v>
+        <v>1.9694279000000006</v>
       </c>
       <c r="E20" s="1">
-        <v>4.0702471333333339</v>
+        <v>2.0351235666666669</v>
       </c>
       <c r="F20" s="1">
-        <v>3.6446674000000008</v>
+        <v>1.8223337000000004</v>
       </c>
       <c r="G20" s="1">
-        <v>3.4546306666666662</v>
+        <v>1.7273153333333331</v>
       </c>
       <c r="H20" s="1">
-        <v>2.8303615999999998</v>
+        <v>1.4151807999999999</v>
       </c>
       <c r="I20" s="1">
-        <v>2.4022181333333337</v>
+        <v>1.2011090666666668</v>
       </c>
       <c r="J20" s="1">
-        <v>2.9377179333333334</v>
+        <v>1.4688589666666667</v>
       </c>
       <c r="K20" s="1">
-        <v>0.51018293333333342</v>
+        <v>0.25509146666666671</v>
       </c>
       <c r="L20" s="1">
-        <v>0.44865333333333335</v>
+        <v>0.22432666666666667</v>
       </c>
       <c r="M20" s="1">
-        <v>0.65407246666666652</v>
+        <v>0.32703623333333326</v>
       </c>
       <c r="N20" s="1">
-        <v>0.38520093333333333</v>
+        <v>0.19260046666666666</v>
       </c>
       <c r="O20" s="1">
-        <v>0.48134093333333322</v>
+        <v>0.24067046666666661</v>
       </c>
       <c r="P20" s="1">
-        <v>0.7668767333333335</v>
+        <v>0.38343836666666675</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.4129375333333334</v>
+        <v>0.70646876666666669</v>
       </c>
       <c r="R20" s="1">
-        <v>1.5074752</v>
+        <v>0.75373760000000001</v>
       </c>
       <c r="S20" s="1">
-        <v>1.4824787999999998</v>
+        <v>0.74123939999999988</v>
       </c>
       <c r="T20" s="1">
-        <v>0.83161099999999999</v>
+        <v>0.41580549999999999</v>
       </c>
       <c r="U20" s="1">
-        <v>1.6939867999999996</v>
+        <v>0.84699339999999979</v>
       </c>
       <c r="V20" s="1">
-        <v>0.99408759999999996</v>
+        <v>0.49704379999999998</v>
       </c>
       <c r="W20" s="1">
-        <v>0.69893779999999983</v>
+        <v>0.34946889999999992</v>
       </c>
       <c r="X20" s="1">
-        <v>1.0613856000000002</v>
+        <v>0.53069280000000008</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.65599526666666663</v>
+        <v>0.32799763333333332</v>
       </c>
       <c r="Z20" s="1">
-        <v>2.994120066666667</v>
+        <v>1.4970600333333335</v>
       </c>
       <c r="AA20" s="1">
-        <v>3.6094160666666664</v>
+        <v>1.8047080333333332</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -72600,76 +72600,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-8.1548280356400031</v>
+        <v>-4.0774140178200016</v>
       </c>
       <c r="E21" s="1">
-        <v>-9.6410996922240013</v>
+        <v>-4.8205498461120007</v>
       </c>
       <c r="F21" s="1">
-        <v>-8.1712522471359978</v>
+        <v>-4.0856261235679989</v>
       </c>
       <c r="G21" s="1">
-        <v>-10.372836222335998</v>
+        <v>-5.186418111167999</v>
       </c>
       <c r="H21" s="1">
-        <v>-13.129428046533429</v>
+        <v>-6.5647140232667143</v>
       </c>
       <c r="I21" s="1">
-        <v>-12.472176717844476</v>
+        <v>-6.2360883589222382</v>
       </c>
       <c r="J21" s="1">
-        <v>-11.782725729713276</v>
+        <v>-5.8913628648566378</v>
       </c>
       <c r="K21" s="1">
-        <v>-12.964576697294738</v>
+        <v>-6.4822883486473692</v>
       </c>
       <c r="L21" s="1">
-        <v>-13.795702876842091</v>
+        <v>-6.8978514384210454</v>
       </c>
       <c r="M21" s="1">
-        <v>-16.753201956351589</v>
+        <v>-8.3766009781757944</v>
       </c>
       <c r="N21" s="1">
-        <v>-19.074438455738491</v>
+        <v>-9.5372192278692456</v>
       </c>
       <c r="O21" s="1">
-        <v>-17.430261965047073</v>
+        <v>-8.7151309825235366</v>
       </c>
       <c r="P21" s="1">
-        <v>-16.220009456230695</v>
+        <v>-8.1100047281153476</v>
       </c>
       <c r="Q21" s="1">
-        <v>-15.465954583899382</v>
+        <v>-7.7329772919496911</v>
       </c>
       <c r="R21" s="1">
-        <v>-14.746526021753288</v>
+        <v>-7.3732630108766442</v>
       </c>
       <c r="S21" s="1">
-        <v>-12.771005558826664</v>
+        <v>-6.3855027794133319</v>
       </c>
       <c r="T21" s="1">
-        <v>-11.467546567468993</v>
+        <v>-5.7337732837344966</v>
       </c>
       <c r="U21" s="1">
-        <v>-11.011810441785753</v>
+        <v>-5.5059052208928767</v>
       </c>
       <c r="V21" s="1">
-        <v>-6.7123819714943993</v>
+        <v>-3.3561909857471997</v>
       </c>
       <c r="W21" s="1">
-        <v>-7.9907582117554083</v>
+        <v>-3.9953791058777042</v>
       </c>
       <c r="X21" s="1">
-        <v>-8.8681111872312943</v>
+        <v>-4.4340555936156472</v>
       </c>
       <c r="Y21" s="1">
-        <v>-7.8719299058977272</v>
+        <v>-3.9359649529488636</v>
       </c>
       <c r="Z21" s="1">
-        <v>-6.6419242807357435</v>
+        <v>-3.3209621403678717</v>
       </c>
       <c r="AA21" s="1">
-        <v>-7.9484685088972782</v>
+        <v>-3.9742342544486391</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -72683,76 +72683,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>6.4706377937337747</v>
+        <v>3.2353188968668873</v>
       </c>
       <c r="E22" s="1">
-        <v>8.314744231639386</v>
+        <v>4.157372115819693</v>
       </c>
       <c r="F22" s="1">
-        <v>10.724875805489662</v>
+        <v>5.3624379027448308</v>
       </c>
       <c r="G22" s="1">
-        <v>9.4399669164404347</v>
+        <v>4.7199834582202174</v>
       </c>
       <c r="H22" s="1">
-        <v>11.445192693390451</v>
+        <v>5.7225963466952257</v>
       </c>
       <c r="I22" s="1">
-        <v>11.205350843090976</v>
+        <v>5.6026754215454879</v>
       </c>
       <c r="J22" s="1">
-        <v>11.000309706287998</v>
+        <v>5.5001548531439992</v>
       </c>
       <c r="K22" s="1">
-        <v>13.181625597295678</v>
+        <v>6.5908127986478391</v>
       </c>
       <c r="L22" s="1">
-        <v>11.607734451441663</v>
+        <v>5.8038672257208317</v>
       </c>
       <c r="M22" s="1">
-        <v>14.807309705787681</v>
+        <v>7.4036548528938404</v>
       </c>
       <c r="N22" s="1">
-        <v>13.101864875325965</v>
+        <v>6.5509324376629827</v>
       </c>
       <c r="O22" s="1">
-        <v>12.48716700378027</v>
+        <v>6.2435835018901349</v>
       </c>
       <c r="P22" s="1">
-        <v>13.592599965794305</v>
+        <v>6.7962999828971524</v>
       </c>
       <c r="Q22" s="1">
-        <v>12.893206159241197</v>
+        <v>6.4466030796205986</v>
       </c>
       <c r="R22" s="1">
-        <v>11.357458373098256</v>
+        <v>5.6787291865491278</v>
       </c>
       <c r="S22" s="1">
-        <v>9.7464383213689327</v>
+        <v>4.8732191606844664</v>
       </c>
       <c r="T22" s="1">
-        <v>10.76058077337734</v>
+        <v>5.38029038668867</v>
       </c>
       <c r="U22" s="1">
-        <v>8.7860694557554115</v>
+        <v>4.3930347278777058</v>
       </c>
       <c r="V22" s="1">
-        <v>8.2289609006671238</v>
+        <v>4.1144804503335619</v>
       </c>
       <c r="W22" s="1">
-        <v>8.5197133270468282</v>
+        <v>4.2598566635234141</v>
       </c>
       <c r="X22" s="1">
-        <v>8.1814853284369935</v>
+        <v>4.0907426642184967</v>
       </c>
       <c r="Y22" s="1">
-        <v>9.740630332492902</v>
+        <v>4.870315166246451</v>
       </c>
       <c r="Z22" s="1">
-        <v>6.7339005330009583</v>
+        <v>3.3669502665004791</v>
       </c>
       <c r="AA22" s="1">
-        <v>7.293788387343362</v>
+        <v>3.646894193671681</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -72766,76 +72766,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>4.1357985900000012</v>
+        <v>2.0678992950000006</v>
       </c>
       <c r="E23" s="1">
-        <v>4.2737594899999998</v>
+        <v>2.1368797449999999</v>
       </c>
       <c r="F23" s="1">
-        <v>3.4988807039999998</v>
+        <v>1.7494403519999999</v>
       </c>
       <c r="G23" s="1">
-        <v>3.3509917466666663</v>
+        <v>1.6754958733333332</v>
       </c>
       <c r="H23" s="1">
-        <v>2.8020579839999997</v>
+        <v>1.4010289919999999</v>
       </c>
       <c r="I23" s="1">
-        <v>2.3541737706666672</v>
+        <v>1.1770868853333336</v>
       </c>
       <c r="J23" s="1">
-        <v>2.9083407539999997</v>
+        <v>1.4541703769999998</v>
       </c>
       <c r="K23" s="1">
-        <v>0.51528476266666667</v>
+        <v>0.25764238133333334</v>
       </c>
       <c r="L23" s="1">
-        <v>0.43968026666666665</v>
+        <v>0.21984013333333333</v>
       </c>
       <c r="M23" s="1">
-        <v>0.66061319133333318</v>
+        <v>0.33030659566666659</v>
       </c>
       <c r="N23" s="1">
-        <v>0.40060897066666673</v>
+        <v>0.20030448533333337</v>
       </c>
       <c r="O23" s="1">
-        <v>0.50059457066666668</v>
+        <v>0.25029728533333334</v>
       </c>
       <c r="P23" s="1">
-        <v>0.75153919866666685</v>
+        <v>0.37576959933333343</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.4694550346666668</v>
+        <v>0.73472751733333341</v>
       </c>
       <c r="R23" s="1">
-        <v>1.5828489599999997</v>
+        <v>0.79142447999999987</v>
       </c>
       <c r="S23" s="1">
-        <v>1.40835486</v>
+        <v>0.70417742999999999</v>
       </c>
       <c r="T23" s="1">
-        <v>0.85655933000000006</v>
+        <v>0.42827966500000003</v>
       </c>
       <c r="U23" s="1">
-        <v>1.7617462719999997</v>
+        <v>0.88087313599999983</v>
       </c>
       <c r="V23" s="1">
-        <v>0.9742058480000001</v>
+        <v>0.48710292400000005</v>
       </c>
       <c r="W23" s="1">
-        <v>0.69194842199999984</v>
+        <v>0.34597421099999992</v>
       </c>
       <c r="X23" s="1">
-        <v>1.0613856000000002</v>
+        <v>0.53069280000000008</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.67567512466666668</v>
+        <v>0.33783756233333334</v>
       </c>
       <c r="Z23" s="1">
-        <v>3.1438260700000007</v>
+        <v>1.5719130350000003</v>
       </c>
       <c r="AA23" s="1">
-        <v>3.6816043880000002</v>
+        <v>1.8408021940000001</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -72849,76 +72849,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-8.2363763159964041</v>
+        <v>-4.118188157998202</v>
       </c>
       <c r="E24" s="1">
-        <v>-9.9303326829907217</v>
+        <v>-4.9651663414953608</v>
       </c>
       <c r="F24" s="1">
-        <v>-8.0078272021932779</v>
+        <v>-4.003913601096639</v>
       </c>
       <c r="G24" s="1">
-        <v>-10.165379497889278</v>
+        <v>-5.082689748944639</v>
       </c>
       <c r="H24" s="1">
-        <v>-13.260722326998765</v>
+        <v>-6.6303611634993826</v>
       </c>
       <c r="I24" s="1">
-        <v>-12.098011416309141</v>
+        <v>-6.0490057081545707</v>
       </c>
       <c r="J24" s="1">
-        <v>-11.547071215119011</v>
+        <v>-5.7735356075595057</v>
       </c>
       <c r="K24" s="1">
-        <v>-13.223868231240631</v>
+        <v>-6.6119341156203157</v>
       </c>
       <c r="L24" s="1">
-        <v>-14.347530991915775</v>
+        <v>-7.1737654959578876</v>
       </c>
       <c r="M24" s="1">
-        <v>-17.255798015042135</v>
+        <v>-8.6278990075210675</v>
       </c>
       <c r="N24" s="1">
-        <v>-18.311460917508953</v>
+        <v>-9.1557304587544763</v>
       </c>
       <c r="O24" s="1">
-        <v>-17.953169823998486</v>
+        <v>-8.9765849119992431</v>
       </c>
       <c r="P24" s="1">
-        <v>-15.733409172543778</v>
+        <v>-7.8667045862718892</v>
       </c>
       <c r="Q24" s="1">
-        <v>-15.156635492221396</v>
+        <v>-7.5783177461106979</v>
       </c>
       <c r="R24" s="1">
-        <v>-14.746526021753288</v>
+        <v>-7.3732630108766442</v>
       </c>
       <c r="S24" s="1">
-        <v>-12.260165336473596</v>
+        <v>-6.1300826682367981</v>
       </c>
       <c r="T24" s="1">
-        <v>-11.582222033143681</v>
+        <v>-5.7911110165718407</v>
       </c>
       <c r="U24" s="1">
-        <v>-10.461219919696466</v>
+        <v>-5.2306099598482332</v>
       </c>
       <c r="V24" s="1">
-        <v>-6.4438866926346243</v>
+        <v>-3.2219433463173122</v>
       </c>
       <c r="W24" s="1">
-        <v>-7.9907582117554083</v>
+        <v>-3.9953791058777042</v>
       </c>
       <c r="X24" s="1">
-        <v>-9.2228356347205462</v>
+        <v>-4.6114178173602731</v>
       </c>
       <c r="Y24" s="1">
-        <v>-7.635772008720795</v>
+        <v>-3.8178860043603975</v>
       </c>
       <c r="Z24" s="1">
-        <v>-6.7747627663504595</v>
+        <v>-3.3873813831752297</v>
       </c>
       <c r="AA24" s="1">
-        <v>-7.8689838238083061</v>
+        <v>-3.934491911904153</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -72932,76 +72932,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>6.4059314157964371</v>
+        <v>3.2029657078982186</v>
       </c>
       <c r="E25" s="1">
-        <v>8.314744231639386</v>
+        <v>4.157372115819693</v>
       </c>
       <c r="F25" s="1">
-        <v>10.188632015215179</v>
+        <v>5.0943160076075893</v>
       </c>
       <c r="G25" s="1">
-        <v>9.6287662547692445</v>
+        <v>4.8143831273846223</v>
       </c>
       <c r="H25" s="1">
-        <v>11.674096547258261</v>
+        <v>5.8370482736291303</v>
       </c>
       <c r="I25" s="1">
-        <v>11.541511368383704</v>
+        <v>5.7707556841918519</v>
       </c>
       <c r="J25" s="1">
-        <v>11.110312803350878</v>
+        <v>5.5551564016754389</v>
       </c>
       <c r="K25" s="1">
-        <v>13.181625597295678</v>
+        <v>6.5908127986478391</v>
       </c>
       <c r="L25" s="1">
-        <v>11.027347728869579</v>
+        <v>5.5136738644347894</v>
       </c>
       <c r="M25" s="1">
-        <v>15.399602094019187</v>
+        <v>7.6998010470095934</v>
       </c>
       <c r="N25" s="1">
-        <v>13.494920821585746</v>
+        <v>6.7474604107928728</v>
       </c>
       <c r="O25" s="1">
-        <v>12.612038673818072</v>
+        <v>6.3060193369090358</v>
       </c>
       <c r="P25" s="1">
-        <v>13.592599965794305</v>
+        <v>6.7962999828971524</v>
       </c>
       <c r="Q25" s="1">
-        <v>12.764274097648787</v>
+        <v>6.3821370488243936</v>
       </c>
       <c r="R25" s="1">
-        <v>10.789585454443342</v>
+        <v>5.3947927272216711</v>
       </c>
       <c r="S25" s="1">
-        <v>9.2591164053004853</v>
+        <v>4.6295582026502426</v>
       </c>
       <c r="T25" s="1">
-        <v>10.437763350176018</v>
+        <v>5.2188816750880092</v>
       </c>
       <c r="U25" s="1">
-        <v>8.6103480666403041</v>
+        <v>4.305174033320152</v>
       </c>
       <c r="V25" s="1">
-        <v>8.2289609006671238</v>
+        <v>4.1144804503335619</v>
       </c>
       <c r="W25" s="1">
-        <v>8.7753047268582325</v>
+        <v>4.3876523634291162</v>
       </c>
       <c r="X25" s="1">
-        <v>7.7724110620151423</v>
+        <v>3.8862055310075712</v>
       </c>
       <c r="Y25" s="1">
-        <v>10.227661849117547</v>
+        <v>5.1138309245587736</v>
       </c>
       <c r="Z25" s="1">
-        <v>6.5992225223409386</v>
+        <v>3.2996112611704693</v>
       </c>
       <c r="AA25" s="1">
-        <v>7.5126020389636627</v>
+        <v>3.7563010194818314</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -73015,76 +73015,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>4.2598725477000015</v>
+        <v>2.1299362738500007</v>
       </c>
       <c r="E26" s="1">
-        <v>4.3164970848999999</v>
+        <v>2.15824854245</v>
       </c>
       <c r="F26" s="1">
-        <v>3.4638918969600003</v>
+        <v>1.7319459484800002</v>
       </c>
       <c r="G26" s="1">
-        <v>3.5185413339999996</v>
+        <v>1.7592706669999998</v>
       </c>
       <c r="H26" s="1">
-        <v>2.8300785638400003</v>
+        <v>1.4150392819200002</v>
       </c>
       <c r="I26" s="1">
-        <v>2.3541737706666672</v>
+        <v>1.1770868853333336</v>
       </c>
       <c r="J26" s="1">
-        <v>2.7629237162999996</v>
+        <v>1.3814618581499998</v>
       </c>
       <c r="K26" s="1">
-        <v>0.48952052453333339</v>
+        <v>0.24476026226666669</v>
       </c>
       <c r="L26" s="1">
-        <v>0.41769625333333332</v>
+        <v>0.20884812666666666</v>
       </c>
       <c r="M26" s="1">
-        <v>0.64079479559333319</v>
+        <v>0.32039739779666659</v>
       </c>
       <c r="N26" s="1">
-        <v>0.39660288096000001</v>
+        <v>0.19830144048000001</v>
       </c>
       <c r="O26" s="1">
-        <v>0.51060646207999993</v>
+        <v>0.25530323103999997</v>
       </c>
       <c r="P26" s="1">
-        <v>0.7365084146933335</v>
+        <v>0.36825420734666675</v>
       </c>
       <c r="Q26" s="1">
-        <v>1.5429277864000002</v>
+        <v>0.77146389320000008</v>
       </c>
       <c r="R26" s="1">
-        <v>1.6619914079999998</v>
+        <v>0.83099570399999989</v>
       </c>
       <c r="S26" s="1">
-        <v>1.4787726029999997</v>
+        <v>0.73938630149999984</v>
       </c>
       <c r="T26" s="1">
-        <v>0.86512492330000013</v>
+        <v>0.43256246165000006</v>
       </c>
       <c r="U26" s="1">
-        <v>1.7617462719999997</v>
+        <v>0.88087313599999983</v>
       </c>
       <c r="V26" s="1">
-        <v>0.9742058480000001</v>
+        <v>0.48710292400000005</v>
       </c>
       <c r="W26" s="1">
-        <v>0.66427048511999987</v>
+        <v>0.33213524255999993</v>
       </c>
       <c r="X26" s="1">
-        <v>1.0295440320000002</v>
+        <v>0.51477201600000011</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.68243187591333332</v>
+        <v>0.34121593795666666</v>
       </c>
       <c r="Z26" s="1">
-        <v>3.0495112879000001</v>
+        <v>1.5247556439500001</v>
       </c>
       <c r="AA26" s="1">
-        <v>3.7920525196399999</v>
+        <v>1.8960262598199999</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -73098,76 +73098,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-8.6481951317962231</v>
+        <v>-4.3240975658981116</v>
       </c>
       <c r="E27" s="1">
-        <v>-9.8310293561608137</v>
+        <v>-4.9155146780804069</v>
       </c>
       <c r="F27" s="1">
-        <v>-7.9277489301713464</v>
+        <v>-3.9638744650856732</v>
       </c>
       <c r="G27" s="1">
-        <v>-9.8604181129525994</v>
+        <v>-4.9302090564762997</v>
       </c>
       <c r="H27" s="1">
-        <v>-13.12811510372878</v>
+        <v>-6.5640575518643898</v>
       </c>
       <c r="I27" s="1">
-        <v>-12.460951758798418</v>
+        <v>-6.2304758793992088</v>
       </c>
       <c r="J27" s="1">
-        <v>-10.969717654363059</v>
+        <v>-5.4848588271815295</v>
       </c>
       <c r="K27" s="1">
-        <v>-13.091629548928227</v>
+        <v>-6.5458147744641133</v>
       </c>
       <c r="L27" s="1">
-        <v>-13.917105062158301</v>
+        <v>-6.9585525310791505</v>
       </c>
       <c r="M27" s="1">
-        <v>-17.773471955493402</v>
+        <v>-8.8867359777467012</v>
       </c>
       <c r="N27" s="1">
-        <v>-18.311460917508953</v>
+        <v>-9.1557304587544763</v>
       </c>
       <c r="O27" s="1">
-        <v>-17.953169823998486</v>
+        <v>-8.9765849119992431</v>
       </c>
       <c r="P27" s="1">
-        <v>-15.418740989092903</v>
+        <v>-7.7093704945464516</v>
       </c>
       <c r="Q27" s="1">
-        <v>-15.156635492221396</v>
+        <v>-7.5783177461106979</v>
       </c>
       <c r="R27" s="1">
-        <v>-15.041456542188355</v>
+        <v>-7.5207282710941774</v>
       </c>
       <c r="S27" s="1">
-        <v>-12.505368643203068</v>
+        <v>-6.2526843216015342</v>
       </c>
       <c r="T27" s="1">
-        <v>-11.929688694137994</v>
+        <v>-5.9648443470689969</v>
       </c>
       <c r="U27" s="1">
-        <v>-10.461219919696466</v>
+        <v>-5.2306099598482332</v>
       </c>
       <c r="V27" s="1">
-        <v>-6.5727644264873177</v>
+        <v>-3.2863822132436589</v>
       </c>
       <c r="W27" s="1">
-        <v>-8.3103885402256257</v>
+        <v>-4.1551942701128128</v>
       </c>
       <c r="X27" s="1">
-        <v>-8.9461505656789306</v>
+        <v>-4.4730752828394653</v>
       </c>
       <c r="Y27" s="1">
-        <v>-7.7121297288080015</v>
+        <v>-3.8560648644040008</v>
       </c>
       <c r="Z27" s="1">
-        <v>-6.4360246280329365</v>
+        <v>-3.2180123140164683</v>
       </c>
       <c r="AA27" s="1">
-        <v>-8.0263635002844733</v>
+        <v>-4.0131817501422367</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -73181,76 +73181,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>6.2137534733225444</v>
+        <v>3.1068767366612722</v>
       </c>
       <c r="E28" s="1">
-        <v>8.065301904690207</v>
+        <v>4.0326509523451035</v>
       </c>
       <c r="F28" s="1">
-        <v>10.188632015215179</v>
+        <v>5.0943160076075893</v>
       </c>
       <c r="G28" s="1">
-        <v>9.9176292424123194</v>
+        <v>4.9588146212061597</v>
       </c>
       <c r="H28" s="1">
-        <v>12.257801374621174</v>
+        <v>6.1289006873105869</v>
       </c>
       <c r="I28" s="1">
-        <v>11.426096254699866</v>
+        <v>5.7130481273499329</v>
       </c>
       <c r="J28" s="1">
-        <v>11.665828443518421</v>
+        <v>5.8329142217592107</v>
       </c>
       <c r="K28" s="1">
-        <v>12.917993085349766</v>
+        <v>6.4589965426748828</v>
       </c>
       <c r="L28" s="1">
-        <v>10.917074251580884</v>
+        <v>5.4585371257904418</v>
       </c>
       <c r="M28" s="1">
-        <v>16.16958219872015</v>
+        <v>8.0847910993600749</v>
       </c>
       <c r="N28" s="1">
-        <v>14.034717654449176</v>
+        <v>7.0173588272245881</v>
       </c>
       <c r="O28" s="1">
-        <v>12.233677513603531</v>
+        <v>6.1168387568017657</v>
       </c>
       <c r="P28" s="1">
-        <v>13.592599965794305</v>
+        <v>6.7962999828971524</v>
       </c>
       <c r="Q28" s="1">
-        <v>13.274845061554736</v>
+        <v>6.6374225307773678</v>
       </c>
       <c r="R28" s="1">
-        <v>10.789585454443342</v>
+        <v>5.3947927272216711</v>
       </c>
       <c r="S28" s="1">
-        <v>9.0739340771944743</v>
+        <v>4.5369670385972372</v>
       </c>
       <c r="T28" s="1">
-        <v>10.124630449670738</v>
+        <v>5.0623152248353689</v>
       </c>
       <c r="U28" s="1">
-        <v>9.040865469972319</v>
+        <v>4.5204327349861595</v>
       </c>
       <c r="V28" s="1">
-        <v>8.2289609006671238</v>
+        <v>4.1144804503335619</v>
       </c>
       <c r="W28" s="1">
-        <v>8.6875516795896512</v>
+        <v>4.3437758397948256</v>
       </c>
       <c r="X28" s="1">
-        <v>8.0833075044957479</v>
+        <v>4.0416537522478739</v>
       </c>
       <c r="Y28" s="1">
-        <v>9.9208319936440201</v>
+        <v>4.9604159968220101</v>
       </c>
       <c r="Z28" s="1">
-        <v>6.7971991980111666</v>
+        <v>3.3985995990055833</v>
       </c>
       <c r="AA28" s="1">
-        <v>7.2872239777947527</v>
+        <v>3.6436119888973764</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -73264,76 +73264,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>3.7419130100000007</v>
+        <v>1.8709565050000003</v>
       </c>
       <c r="E29" s="1">
-        <v>3.8667347766666667</v>
+        <v>1.9333673883333333</v>
       </c>
       <c r="F29" s="1">
-        <v>3.4624340300000003</v>
+        <v>1.7312170150000001</v>
       </c>
       <c r="G29" s="1">
-        <v>3.2818991333333329</v>
+        <v>1.6409495666666665</v>
       </c>
       <c r="H29" s="1">
-        <v>2.6888435200000003</v>
+        <v>1.3444217600000001</v>
       </c>
       <c r="I29" s="1">
-        <v>2.2821072266666667</v>
+        <v>1.1410536133333333</v>
       </c>
       <c r="J29" s="1">
-        <v>2.7908320366666666</v>
+        <v>1.3954160183333333</v>
       </c>
       <c r="K29" s="1">
-        <v>0.48467378666666677</v>
+        <v>0.24233689333333339</v>
       </c>
       <c r="L29" s="1">
-        <v>0.42622066666666664</v>
+        <v>0.21311033333333332</v>
       </c>
       <c r="M29" s="1">
-        <v>0.6213688433333332</v>
+        <v>0.3106844216666666</v>
       </c>
       <c r="N29" s="1">
-        <v>0.36594088666666669</v>
+        <v>0.18297044333333334</v>
       </c>
       <c r="O29" s="1">
-        <v>0.45727388666666652</v>
+        <v>0.22863694333333326</v>
       </c>
       <c r="P29" s="1">
-        <v>0.72853289666666676</v>
+        <v>0.36426644833333338</v>
       </c>
       <c r="Q29" s="1">
-        <v>1.3422906566666668</v>
+        <v>0.6711453283333334</v>
       </c>
       <c r="R29" s="1">
-        <v>1.4321014400000001</v>
+        <v>0.71605072000000003</v>
       </c>
       <c r="S29" s="1">
-        <v>1.4083548599999995</v>
+        <v>0.70417742999999977</v>
       </c>
       <c r="T29" s="1">
-        <v>0.79003044999999983</v>
+        <v>0.39501522499999991</v>
       </c>
       <c r="U29" s="1">
-        <v>1.6092874599999998</v>
+        <v>0.80464372999999989</v>
       </c>
       <c r="V29" s="1">
-        <v>0.94438321999999986</v>
+        <v>0.47219160999999993</v>
       </c>
       <c r="W29" s="1">
-        <v>0.66399090999999988</v>
+        <v>0.33199545499999994</v>
       </c>
       <c r="X29" s="1">
-        <v>1.00831632</v>
+        <v>0.50415816000000002</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.62319550333333329</v>
+        <v>0.31159775166666664</v>
       </c>
       <c r="Z29" s="1">
-        <v>2.8444140633333337</v>
+        <v>1.4222070316666668</v>
       </c>
       <c r="AA29" s="1">
-        <v>3.428945263333333</v>
+        <v>1.7144726316666665</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -73347,76 +73347,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-8.5617131804782609</v>
+        <v>-4.2808565902391305</v>
       </c>
       <c r="E30" s="1">
-        <v>-9.8310293561608137</v>
+        <v>-4.9155146780804069</v>
       </c>
       <c r="F30" s="1">
-        <v>-7.6899164622662068</v>
+        <v>-3.8449582311331034</v>
       </c>
       <c r="G30" s="1">
-        <v>-10.254834837470703</v>
+        <v>-5.1274174187353516</v>
       </c>
       <c r="H30" s="1">
-        <v>-13.653239707877932</v>
+        <v>-6.8266198539389658</v>
       </c>
       <c r="I30" s="1">
-        <v>-12.959389829150354</v>
+        <v>-6.4796949145751768</v>
       </c>
       <c r="J30" s="1">
-        <v>-11.518203537081211</v>
+        <v>-5.7591017685406056</v>
       </c>
       <c r="K30" s="1">
-        <v>-13.615294730885358</v>
+        <v>-6.807647365442679</v>
       </c>
       <c r="L30" s="1">
-        <v>-14.334618214023052</v>
+        <v>-7.1673091070115262</v>
       </c>
       <c r="M30" s="1">
-        <v>-18.12894139460327</v>
+        <v>-9.0644706973016351</v>
       </c>
       <c r="N30" s="1">
-        <v>-18.494575526684041</v>
+        <v>-9.2472877633420207</v>
       </c>
       <c r="O30" s="1">
-        <v>-18.13270152223847</v>
+        <v>-9.0663507611192351</v>
       </c>
       <c r="P30" s="1">
-        <v>-14.801991349529187</v>
+        <v>-7.4009956747645935</v>
       </c>
       <c r="Q30" s="1">
-        <v>-14.550370072532539</v>
+        <v>-7.2751850362662696</v>
       </c>
       <c r="R30" s="1">
-        <v>-15.342285673032121</v>
+        <v>-7.6711428365160605</v>
       </c>
       <c r="S30" s="1">
-        <v>-12.630422329635101</v>
+        <v>-6.3152111648175504</v>
       </c>
       <c r="T30" s="1">
-        <v>-12.048985581079373</v>
+        <v>-6.0244927905396866</v>
       </c>
       <c r="U30" s="1">
-        <v>-10.775056517287359</v>
+        <v>-5.3875282586436795</v>
       </c>
       <c r="V30" s="1">
-        <v>-6.2441262051629502</v>
+        <v>-3.1220631025814751</v>
       </c>
       <c r="W30" s="1">
-        <v>-8.3934924256278816</v>
+        <v>-4.1967462128139408</v>
       </c>
       <c r="X30" s="1">
-        <v>-8.5883045430517733</v>
+        <v>-4.2941522715258866</v>
       </c>
       <c r="Y30" s="1">
-        <v>-7.9434936206722417</v>
+        <v>-3.9717468103361209</v>
       </c>
       <c r="Z30" s="1">
-        <v>-6.5647451205935958</v>
+        <v>-3.2823725602967979</v>
       </c>
       <c r="AA30" s="1">
-        <v>-8.4276816752986967</v>
+        <v>-4.2138408376493484</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -73430,76 +73430,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>6.4623036122554458</v>
+        <v>3.2311518061277229</v>
       </c>
       <c r="E31" s="1">
-        <v>8.1459549237371078</v>
+        <v>4.0729774618685539</v>
       </c>
       <c r="F31" s="1">
-        <v>10.596177295823786</v>
+        <v>5.2980886479118929</v>
       </c>
       <c r="G31" s="1">
-        <v>10.115981827260565</v>
+        <v>5.0579909136302827</v>
       </c>
       <c r="H31" s="1">
-        <v>12.625535415859808</v>
+        <v>6.312767707929904</v>
       </c>
       <c r="I31" s="1">
-        <v>11.197574329605871</v>
+        <v>5.5987871648029355</v>
       </c>
       <c r="J31" s="1">
-        <v>11.082537021342498</v>
+        <v>5.5412685106712489</v>
       </c>
       <c r="K31" s="1">
-        <v>12.917993085349766</v>
+        <v>6.4589965426748828</v>
       </c>
       <c r="L31" s="1">
-        <v>11.135415736612503</v>
+        <v>5.5677078683062513</v>
       </c>
       <c r="M31" s="1">
-        <v>16.978061308656155</v>
+        <v>8.4890306543280776</v>
       </c>
       <c r="N31" s="1">
-        <v>13.754023301360194</v>
+        <v>6.8770116506800969</v>
       </c>
       <c r="O31" s="1">
-        <v>12.233677513603531</v>
+        <v>6.1168387568017657</v>
       </c>
       <c r="P31" s="1">
-        <v>14.136303964426075</v>
+        <v>7.0681519822130374</v>
       </c>
       <c r="Q31" s="1">
-        <v>12.611102808476998</v>
+        <v>6.305551404238499</v>
       </c>
       <c r="R31" s="1">
-        <v>10.789585454443342</v>
+        <v>5.3947927272216711</v>
       </c>
       <c r="S31" s="1">
-        <v>9.5276307810541976</v>
+        <v>4.7638153905270988</v>
       </c>
       <c r="T31" s="1">
-        <v>10.023384145174031</v>
+        <v>5.0116920725870155</v>
       </c>
       <c r="U31" s="1">
-        <v>8.8600481605728714</v>
+        <v>4.4300240802864357</v>
       </c>
       <c r="V31" s="1">
-        <v>8.3935401186804679</v>
+        <v>4.1967700593402339</v>
       </c>
       <c r="W31" s="1">
-        <v>8.9481782299773389</v>
+        <v>4.4740891149886695</v>
       </c>
       <c r="X31" s="1">
-        <v>8.2449736545856638</v>
+        <v>4.1224868272928319</v>
       </c>
       <c r="Y31" s="1">
-        <v>9.6232070338346993</v>
+        <v>4.8116035169173497</v>
       </c>
       <c r="Z31" s="1">
-        <v>6.8651711899912788</v>
+        <v>3.4325855949956394</v>
       </c>
       <c r="AA31" s="1">
-        <v>7.3600962175726998</v>
+        <v>3.6800481087863499</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -73513,76 +73513,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>3.7044938799000007</v>
+        <v>1.8522469399500003</v>
       </c>
       <c r="E32" s="1">
-        <v>4.0600715155000007</v>
+        <v>2.0300357577500003</v>
       </c>
       <c r="F32" s="1">
-        <v>3.4624340300000003</v>
+        <v>1.7312170150000001</v>
       </c>
       <c r="G32" s="1">
-        <v>3.1178041766666662</v>
+        <v>1.5589020883333331</v>
       </c>
       <c r="H32" s="1">
-        <v>2.6619550848000002</v>
+        <v>1.3309775424000001</v>
       </c>
       <c r="I32" s="1">
-        <v>2.1680018653333337</v>
+        <v>1.0840009326666669</v>
       </c>
       <c r="J32" s="1">
-        <v>2.6791987551999998</v>
+        <v>1.3395993775999999</v>
       </c>
       <c r="K32" s="1">
-        <v>0.49921400026666679</v>
+        <v>0.2496070001333334</v>
       </c>
       <c r="L32" s="1">
-        <v>0.42622066666666664</v>
+        <v>0.21311033333333332</v>
       </c>
       <c r="M32" s="1">
-        <v>0.60894146646666647</v>
+        <v>0.30447073323333324</v>
       </c>
       <c r="N32" s="1">
-        <v>0.36228147780000003</v>
+        <v>0.18114073890000001</v>
       </c>
       <c r="O32" s="1">
-        <v>0.46184662553333317</v>
+        <v>0.23092331276666658</v>
       </c>
       <c r="P32" s="1">
-        <v>0.7212475677000002</v>
+        <v>0.3606237838500001</v>
       </c>
       <c r="Q32" s="1">
-        <v>1.3288677500999999</v>
+        <v>0.66443387504999996</v>
       </c>
       <c r="R32" s="1">
-        <v>1.4464224543999997</v>
+        <v>0.72321122719999986</v>
       </c>
       <c r="S32" s="1">
-        <v>1.3520206655999998</v>
+        <v>0.67601033279999989</v>
       </c>
       <c r="T32" s="1">
-        <v>0.79003044999999983</v>
+        <v>0.39501522499999991</v>
       </c>
       <c r="U32" s="1">
-        <v>1.6897518329999996</v>
+        <v>0.84487591649999982</v>
       </c>
       <c r="V32" s="1">
-        <v>0.90660789120000007</v>
+        <v>0.45330394560000004</v>
       </c>
       <c r="W32" s="1">
-        <v>0.67727072819999978</v>
+        <v>0.33863536409999989</v>
       </c>
       <c r="X32" s="1">
-        <v>0.96798366720000006</v>
+        <v>0.48399183360000003</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.5982676831999999</v>
+        <v>0.29913384159999995</v>
       </c>
       <c r="Z32" s="1">
-        <v>2.8159699227000003</v>
+        <v>1.4079849613500002</v>
       </c>
       <c r="AA32" s="1">
-        <v>3.428945263333333</v>
+        <v>1.7144726316666665</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -73596,76 +73596,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-8.3904789168686946</v>
+        <v>-4.1952394584343473</v>
       </c>
       <c r="E33" s="1">
-        <v>-9.6344087690375986</v>
+        <v>-4.8172043845187993</v>
       </c>
       <c r="F33" s="1">
-        <v>-7.5361181330208815</v>
+        <v>-3.7680590665104408</v>
       </c>
       <c r="G33" s="1">
-        <v>-9.9471897923465793</v>
+        <v>-4.9735948961732896</v>
       </c>
       <c r="H33" s="1">
-        <v>-14.335901693271827</v>
+        <v>-7.1679508466359136</v>
       </c>
       <c r="I33" s="1">
-        <v>-12.570608134275844</v>
+        <v>-6.2853040671379219</v>
       </c>
       <c r="J33" s="1">
-        <v>-11.748567607822835</v>
+        <v>-5.8742838039114176</v>
       </c>
       <c r="K33" s="1">
-        <v>-13.479141783576503</v>
+        <v>-6.7395708917882517</v>
       </c>
       <c r="L33" s="1">
-        <v>-13.904579667602361</v>
+        <v>-6.9522898338011805</v>
       </c>
       <c r="M33" s="1">
-        <v>-17.585073152765172</v>
+        <v>-8.7925365763825862</v>
       </c>
       <c r="N33" s="1">
-        <v>-17.569846750349836</v>
+        <v>-8.7849233751749178</v>
       </c>
       <c r="O33" s="1">
-        <v>-19.039336598350395</v>
+        <v>-9.5196682991751977</v>
       </c>
       <c r="P33" s="1">
-        <v>-15.246051090015063</v>
+        <v>-7.6230255450075317</v>
       </c>
       <c r="Q33" s="1">
-        <v>-14.841377473983188</v>
+        <v>-7.4206887369915941</v>
       </c>
       <c r="R33" s="1">
-        <v>-15.955977099953408</v>
+        <v>-7.977988549976704</v>
       </c>
       <c r="S33" s="1">
-        <v>-13.135639222820503</v>
+        <v>-6.5678196114102514</v>
       </c>
       <c r="T33" s="1">
-        <v>-11.928495725268581</v>
+        <v>-5.9642478626342905</v>
       </c>
       <c r="U33" s="1">
-        <v>-10.667305952114488</v>
+        <v>-5.3336529760572438</v>
       </c>
       <c r="V33" s="1">
-        <v>-6.3065674672145802</v>
+        <v>-3.1532837336072901</v>
       </c>
       <c r="W33" s="1">
-        <v>-8.3934924256278816</v>
+        <v>-4.1967462128139408</v>
       </c>
       <c r="X33" s="1">
-        <v>-8.7600706339128092</v>
+        <v>-4.3800353169564046</v>
       </c>
       <c r="Y33" s="1">
-        <v>-8.340668301705854</v>
+        <v>-4.170334150852927</v>
       </c>
       <c r="Z33" s="1">
-        <v>-6.8929823766232756</v>
+        <v>-3.4464911883116378</v>
       </c>
       <c r="AA33" s="1">
-        <v>-8.0905744082867503</v>
+        <v>-4.0452872041433752</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -73679,76 +73679,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>6.1391884316426735</v>
+        <v>3.0695942158213367</v>
       </c>
       <c r="E34" s="1">
-        <v>8.3903335714492204</v>
+        <v>4.1951667857246102</v>
       </c>
       <c r="F34" s="1">
-        <v>10.066368431032597</v>
+        <v>5.0331842155162985</v>
       </c>
       <c r="G34" s="1">
-        <v>9.7113425541701446</v>
+        <v>4.8556712770850723</v>
       </c>
       <c r="H34" s="1">
-        <v>11.99425864506682</v>
+        <v>5.9971293225334099</v>
       </c>
       <c r="I34" s="1">
-        <v>11.533501559494047</v>
+        <v>5.7667507797470234</v>
       </c>
       <c r="J34" s="1">
-        <v>10.639235540488798</v>
+        <v>5.319617770244399</v>
       </c>
       <c r="K34" s="1">
-        <v>12.272093431082277</v>
+        <v>6.1360467155411387</v>
       </c>
       <c r="L34" s="1">
-        <v>11.580832366077003</v>
+        <v>5.7904161830385013</v>
       </c>
       <c r="M34" s="1">
-        <v>16.129158243223348</v>
+        <v>8.0645791216116738</v>
       </c>
       <c r="N34" s="1">
-        <v>13.066322136292184</v>
+        <v>6.5331610681460921</v>
       </c>
       <c r="O34" s="1">
-        <v>12.845361389283708</v>
+        <v>6.422680694641854</v>
       </c>
       <c r="P34" s="1">
-        <v>14.419030043714594</v>
+        <v>7.209515021857297</v>
       </c>
       <c r="Q34" s="1">
-        <v>12.863324864646538</v>
+        <v>6.431662432323269</v>
       </c>
       <c r="R34" s="1">
-        <v>11.005377163532211</v>
+        <v>5.5026885817661055</v>
       </c>
       <c r="S34" s="1">
-        <v>9.5276307810541976</v>
+        <v>4.7638153905270988</v>
       </c>
       <c r="T34" s="1">
-        <v>10.123617986625771</v>
+        <v>5.0618089933128854</v>
       </c>
       <c r="U34" s="1">
-        <v>8.5942467157556859</v>
+        <v>4.2971233578778429</v>
       </c>
       <c r="V34" s="1">
-        <v>8.6453463222408811</v>
+        <v>4.3226731611204405</v>
       </c>
       <c r="W34" s="1">
-        <v>9.127141794576886</v>
+        <v>4.563570897288443</v>
       </c>
       <c r="X34" s="1">
-        <v>7.8327249718563801</v>
+        <v>3.91636248592819</v>
       </c>
       <c r="Y34" s="1">
-        <v>9.5269749634963521</v>
+        <v>4.763487481748176</v>
       </c>
       <c r="Z34" s="1">
-        <v>6.5219126304917152</v>
+        <v>3.2609563152458576</v>
       </c>
       <c r="AA34" s="1">
-        <v>7.5808991040998803</v>
+        <v>3.7904495520499402</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -73762,76 +73762,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>3.7044938799000007</v>
+        <v>1.8522469399500003</v>
       </c>
       <c r="E35" s="1">
-        <v>4.222474376120001</v>
+        <v>2.1112371880600005</v>
       </c>
       <c r="F35" s="1">
-        <v>3.4624340300000003</v>
+        <v>1.7312170150000001</v>
       </c>
       <c r="G35" s="1">
-        <v>3.0554480931333328</v>
+        <v>1.5277240465666664</v>
       </c>
       <c r="H35" s="1">
-        <v>2.5288573305600006</v>
+        <v>1.2644286652800003</v>
       </c>
       <c r="I35" s="1">
-        <v>2.1246418280266668</v>
+        <v>1.0623209140133334</v>
       </c>
       <c r="J35" s="1">
-        <v>2.54523881744</v>
+        <v>1.27261940872</v>
       </c>
       <c r="K35" s="1">
-        <v>0.48922972026133354</v>
+        <v>0.24461486013066677</v>
       </c>
       <c r="L35" s="1">
-        <v>0.42622066666666664</v>
+        <v>0.21311033333333332</v>
       </c>
       <c r="M35" s="1">
-        <v>0.6150308811313332</v>
+        <v>0.3075154405656666</v>
       </c>
       <c r="N35" s="1">
-        <v>0.38039555169</v>
+        <v>0.190197775845</v>
       </c>
       <c r="O35" s="1">
-        <v>0.45722815927799987</v>
+        <v>0.22861407963899993</v>
       </c>
       <c r="P35" s="1">
-        <v>0.75730994608500024</v>
+        <v>0.37865497304250012</v>
       </c>
       <c r="Q35" s="1">
-        <v>1.3554451051019998</v>
+        <v>0.67772255255099989</v>
       </c>
       <c r="R35" s="1">
-        <v>1.4753509034879997</v>
+        <v>0.73767545174399984</v>
       </c>
       <c r="S35" s="1">
-        <v>1.3114600456319998</v>
+        <v>0.6557300228159999</v>
       </c>
       <c r="T35" s="1">
-        <v>0.81373136349999997</v>
+        <v>0.40686568174999999</v>
       </c>
       <c r="U35" s="1">
-        <v>1.6390592780099995</v>
+        <v>0.81952963900499975</v>
       </c>
       <c r="V35" s="1">
-        <v>0.94287220684799999</v>
+        <v>0.471436103424</v>
       </c>
       <c r="W35" s="1">
-        <v>0.65695260635399977</v>
+        <v>0.32847630317699988</v>
       </c>
       <c r="X35" s="1">
-        <v>0.91958448384000002</v>
+        <v>0.45979224192000001</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.59228500636799997</v>
+        <v>0.29614250318399998</v>
       </c>
       <c r="Z35" s="1">
-        <v>2.8722893211540002</v>
+        <v>1.4361446605770001</v>
       </c>
       <c r="AA35" s="1">
-        <v>3.3946558107000002</v>
+        <v>1.6973279053500001</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -73845,76 +73845,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-8.8100028627121301</v>
+        <v>-4.405001431356065</v>
       </c>
       <c r="E36" s="1">
-        <v>-10.116129207489479</v>
+        <v>-5.0580646037447394</v>
       </c>
       <c r="F36" s="1">
-        <v>-7.7622016770115074</v>
+        <v>-3.8811008385057537</v>
       </c>
       <c r="G36" s="1">
-        <v>-10.146133588193512</v>
+        <v>-5.0730667940967562</v>
       </c>
       <c r="H36" s="1">
-        <v>-14.622619727137264</v>
+        <v>-7.3113098635686322</v>
       </c>
       <c r="I36" s="1">
-        <v>-13.199138540989637</v>
+        <v>-6.5995692704948183</v>
       </c>
       <c r="J36" s="1">
-        <v>-11.396110579588148</v>
+        <v>-5.6980552897940742</v>
       </c>
       <c r="K36" s="1">
-        <v>-13.748724619248035</v>
+        <v>-6.8743623096240176</v>
       </c>
       <c r="L36" s="1">
-        <v>-13.765533870926339</v>
+        <v>-6.8827669354631693</v>
       </c>
       <c r="M36" s="1">
-        <v>-17.05752095818222</v>
+        <v>-8.52876047909111</v>
       </c>
       <c r="N36" s="1">
-        <v>-16.69135441283235</v>
+        <v>-8.3456772064161751</v>
       </c>
       <c r="O36" s="1">
-        <v>-18.658549866383385</v>
+        <v>-9.3292749331916927</v>
       </c>
       <c r="P36" s="1">
-        <v>-14.483748535514309</v>
+        <v>-7.2418742677571544</v>
       </c>
       <c r="Q36" s="1">
-        <v>-14.692963699243357</v>
+        <v>-7.3464818496216786</v>
       </c>
       <c r="R36" s="1">
-        <v>-16.753775954951077</v>
+        <v>-8.3768879774755387</v>
       </c>
       <c r="S36" s="1">
-        <v>-13.52970839950512</v>
+        <v>-6.76485419975256</v>
       </c>
       <c r="T36" s="1">
-        <v>-11.332070939005149</v>
+        <v>-5.6660354695025745</v>
       </c>
       <c r="U36" s="1">
-        <v>-11.200671249720209</v>
+        <v>-5.6003356248601044</v>
       </c>
       <c r="V36" s="1">
-        <v>-6.3696331418867258</v>
+        <v>-3.1848165709433629</v>
       </c>
       <c r="W36" s="1">
-        <v>-8.5613622741404374</v>
+        <v>-4.2806811370702187</v>
       </c>
       <c r="X36" s="1">
-        <v>-8.4972685148954223</v>
+        <v>-4.2486342574477112</v>
       </c>
       <c r="Y36" s="1">
-        <v>-8.0070415696376198</v>
+        <v>-4.0035207848188099</v>
       </c>
       <c r="Z36" s="1">
-        <v>-7.1687016716882068</v>
+        <v>-3.5843508358441034</v>
       </c>
       <c r="AA36" s="1">
-        <v>-7.9287629201210139</v>
+        <v>-3.964381460060507</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -73928,76 +73928,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>6.1391884316426735</v>
+        <v>3.0695942158213367</v>
       </c>
       <c r="E37" s="1">
-        <v>8.2225269000202363</v>
+        <v>4.1112634500101182</v>
       </c>
       <c r="F37" s="1">
-        <v>10.066368431032597</v>
+        <v>5.0331842155162985</v>
       </c>
       <c r="G37" s="1">
-        <v>9.2257754264616363</v>
+        <v>4.6128877132308181</v>
       </c>
       <c r="H37" s="1">
-        <v>12.354086404418824</v>
+        <v>6.1770432022094122</v>
       </c>
       <c r="I37" s="1">
-        <v>12.110176637468749</v>
+        <v>6.0550883187343745</v>
       </c>
       <c r="J37" s="1">
-        <v>11.064804962108349</v>
+        <v>5.5324024810541745</v>
       </c>
       <c r="K37" s="1">
-        <v>12.517535299703921</v>
+        <v>6.2587676498519604</v>
       </c>
       <c r="L37" s="1">
-        <v>11.580832366077003</v>
+        <v>5.7904161830385013</v>
       </c>
       <c r="M37" s="1">
-        <v>16.451741408087809</v>
+        <v>8.2258707040439045</v>
       </c>
       <c r="N37" s="1">
-        <v>13.588975021743872</v>
+        <v>6.794487510871936</v>
       </c>
       <c r="O37" s="1">
-        <v>13.230722230962217</v>
+        <v>6.6153611154811083</v>
       </c>
       <c r="P37" s="1">
-        <v>13.698078541528867</v>
+        <v>6.8490392707644334</v>
       </c>
       <c r="Q37" s="1">
-        <v>12.220158621414212</v>
+        <v>6.1100793107071061</v>
       </c>
       <c r="R37" s="1">
-        <v>11.225484706802854</v>
+        <v>5.6127423534014271</v>
       </c>
       <c r="S37" s="1">
-        <v>9.3370781654331143</v>
+        <v>4.6685390827165572</v>
       </c>
       <c r="T37" s="1">
-        <v>10.326090346358287</v>
+        <v>5.1630451731791434</v>
       </c>
       <c r="U37" s="1">
-        <v>8.3364193142830167</v>
+        <v>4.1682096571415084</v>
       </c>
       <c r="V37" s="1">
-        <v>8.9911601751305152</v>
+        <v>4.4955800875652576</v>
       </c>
       <c r="W37" s="1">
-        <v>8.9445989586853472</v>
+        <v>4.4722994793426736</v>
       </c>
       <c r="X37" s="1">
-        <v>7.7543977221378162</v>
+        <v>3.8771988610689081</v>
       </c>
       <c r="Y37" s="1">
-        <v>9.5269749634963521</v>
+        <v>4.763487481748176</v>
       </c>
       <c r="Z37" s="1">
-        <v>6.2610361252720459</v>
+        <v>3.1305180626360229</v>
       </c>
       <c r="AA37" s="1">
-        <v>7.5808991040998803</v>
+        <v>3.7904495520499402</v>
       </c>
     </row>
   </sheetData>

--- a/data/OP2/case18_2_2/case18_operational_data.xlsx
+++ b/data/OP2/case18_2_2/case18_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case18_2_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A2B29F-59F8-1548-9AAC-03CADE5D0251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CCF92C-D1F0-A24B-8E11-EE9B3C0FCC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71023,76 +71023,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>1.8846200000000002</v>
+        <v>1.2564133333333334</v>
       </c>
       <c r="E2" s="1">
-        <v>1.947486666666667</v>
+        <v>1.2983244444444446</v>
       </c>
       <c r="F2" s="1">
-        <v>1.7438599999999997</v>
+        <v>1.1625733333333332</v>
       </c>
       <c r="G2" s="1">
-        <v>1.6529333333333331</v>
+        <v>1.1019555555555554</v>
       </c>
       <c r="H2" s="1">
-        <v>1.3542400000000001</v>
+        <v>0.90282666666666678</v>
       </c>
       <c r="I2" s="1">
-        <v>1.1493866666666668</v>
+        <v>0.76625777777777782</v>
       </c>
       <c r="J2" s="1">
-        <v>1.4056066666666667</v>
+        <v>0.93707111111111108</v>
       </c>
       <c r="K2" s="1">
-        <v>0.24410666666666667</v>
+        <v>0.16273777777777779</v>
       </c>
       <c r="L2" s="1">
-        <v>0.21466666666666667</v>
+        <v>0.14311111111111111</v>
       </c>
       <c r="M2" s="1">
-        <v>0.31295333333333325</v>
+        <v>0.20863555555555549</v>
       </c>
       <c r="N2" s="1">
-        <v>0.1843066666666667</v>
+        <v>0.12287111111111114</v>
       </c>
       <c r="O2" s="1">
-        <v>0.23030666666666666</v>
+        <v>0.15353777777777777</v>
       </c>
       <c r="P2" s="1">
-        <v>0.36692666666666679</v>
+        <v>0.24461777777777785</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.67604666666666668</v>
+        <v>0.45069777777777781</v>
       </c>
       <c r="R2" s="1">
-        <v>0.72127999999999981</v>
+        <v>0.48085333333333319</v>
       </c>
       <c r="S2" s="1">
-        <v>0.70931999999999995</v>
+        <v>0.47287999999999997</v>
       </c>
       <c r="T2" s="1">
-        <v>0.39789999999999998</v>
+        <v>0.26526666666666665</v>
       </c>
       <c r="U2" s="1">
-        <v>0.81051999999999991</v>
+        <v>0.54034666666666664</v>
       </c>
       <c r="V2" s="1">
-        <v>0.47564000000000001</v>
+        <v>0.31709333333333334</v>
       </c>
       <c r="W2" s="1">
-        <v>0.33441999999999994</v>
+        <v>0.22294666666666663</v>
       </c>
       <c r="X2" s="1">
-        <v>0.50784000000000007</v>
+        <v>0.33856000000000003</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.31387333333333334</v>
+        <v>0.2092488888888889</v>
       </c>
       <c r="Z2" s="1">
-        <v>1.4325933333333334</v>
+        <v>0.95506222222222226</v>
       </c>
       <c r="AA2" s="1">
-        <v>1.7269933333333334</v>
+        <v>1.1513288888888888</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -71106,76 +71106,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-4.2549999999999999</v>
+        <v>-2.8366666666666664</v>
       </c>
       <c r="E3" s="1">
-        <v>-4.5500133333333332</v>
+        <v>-3.0333422222222222</v>
       </c>
       <c r="F3" s="1">
-        <v>-5.1173466666666672</v>
+        <v>-3.4115644444444446</v>
       </c>
       <c r="G3" s="1">
-        <v>-5.520153333333333</v>
+        <v>-3.6801022222222222</v>
       </c>
       <c r="H3" s="1">
-        <v>-5.900266666666667</v>
+        <v>-3.9335111111111112</v>
       </c>
       <c r="I3" s="1">
-        <v>-6.439233333333334</v>
+        <v>-4.292822222222223</v>
       </c>
       <c r="J3" s="1">
-        <v>-6.1442199999999998</v>
+        <v>-4.0961466666666668</v>
       </c>
       <c r="K3" s="1">
-        <v>-6.8922413333333319</v>
+        <v>-4.5948275555555549</v>
       </c>
       <c r="L3" s="1">
-        <v>-6.2511546666666646</v>
+        <v>-4.1674364444444434</v>
       </c>
       <c r="M3" s="1">
-        <v>-9.1819219999999984</v>
+        <v>-6.1212813333333322</v>
       </c>
       <c r="N3" s="1">
-        <v>-9.0878213333333342</v>
+        <v>-6.0585475555555561</v>
       </c>
       <c r="O3" s="1">
-        <v>-8.3076613333333338</v>
+        <v>-5.5384408888888892</v>
       </c>
       <c r="P3" s="1">
-        <v>-7.963581333333333</v>
+        <v>-5.3090542222222217</v>
       </c>
       <c r="Q3" s="1">
-        <v>-7.6887006666666666</v>
+        <v>-5.1258004444444447</v>
       </c>
       <c r="R3" s="1">
-        <v>-7.247177333333334</v>
+        <v>-4.8314515555555557</v>
       </c>
       <c r="S3" s="1">
-        <v>-6.594958666666666</v>
+        <v>-4.3966391111111109</v>
       </c>
       <c r="T3" s="1">
-        <v>-6.1666680000000005</v>
+        <v>-4.1111120000000003</v>
       </c>
       <c r="U3" s="1">
-        <v>-5.5185586666666673</v>
+        <v>-3.6790391111111114</v>
       </c>
       <c r="V3" s="1">
-        <v>-3.5027926666666662</v>
+        <v>-2.3351951111111107</v>
       </c>
       <c r="W3" s="1">
-        <v>-3.9201506666666659</v>
+        <v>-2.6134337777777774</v>
       </c>
       <c r="X3" s="1">
-        <v>-4.1437719999999993</v>
+        <v>-2.7625146666666662</v>
       </c>
       <c r="Y3" s="1">
-        <v>-4.4487366666666661</v>
+        <v>-2.9658244444444439</v>
       </c>
       <c r="Z3" s="1">
-        <v>-3.5344866666666666</v>
+        <v>-2.3563244444444442</v>
       </c>
       <c r="AA3" s="1">
-        <v>-3.755746666666667</v>
+        <v>-2.5038311111111113</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -71189,76 +71189,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>4.0991979999999995</v>
+        <v>2.7327986666666662</v>
       </c>
       <c r="E4" s="1">
-        <v>4.3854559999999987</v>
+        <v>2.9236373333333323</v>
       </c>
       <c r="F4" s="1">
-        <v>4.9171086666666666</v>
+        <v>3.2780724444444442</v>
       </c>
       <c r="G4" s="1">
-        <v>5.2909353333333344</v>
+        <v>3.5272902222222231</v>
       </c>
       <c r="H4" s="1">
-        <v>5.6317033333333315</v>
+        <v>3.7544688888888875</v>
       </c>
       <c r="I4" s="1">
-        <v>6.1494333333333335</v>
+        <v>4.0996222222222221</v>
       </c>
       <c r="J4" s="1">
-        <v>5.8626999999999994</v>
+        <v>3.9084666666666661</v>
       </c>
       <c r="K4" s="1">
-        <v>6.6160113333333328</v>
+        <v>4.4106742222222222</v>
       </c>
       <c r="L4" s="1">
-        <v>6.0601780000000005</v>
+        <v>4.0401186666666673</v>
       </c>
       <c r="M4" s="1">
-        <v>6.9151186666666655</v>
+        <v>4.6100791111111104</v>
       </c>
       <c r="N4" s="1">
-        <v>6.969567333333333</v>
+        <v>4.6463782222222223</v>
       </c>
       <c r="O4" s="1">
-        <v>6.5241953333333322</v>
+        <v>4.3494635555555545</v>
       </c>
       <c r="P4" s="1">
-        <v>6.3043000000000005</v>
+        <v>4.202866666666667</v>
       </c>
       <c r="Q4" s="1">
-        <v>6.1422573333333332</v>
+        <v>4.0948382222222222</v>
       </c>
       <c r="R4" s="1">
-        <v>5.7562560000000005</v>
+        <v>3.8375040000000005</v>
       </c>
       <c r="S4" s="1">
-        <v>5.2407340000000007</v>
+        <v>3.493822666666667</v>
       </c>
       <c r="T4" s="1">
-        <v>4.8821486666666649</v>
+        <v>3.2547657777777768</v>
       </c>
       <c r="U4" s="1">
-        <v>4.3634373333333327</v>
+        <v>2.9089582222222217</v>
       </c>
       <c r="V4" s="1">
-        <v>3.4152546666666663</v>
+        <v>2.2768364444444442</v>
       </c>
       <c r="W4" s="1">
-        <v>3.822661333333333</v>
+        <v>2.5484408888888885</v>
       </c>
       <c r="X4" s="1">
-        <v>4.0620146666666672</v>
+        <v>2.7080097777777783</v>
       </c>
       <c r="Y4" s="1">
-        <v>4.3755813333333338</v>
+        <v>2.9170542222222227</v>
       </c>
       <c r="Z4" s="1">
-        <v>3.4047666666666667</v>
+        <v>2.2698444444444443</v>
       </c>
       <c r="AA4" s="1">
-        <v>3.6205066666666674</v>
+        <v>2.4136711111111118</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -71272,76 +71272,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>1.8657738000000006</v>
+        <v>1.2438492000000003</v>
       </c>
       <c r="E5" s="1">
-        <v>1.947486666666667</v>
+        <v>1.2983244444444446</v>
       </c>
       <c r="F5" s="1">
-        <v>1.8136143999999998</v>
+        <v>1.2090762666666666</v>
       </c>
       <c r="G5" s="1">
-        <v>1.6859919999999997</v>
+        <v>1.1239946666666665</v>
       </c>
       <c r="H5" s="1">
-        <v>1.3271552</v>
+        <v>0.88477013333333332</v>
       </c>
       <c r="I5" s="1">
-        <v>1.1034112000000003</v>
+        <v>0.73560746666666688</v>
       </c>
       <c r="J5" s="1">
-        <v>1.4196627333333334</v>
+        <v>0.94644182222222228</v>
       </c>
       <c r="K5" s="1">
-        <v>0.23922453333333335</v>
+        <v>0.15948302222222224</v>
       </c>
       <c r="L5" s="1">
-        <v>0.22325333333333339</v>
+        <v>0.14883555555555558</v>
       </c>
       <c r="M5" s="1">
-        <v>0.32860099999999998</v>
+        <v>0.21906733333333331</v>
       </c>
       <c r="N5" s="1">
-        <v>0.18062053333333336</v>
+        <v>0.12041368888888891</v>
       </c>
       <c r="O5" s="1">
-        <v>0.23260973333333332</v>
+        <v>0.15507315555555554</v>
       </c>
       <c r="P5" s="1">
-        <v>0.36692666666666679</v>
+        <v>0.24461777777777785</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.70984900000000006</v>
+        <v>0.47323266666666669</v>
       </c>
       <c r="R5" s="1">
-        <v>0.72127999999999981</v>
+        <v>0.48085333333333319</v>
       </c>
       <c r="S5" s="1">
-        <v>0.72350639999999988</v>
+        <v>0.48233759999999992</v>
       </c>
       <c r="T5" s="1">
-        <v>0.37800499999999998</v>
+        <v>0.2520033333333333</v>
       </c>
       <c r="U5" s="1">
-        <v>0.85104599999999975</v>
+        <v>0.56736399999999987</v>
       </c>
       <c r="V5" s="1">
-        <v>0.4803964</v>
+        <v>0.32026426666666669</v>
       </c>
       <c r="W5" s="1">
-        <v>0.34445259999999989</v>
+        <v>0.22963506666666658</v>
       </c>
       <c r="X5" s="1">
-        <v>0.51291840000000011</v>
+        <v>0.34194560000000007</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.29817966666666668</v>
+        <v>0.19878644444444446</v>
       </c>
       <c r="Z5" s="1">
-        <v>1.4612452000000002</v>
+        <v>0.97416346666666687</v>
       </c>
       <c r="AA5" s="1">
-        <v>1.7269933333333334</v>
+        <v>1.1513288888888888</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -71355,76 +71355,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-4.2549999999999999</v>
+        <v>-2.8366666666666664</v>
       </c>
       <c r="E6" s="1">
-        <v>-4.5045131999999999</v>
+        <v>-3.0030087999999999</v>
       </c>
       <c r="F6" s="1">
-        <v>-5.1173466666666672</v>
+        <v>-3.4115644444444446</v>
       </c>
       <c r="G6" s="1">
-        <v>-5.2441456666666664</v>
+        <v>-3.4960971111111108</v>
       </c>
       <c r="H6" s="1">
-        <v>-5.7232586666666663</v>
+        <v>-3.8155057777777777</v>
       </c>
       <c r="I6" s="1">
-        <v>-6.1816640000000005</v>
+        <v>-4.121109333333334</v>
       </c>
       <c r="J6" s="1">
-        <v>-6.2056621999999999</v>
+        <v>-4.1371081333333333</v>
       </c>
       <c r="K6" s="1">
-        <v>-6.8922413333333319</v>
+        <v>-4.5948275555555549</v>
       </c>
       <c r="L6" s="1">
-        <v>-6.2511546666666646</v>
+        <v>-4.1674364444444434</v>
       </c>
       <c r="M6" s="1">
-        <v>-9.0901027799999987</v>
+        <v>-6.0600685199999988</v>
       </c>
       <c r="N6" s="1">
-        <v>-9.2695777600000024</v>
+        <v>-6.179718506666668</v>
       </c>
       <c r="O6" s="1">
-        <v>-8.1415081066666666</v>
+        <v>-5.4276720711111111</v>
       </c>
       <c r="P6" s="1">
-        <v>-8.2821245866666668</v>
+        <v>-5.5214163911111109</v>
       </c>
       <c r="Q6" s="1">
-        <v>-7.6118136599999993</v>
+        <v>-5.0745424399999992</v>
       </c>
       <c r="R6" s="1">
-        <v>-7.5370644266666682</v>
+        <v>-5.0247096177777788</v>
       </c>
       <c r="S6" s="1">
-        <v>-6.594958666666666</v>
+        <v>-4.3966391111111109</v>
       </c>
       <c r="T6" s="1">
-        <v>-6.0433346400000003</v>
+        <v>-4.0288897600000002</v>
       </c>
       <c r="U6" s="1">
-        <v>-5.2978163199999999</v>
+        <v>-3.5318775466666668</v>
       </c>
       <c r="V6" s="1">
-        <v>-3.5027926666666662</v>
+        <v>-2.3351951111111107</v>
       </c>
       <c r="W6" s="1">
-        <v>-3.8809491599999988</v>
+        <v>-2.5872994399999993</v>
       </c>
       <c r="X6" s="1">
-        <v>-4.0608965599999989</v>
+        <v>-2.7072643733333326</v>
       </c>
       <c r="Y6" s="1">
-        <v>-4.3152745666666661</v>
+        <v>-2.8768497111111109</v>
       </c>
       <c r="Z6" s="1">
-        <v>-3.6758661333333333</v>
+        <v>-2.4505774222222221</v>
       </c>
       <c r="AA6" s="1">
-        <v>-3.6055168000000002</v>
+        <v>-2.4036778666666669</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -71438,76 +71438,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>3.8942380999999995</v>
+        <v>2.5961587333333331</v>
       </c>
       <c r="E7" s="1">
-        <v>4.5170196799999989</v>
+        <v>3.0113464533333327</v>
       </c>
       <c r="F7" s="1">
-        <v>4.7204243199999993</v>
+        <v>3.1469495466666664</v>
       </c>
       <c r="G7" s="1">
-        <v>5.0263885666666672</v>
+        <v>3.3509257111111115</v>
       </c>
       <c r="H7" s="1">
-        <v>5.4627522333333323</v>
+        <v>3.6418348222222217</v>
       </c>
       <c r="I7" s="1">
-        <v>6.3339163333333346</v>
+        <v>4.22261088888889</v>
       </c>
       <c r="J7" s="1">
-        <v>5.6281919999999994</v>
+        <v>3.7521279999999995</v>
       </c>
       <c r="K7" s="1">
-        <v>6.3513708800000011</v>
+        <v>4.2342472533333337</v>
       </c>
       <c r="L7" s="1">
-        <v>6.1207797800000003</v>
+        <v>4.0805198533333336</v>
       </c>
       <c r="M7" s="1">
-        <v>6.7076651066666662</v>
+        <v>4.4717767377777777</v>
       </c>
       <c r="N7" s="1">
-        <v>6.969567333333333</v>
+        <v>4.6463782222222223</v>
       </c>
       <c r="O7" s="1">
-        <v>6.6546792399999992</v>
+        <v>4.4364528266666658</v>
       </c>
       <c r="P7" s="1">
-        <v>6.0521280000000006</v>
+        <v>4.0347520000000001</v>
       </c>
       <c r="Q7" s="1">
-        <v>6.2651024799999986</v>
+        <v>4.1767349866666654</v>
       </c>
       <c r="R7" s="1">
-        <v>6.0440688000000016</v>
+        <v>4.029379200000001</v>
       </c>
       <c r="S7" s="1">
-        <v>5.3979560200000014</v>
+        <v>3.5986373466666675</v>
       </c>
       <c r="T7" s="1">
-        <v>4.7356842066666651</v>
+        <v>3.1571228044444433</v>
       </c>
       <c r="U7" s="1">
-        <v>4.537974826666666</v>
+        <v>3.0253165511111106</v>
       </c>
       <c r="V7" s="1">
-        <v>3.5860173999999994</v>
+        <v>2.3906782666666664</v>
       </c>
       <c r="W7" s="1">
-        <v>3.822661333333333</v>
+        <v>2.5484408888888885</v>
       </c>
       <c r="X7" s="1">
-        <v>3.8589139333333335</v>
+        <v>2.5726092888888892</v>
       </c>
       <c r="Y7" s="1">
-        <v>4.5943604000000002</v>
+        <v>3.0629069333333336</v>
       </c>
       <c r="Z7" s="1">
-        <v>3.3707189999999994</v>
+        <v>2.2471459999999994</v>
       </c>
       <c r="AA7" s="1">
-        <v>3.6205066666666674</v>
+        <v>2.4136711111111118</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -71521,76 +71521,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>1.8284583240000003</v>
+        <v>1.2189722160000003</v>
       </c>
       <c r="E8" s="1">
-        <v>1.9864363999999999</v>
+        <v>1.3242909333333333</v>
       </c>
       <c r="F8" s="1">
-        <v>1.8317505439999999</v>
+        <v>1.2211670293333332</v>
       </c>
       <c r="G8" s="1">
-        <v>1.6185523199999998</v>
+        <v>1.0790348799999998</v>
       </c>
       <c r="H8" s="1">
-        <v>1.2607974399999999</v>
+        <v>0.84053162666666659</v>
       </c>
       <c r="I8" s="1">
-        <v>1.1144453120000002</v>
+        <v>0.74296354133333342</v>
       </c>
       <c r="J8" s="1">
-        <v>1.4054661060000002</v>
+        <v>0.93697740400000018</v>
       </c>
       <c r="K8" s="1">
-        <v>0.24879351466666666</v>
+        <v>0.16586234311111112</v>
       </c>
       <c r="L8" s="1">
-        <v>0.22325333333333339</v>
+        <v>0.14883555555555558</v>
       </c>
       <c r="M8" s="1">
-        <v>0.31217095</v>
+        <v>0.20811396666666668</v>
       </c>
       <c r="N8" s="1">
-        <v>0.18242673866666667</v>
+        <v>0.12161782577777779</v>
       </c>
       <c r="O8" s="1">
-        <v>0.23260973333333332</v>
+        <v>0.15507315555555554</v>
       </c>
       <c r="P8" s="1">
-        <v>0.36325740000000012</v>
+        <v>0.24217160000000007</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.67435655000000005</v>
+        <v>0.44957103333333337</v>
       </c>
       <c r="R8" s="1">
-        <v>0.69964159999999997</v>
+        <v>0.46642773333333332</v>
       </c>
       <c r="S8" s="1">
-        <v>0.7018012079999999</v>
+        <v>0.46786747199999995</v>
       </c>
       <c r="T8" s="1">
-        <v>0.37800499999999998</v>
+        <v>0.2520033333333333</v>
       </c>
       <c r="U8" s="1">
-        <v>0.82551461999999975</v>
+        <v>0.55034307999999987</v>
       </c>
       <c r="V8" s="1">
-        <v>0.47078847199999996</v>
+        <v>0.31385898133333329</v>
       </c>
       <c r="W8" s="1">
-        <v>0.3616752299999999</v>
+        <v>0.24111681999999993</v>
       </c>
       <c r="X8" s="1">
-        <v>0.51291840000000011</v>
+        <v>0.34194560000000007</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.31010685333333332</v>
+        <v>0.20673790222222221</v>
       </c>
       <c r="Z8" s="1">
-        <v>1.4320202960000001</v>
+        <v>0.95468019733333342</v>
       </c>
       <c r="AA8" s="1">
-        <v>1.6579135999999999</v>
+        <v>1.1052757333333332</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -71604,76 +71604,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-4.0422500000000001</v>
+        <v>-2.6948333333333334</v>
       </c>
       <c r="E9" s="1">
-        <v>-4.5045131999999999</v>
+        <v>-3.0030087999999999</v>
       </c>
       <c r="F9" s="1">
-        <v>-4.8614793333333344</v>
+        <v>-3.2409862222222228</v>
       </c>
       <c r="G9" s="1">
-        <v>-5.2441456666666664</v>
+        <v>-3.4960971111111108</v>
       </c>
       <c r="H9" s="1">
-        <v>-5.9521890133333342</v>
+        <v>-3.9681260088888894</v>
       </c>
       <c r="I9" s="1">
-        <v>-6.0580307200000005</v>
+        <v>-4.0386871466666667</v>
       </c>
       <c r="J9" s="1">
-        <v>-6.3918320660000001</v>
+        <v>-4.2612213773333334</v>
       </c>
       <c r="K9" s="1">
-        <v>-6.7543965066666658</v>
+        <v>-4.5029310044444442</v>
       </c>
       <c r="L9" s="1">
-        <v>-6.5637123999999973</v>
+        <v>-4.3758082666666649</v>
       </c>
       <c r="M9" s="1">
-        <v>-9.181003807799998</v>
+        <v>-6.1206692051999987</v>
       </c>
       <c r="N9" s="1">
-        <v>-8.9914904272000022</v>
+        <v>-5.9943269514666682</v>
       </c>
       <c r="O9" s="1">
-        <v>-8.3857533498666665</v>
+        <v>-5.5905022332444441</v>
       </c>
       <c r="P9" s="1">
-        <v>-8.199303340800002</v>
+        <v>-5.466202227200001</v>
       </c>
       <c r="Q9" s="1">
-        <v>-7.9924043429999996</v>
+        <v>-5.328269562</v>
       </c>
       <c r="R9" s="1">
-        <v>-7.4616937824000011</v>
+        <v>-4.9744625216000005</v>
       </c>
       <c r="S9" s="1">
-        <v>-6.594958666666666</v>
+        <v>-4.3966391111111109</v>
       </c>
       <c r="T9" s="1">
-        <v>-5.9829012936000003</v>
+        <v>-3.9886008624000002</v>
       </c>
       <c r="U9" s="1">
-        <v>-5.5097289728000005</v>
+        <v>-3.6731526485333337</v>
       </c>
       <c r="V9" s="1">
-        <v>-3.6078764466666668</v>
+        <v>-2.4052509644444444</v>
       </c>
       <c r="W9" s="1">
-        <v>-3.8421396683999984</v>
+        <v>-2.5614264455999991</v>
       </c>
       <c r="X9" s="1">
-        <v>-4.0608965599999989</v>
+        <v>-2.7072643733333326</v>
       </c>
       <c r="Y9" s="1">
-        <v>-4.099510838333333</v>
+        <v>-2.7330072255555553</v>
       </c>
       <c r="Z9" s="1">
-        <v>-3.6391074719999996</v>
+        <v>-2.4260716479999997</v>
       </c>
       <c r="AA9" s="1">
-        <v>-3.7857926399999999</v>
+        <v>-2.52386176</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -71687,76 +71687,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>3.9721228619999995</v>
+        <v>2.6480819079999995</v>
       </c>
       <c r="E10" s="1">
-        <v>4.2911686959999988</v>
+        <v>2.8607791306666659</v>
       </c>
       <c r="F10" s="1">
-        <v>4.7204243199999993</v>
+        <v>3.1469495466666664</v>
       </c>
       <c r="G10" s="1">
-        <v>4.8755969096666671</v>
+        <v>3.2503979397777782</v>
       </c>
       <c r="H10" s="1">
-        <v>5.1896146216666645</v>
+        <v>3.4597430811111098</v>
       </c>
       <c r="I10" s="1">
-        <v>6.0172205166666677</v>
+        <v>4.0114803444444451</v>
       </c>
       <c r="J10" s="1">
-        <v>5.3467823999999986</v>
+        <v>3.5645215999999991</v>
       </c>
       <c r="K10" s="1">
-        <v>6.0338023360000008</v>
+        <v>4.0225348906666669</v>
       </c>
       <c r="L10" s="1">
-        <v>5.9983641844000006</v>
+        <v>3.9989094562666669</v>
       </c>
       <c r="M10" s="1">
-        <v>6.8418184088000009</v>
+        <v>4.5612122725333339</v>
       </c>
       <c r="N10" s="1">
-        <v>7.1089586799999998</v>
+        <v>4.7393057866666668</v>
       </c>
       <c r="O10" s="1">
-        <v>6.3219452780000003</v>
+        <v>4.2146301853333332</v>
       </c>
       <c r="P10" s="1">
-        <v>6.2942131200000011</v>
+        <v>4.1961420800000004</v>
       </c>
       <c r="Q10" s="1">
-        <v>6.3277535047999995</v>
+        <v>4.2185023365333327</v>
       </c>
       <c r="R10" s="1">
-        <v>6.1649501760000014</v>
+        <v>4.1099667840000009</v>
       </c>
       <c r="S10" s="1">
-        <v>5.1820377792000007</v>
+        <v>3.4546918528000004</v>
       </c>
       <c r="T10" s="1">
-        <v>4.9251115749333314</v>
+        <v>3.2834077166222211</v>
       </c>
       <c r="U10" s="1">
-        <v>4.3564558335999992</v>
+        <v>2.9043038890666661</v>
       </c>
       <c r="V10" s="1">
-        <v>3.7653182699999994</v>
+        <v>2.5102121799999995</v>
       </c>
       <c r="W10" s="1">
-        <v>3.8608879466666668</v>
+        <v>2.573925297777778</v>
       </c>
       <c r="X10" s="1">
-        <v>4.0132704906666667</v>
+        <v>2.6755136604444445</v>
       </c>
       <c r="Y10" s="1">
-        <v>4.7321912120000009</v>
+        <v>3.1547941413333338</v>
       </c>
       <c r="Z10" s="1">
-        <v>3.4044261899999992</v>
+        <v>2.2696174599999996</v>
       </c>
       <c r="AA10" s="1">
-        <v>3.8015320000000012</v>
+        <v>2.5343546666666676</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -71770,76 +71770,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>1.7903890000000002</v>
+        <v>1.1935926666666667</v>
       </c>
       <c r="E11" s="1">
-        <v>1.8501123333333334</v>
+        <v>1.2334082222222222</v>
       </c>
       <c r="F11" s="1">
-        <v>1.6566669999999999</v>
+        <v>1.1044446666666665</v>
       </c>
       <c r="G11" s="1">
-        <v>1.5702866666666662</v>
+        <v>1.0468577777777774</v>
       </c>
       <c r="H11" s="1">
-        <v>1.2865279999999999</v>
+        <v>0.8576853333333333</v>
       </c>
       <c r="I11" s="1">
-        <v>1.0919173333333334</v>
+        <v>0.72794488888888897</v>
       </c>
       <c r="J11" s="1">
-        <v>1.3353263333333334</v>
+        <v>0.8902175555555556</v>
       </c>
       <c r="K11" s="1">
-        <v>0.23190133333333332</v>
+        <v>0.15460088888888887</v>
       </c>
       <c r="L11" s="1">
-        <v>0.20393333333333333</v>
+        <v>0.13595555555555555</v>
       </c>
       <c r="M11" s="1">
-        <v>0.29730566666666658</v>
+        <v>0.19820377777777773</v>
       </c>
       <c r="N11" s="1">
-        <v>0.17509133333333335</v>
+        <v>0.11672755555555557</v>
       </c>
       <c r="O11" s="1">
-        <v>0.21879133333333331</v>
+        <v>0.14586088888888887</v>
       </c>
       <c r="P11" s="1">
-        <v>0.34858033333333344</v>
+        <v>0.23238688888888895</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.64224433333333331</v>
+        <v>0.42816288888888887</v>
       </c>
       <c r="R11" s="1">
-        <v>0.68521599999999994</v>
+        <v>0.45681066666666664</v>
       </c>
       <c r="S11" s="1">
-        <v>0.67385399999999984</v>
+        <v>0.44923599999999991</v>
       </c>
       <c r="T11" s="1">
-        <v>0.37800499999999998</v>
+        <v>0.2520033333333333</v>
       </c>
       <c r="U11" s="1">
-        <v>0.76999399999999973</v>
+        <v>0.51332933333333319</v>
       </c>
       <c r="V11" s="1">
-        <v>0.45185799999999993</v>
+        <v>0.3012386666666666</v>
       </c>
       <c r="W11" s="1">
-        <v>0.3176989999999999</v>
+        <v>0.21179933333333326</v>
       </c>
       <c r="X11" s="1">
-        <v>0.48244799999999999</v>
+        <v>0.32163199999999997</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.29817966666666668</v>
+        <v>0.19878644444444446</v>
       </c>
       <c r="Z11" s="1">
-        <v>1.3609636666666667</v>
+        <v>0.90730911111111112</v>
       </c>
       <c r="AA11" s="1">
-        <v>1.6406436666666666</v>
+        <v>1.0937624444444445</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -71853,76 +71853,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-4.2039400000000002</v>
+        <v>-2.8026266666666668</v>
       </c>
       <c r="E12" s="1">
-        <v>-4.5045131999999999</v>
+        <v>-3.0030087999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>-4.6184053666666669</v>
+        <v>-3.0789369111111111</v>
       </c>
       <c r="G12" s="1">
-        <v>-5.2441456666666664</v>
+        <v>-3.4960971111111108</v>
       </c>
       <c r="H12" s="1">
-        <v>-5.8926671231999999</v>
+        <v>-3.9284447488000001</v>
       </c>
       <c r="I12" s="1">
-        <v>-6.3003519487999995</v>
+        <v>-4.2002346325333333</v>
       </c>
       <c r="J12" s="1">
-        <v>-6.2000771040200009</v>
+        <v>-4.1333847360133342</v>
       </c>
       <c r="K12" s="1">
-        <v>-6.6868525415999978</v>
+        <v>-4.4579016943999985</v>
       </c>
       <c r="L12" s="1">
-        <v>-6.6949866479999978</v>
+        <v>-4.4633244319999985</v>
       </c>
       <c r="M12" s="1">
-        <v>-8.8137636554879979</v>
+        <v>-5.8758424369919986</v>
       </c>
       <c r="N12" s="1">
-        <v>-9.0814053314720038</v>
+        <v>-6.0542702209813362</v>
       </c>
       <c r="O12" s="1">
-        <v>-8.6373259503626674</v>
+        <v>-5.7582173002417782</v>
       </c>
       <c r="P12" s="1">
-        <v>-7.9533242405759994</v>
+        <v>-5.3022161603839999</v>
       </c>
       <c r="Q12" s="1">
-        <v>-7.5927841258499988</v>
+        <v>-5.0618560838999995</v>
       </c>
       <c r="R12" s="1">
-        <v>-7.3870768445760016</v>
+        <v>-4.924717896384001</v>
       </c>
       <c r="S12" s="1">
-        <v>-6.594958666666666</v>
+        <v>-4.3966391111111109</v>
       </c>
       <c r="T12" s="1">
-        <v>-6.2222173453440002</v>
+        <v>-4.1481448968960004</v>
       </c>
       <c r="U12" s="1">
-        <v>-5.3995343933439992</v>
+        <v>-3.599689595562666</v>
       </c>
       <c r="V12" s="1">
-        <v>-3.4635613888000001</v>
+        <v>-2.3090409258666669</v>
       </c>
       <c r="W12" s="1">
-        <v>-3.8805610650839988</v>
+        <v>-2.5870407100559993</v>
       </c>
       <c r="X12" s="1">
-        <v>-4.2639413879999992</v>
+        <v>-2.8426275919999995</v>
       </c>
       <c r="Y12" s="1">
-        <v>-4.099510838333333</v>
+        <v>-2.7330072255555553</v>
       </c>
       <c r="Z12" s="1">
-        <v>-3.52993424784</v>
+        <v>-2.3532894985600001</v>
       </c>
       <c r="AA12" s="1">
-        <v>-3.7100767871999998</v>
+        <v>-2.4733845247999997</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -71936,76 +71936,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>3.7735167188999998</v>
+        <v>2.5156778125999999</v>
       </c>
       <c r="E13" s="1">
-        <v>4.1624336351200002</v>
+        <v>2.7749557567466669</v>
       </c>
       <c r="F13" s="1">
-        <v>4.7676285631999988</v>
+        <v>3.1784190421333327</v>
       </c>
       <c r="G13" s="1">
-        <v>4.7780849714733344</v>
+        <v>3.1853899809822228</v>
       </c>
       <c r="H13" s="1">
-        <v>5.137718475449998</v>
+        <v>3.4251456502999988</v>
       </c>
       <c r="I13" s="1">
-        <v>6.0773927218333341</v>
+        <v>4.0515951478888894</v>
       </c>
       <c r="J13" s="1">
-        <v>5.3467823999999986</v>
+        <v>3.5645215999999991</v>
       </c>
       <c r="K13" s="1">
-        <v>6.0941403593599999</v>
+        <v>4.0627602395733335</v>
       </c>
       <c r="L13" s="1">
-        <v>5.9983641844000006</v>
+        <v>3.9989094562666669</v>
       </c>
       <c r="M13" s="1">
-        <v>7.0470729610640008</v>
+        <v>4.6980486407093336</v>
       </c>
       <c r="N13" s="1">
-        <v>6.7535107459999999</v>
+        <v>4.502340497333333</v>
       </c>
       <c r="O13" s="1">
-        <v>6.0058480140999997</v>
+        <v>4.0038986760666662</v>
       </c>
       <c r="P13" s="1">
-        <v>6.4830395136000005</v>
+        <v>4.3220263424000001</v>
       </c>
       <c r="Q13" s="1">
-        <v>6.2644759697519996</v>
+        <v>4.176317313168</v>
       </c>
       <c r="R13" s="1">
-        <v>6.0416511724800017</v>
+        <v>4.0277674483200014</v>
       </c>
       <c r="S13" s="1">
-        <v>4.9229358902400007</v>
+        <v>3.2819572601600004</v>
       </c>
       <c r="T13" s="1">
-        <v>5.1713671536799986</v>
+        <v>3.4475781024533325</v>
       </c>
       <c r="U13" s="1">
-        <v>4.5307140669439994</v>
+        <v>3.0204760446293331</v>
       </c>
       <c r="V13" s="1">
-        <v>3.8029714526999996</v>
+        <v>2.5353143017999997</v>
       </c>
       <c r="W13" s="1">
-        <v>3.976714585066667</v>
+        <v>2.6511430567111112</v>
       </c>
       <c r="X13" s="1">
-        <v>3.9731377857600005</v>
+        <v>2.6487585238400002</v>
       </c>
       <c r="Y13" s="1">
-        <v>4.9214788604800015</v>
+        <v>3.2809859069866678</v>
       </c>
       <c r="Z13" s="1">
-        <v>3.4044261899999992</v>
+        <v>2.2696174599999996</v>
       </c>
       <c r="AA13" s="1">
-        <v>3.8775626400000012</v>
+        <v>2.5850417600000006</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -72019,76 +72019,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>1.8620045600000001</v>
+        <v>1.2413363733333334</v>
       </c>
       <c r="E14" s="1">
-        <v>1.8686134566666668</v>
+        <v>1.2457423044444444</v>
       </c>
       <c r="F14" s="1">
-        <v>1.6566669999999999</v>
+        <v>1.1044446666666665</v>
       </c>
       <c r="G14" s="1">
-        <v>1.6016923999999992</v>
+        <v>1.0677949333333328</v>
       </c>
       <c r="H14" s="1">
-        <v>1.2993932799999999</v>
+        <v>0.86626218666666654</v>
       </c>
       <c r="I14" s="1">
-        <v>1.0591598133333333</v>
+        <v>0.70610654222222224</v>
       </c>
       <c r="J14" s="1">
-        <v>1.3887393866666666</v>
+        <v>0.92582625777777772</v>
       </c>
       <c r="K14" s="1">
-        <v>0.22958232000000001</v>
+        <v>0.15305488</v>
       </c>
       <c r="L14" s="1">
-        <v>0.21005133333333337</v>
+        <v>0.14003422222222225</v>
       </c>
       <c r="M14" s="1">
-        <v>0.29433260999999994</v>
+        <v>0.19622173999999995</v>
       </c>
       <c r="N14" s="1">
-        <v>0.18034407333333333</v>
+        <v>0.12022938222222222</v>
       </c>
       <c r="O14" s="1">
-        <v>0.20785176666666663</v>
+        <v>0.13856784444444442</v>
       </c>
       <c r="P14" s="1">
-        <v>0.34858033333333344</v>
+        <v>0.23238688888888895</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.66151166333333333</v>
+        <v>0.44100777555555554</v>
       </c>
       <c r="R14" s="1">
-        <v>0.67151167999999994</v>
+        <v>0.44767445333333328</v>
       </c>
       <c r="S14" s="1">
-        <v>0.68733107999999976</v>
+        <v>0.45822071999999986</v>
       </c>
       <c r="T14" s="1">
-        <v>0.36288479999999995</v>
+        <v>0.24192319999999998</v>
       </c>
       <c r="U14" s="1">
-        <v>0.73919423999999978</v>
+        <v>0.49279615999999987</v>
       </c>
       <c r="V14" s="1">
-        <v>0.43378367999999995</v>
+        <v>0.28918911999999997</v>
       </c>
       <c r="W14" s="1">
-        <v>0.33358394999999991</v>
+        <v>0.22238929999999993</v>
       </c>
       <c r="X14" s="1">
-        <v>0.46797456000000004</v>
+        <v>0.31198304000000004</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.30712505666666662</v>
+        <v>0.20475003777777775</v>
       </c>
       <c r="Z14" s="1">
-        <v>1.3745733033333334</v>
+        <v>0.91638220222222222</v>
       </c>
       <c r="AA14" s="1">
-        <v>1.6078307933333333</v>
+        <v>1.0718871955555556</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -72102,76 +72102,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-4.2459794000000004</v>
+        <v>-2.8306529333333335</v>
       </c>
       <c r="E15" s="1">
-        <v>-4.4144229360000002</v>
+        <v>-2.942948624</v>
       </c>
       <c r="F15" s="1">
-        <v>-4.4336691520000002</v>
+        <v>-2.9557794346666668</v>
       </c>
       <c r="G15" s="1">
-        <v>-5.0343798399999988</v>
+        <v>-3.356253226666666</v>
       </c>
       <c r="H15" s="1">
-        <v>-6.1283738081280008</v>
+        <v>-4.0855825387520008</v>
       </c>
       <c r="I15" s="1">
-        <v>-6.1743449098239997</v>
+        <v>-4.1162299398826665</v>
       </c>
       <c r="J15" s="1">
-        <v>-6.0760755619396001</v>
+        <v>-4.0507170412930664</v>
       </c>
       <c r="K15" s="1">
-        <v>-6.419378439935997</v>
+        <v>-4.279585626623998</v>
       </c>
       <c r="L15" s="1">
-        <v>-6.7619365144799986</v>
+        <v>-4.5079576763199993</v>
       </c>
       <c r="M15" s="1">
-        <v>-8.7256260189331183</v>
+        <v>-5.8170840126220789</v>
       </c>
       <c r="N15" s="1">
-        <v>-9.4446615447308826</v>
+        <v>-6.2964410298205884</v>
       </c>
       <c r="O15" s="1">
-        <v>-8.4645794313554159</v>
+        <v>-5.6430529542369436</v>
       </c>
       <c r="P15" s="1">
-        <v>-7.8737909981702403</v>
+        <v>-5.2491939987801599</v>
       </c>
       <c r="Q15" s="1">
-        <v>-7.2890727608159978</v>
+        <v>-4.8593818405439988</v>
       </c>
       <c r="R15" s="1">
-        <v>-7.2393353076844811</v>
+        <v>-4.826223538456321</v>
       </c>
       <c r="S15" s="1">
-        <v>-6.2652107333333324</v>
+        <v>-4.1768071555555553</v>
       </c>
       <c r="T15" s="1">
-        <v>-6.2222173453440002</v>
+        <v>-4.1481448968960004</v>
       </c>
       <c r="U15" s="1">
-        <v>-5.3455390494105588</v>
+        <v>-3.563692699607039</v>
       </c>
       <c r="V15" s="1">
-        <v>-3.4635613888000001</v>
+        <v>-2.3090409258666669</v>
       </c>
       <c r="W15" s="1">
-        <v>-3.958172286385679</v>
+        <v>-2.6387815242571193</v>
       </c>
       <c r="X15" s="1">
-        <v>-4.3065808018799991</v>
+        <v>-2.8710538679199993</v>
       </c>
       <c r="Y15" s="1">
-        <v>-4.1405059467166661</v>
+        <v>-2.7603372978111107</v>
       </c>
       <c r="Z15" s="1">
-        <v>-3.3887368779263998</v>
+        <v>-2.2591579186175998</v>
       </c>
       <c r="AA15" s="1">
-        <v>-3.8584798586879998</v>
+        <v>-2.5723199057919999</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -72185,76 +72185,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>3.5848408829549996</v>
+        <v>2.3898939219699997</v>
       </c>
       <c r="E16" s="1">
-        <v>3.9959362897151998</v>
+        <v>2.6639575264767998</v>
       </c>
       <c r="F16" s="1">
-        <v>5.0060099913599991</v>
+        <v>3.3373399942399993</v>
       </c>
       <c r="G16" s="1">
-        <v>4.5869615726144</v>
+        <v>3.0579743817429335</v>
       </c>
       <c r="H16" s="1">
-        <v>5.3946043992224979</v>
+        <v>3.5964029328149985</v>
       </c>
       <c r="I16" s="1">
-        <v>5.8342970129600005</v>
+        <v>3.8895313419733335</v>
       </c>
       <c r="J16" s="1">
-        <v>5.4002502239999997</v>
+        <v>3.6001668159999998</v>
       </c>
       <c r="K16" s="1">
-        <v>6.0941403593599999</v>
+        <v>4.0627602395733335</v>
       </c>
       <c r="L16" s="1">
-        <v>5.6984459751800012</v>
+        <v>3.798963983453334</v>
       </c>
       <c r="M16" s="1">
-        <v>7.1880144202852811</v>
+        <v>4.7920096135235211</v>
       </c>
       <c r="N16" s="1">
-        <v>6.6184405310800001</v>
+        <v>4.4122936873866667</v>
       </c>
       <c r="O16" s="1">
-        <v>6.2460819346639989</v>
+        <v>4.1640546231093323</v>
       </c>
       <c r="P16" s="1">
-        <v>6.2237179330560002</v>
+        <v>4.1491452887040001</v>
       </c>
       <c r="Q16" s="1">
-        <v>6.4524102488445587</v>
+        <v>4.3016068325630394</v>
       </c>
       <c r="R16" s="1">
-        <v>6.1624841959296015</v>
+        <v>4.1083227972864007</v>
       </c>
       <c r="S16" s="1">
-        <v>4.9721652491424004</v>
+        <v>3.3147768327616003</v>
       </c>
       <c r="T16" s="1">
-        <v>5.2747944967535982</v>
+        <v>3.5165296645023987</v>
       </c>
       <c r="U16" s="1">
-        <v>4.4400997856051196</v>
+        <v>2.9600665237367463</v>
       </c>
       <c r="V16" s="1">
-        <v>3.8410011672269992</v>
+        <v>2.5606674448179993</v>
       </c>
       <c r="W16" s="1">
-        <v>3.976714585066667</v>
+        <v>2.6511430567111112</v>
       </c>
       <c r="X16" s="1">
-        <v>4.1320632971903999</v>
+        <v>2.7547088647935998</v>
       </c>
       <c r="Y16" s="1">
-        <v>5.0199084376896019</v>
+        <v>3.3466056251264011</v>
       </c>
       <c r="Z16" s="1">
-        <v>3.4384704518999993</v>
+        <v>2.2923136345999997</v>
       </c>
       <c r="AA16" s="1">
-        <v>3.7224601344000017</v>
+        <v>2.4816400896000013</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -72268,76 +72268,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>1.7689043320000002</v>
+        <v>1.1792695546666667</v>
       </c>
       <c r="E17" s="1">
-        <v>1.9433579949333335</v>
+        <v>1.2955719966222223</v>
       </c>
       <c r="F17" s="1">
-        <v>1.6401003299999999</v>
+        <v>1.0934002199999999</v>
       </c>
       <c r="G17" s="1">
-        <v>1.6817770199999993</v>
+        <v>1.1211846799999996</v>
       </c>
       <c r="H17" s="1">
-        <v>1.3123872127999998</v>
+        <v>0.87492480853333321</v>
       </c>
       <c r="I17" s="1">
-        <v>1.0485682152000002</v>
+        <v>0.69904547680000018</v>
       </c>
       <c r="J17" s="1">
-        <v>1.3470772050666664</v>
+        <v>0.8980514700444443</v>
       </c>
       <c r="K17" s="1">
-        <v>0.2318781432</v>
+        <v>0.15458542880000001</v>
       </c>
       <c r="L17" s="1">
-        <v>0.21005133333333337</v>
+        <v>0.14003422222222225</v>
       </c>
       <c r="M17" s="1">
-        <v>0.28550263169999995</v>
+        <v>0.19033508779999997</v>
       </c>
       <c r="N17" s="1">
-        <v>0.1785406326</v>
+        <v>0.11902708839999999</v>
       </c>
       <c r="O17" s="1">
-        <v>0.20577324899999996</v>
+        <v>0.13718216599999997</v>
       </c>
       <c r="P17" s="1">
-        <v>0.34858033333333344</v>
+        <v>0.23238688888888895</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.6681267799666667</v>
+        <v>0.44541785331111111</v>
       </c>
       <c r="R17" s="1">
-        <v>0.70508726399999988</v>
+        <v>0.47005817599999994</v>
       </c>
       <c r="S17" s="1">
-        <v>0.65296452599999966</v>
+        <v>0.43530968399999975</v>
       </c>
       <c r="T17" s="1">
-        <v>0.35199825599999995</v>
+        <v>0.23466550399999997</v>
       </c>
       <c r="U17" s="1">
-        <v>0.73180229759999982</v>
+        <v>0.4878681983999999</v>
       </c>
       <c r="V17" s="1">
-        <v>0.44245935359999988</v>
+        <v>0.2949729023999999</v>
       </c>
       <c r="W17" s="1">
-        <v>0.33358394999999991</v>
+        <v>0.22238929999999993</v>
       </c>
       <c r="X17" s="1">
-        <v>0.45861506880000008</v>
+        <v>0.30574337920000005</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.30712505666666662</v>
+        <v>0.20475003777777775</v>
       </c>
       <c r="Z17" s="1">
-        <v>1.3195903712000001</v>
+        <v>0.87972691413333337</v>
       </c>
       <c r="AA17" s="1">
-        <v>1.5756741774666665</v>
+        <v>1.0504494516444443</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -72351,76 +72351,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-4.2035196060000013</v>
+        <v>-2.802346404000001</v>
       </c>
       <c r="E18" s="1">
-        <v>-4.5909998534400005</v>
+        <v>-3.0606665689600003</v>
       </c>
       <c r="F18" s="1">
-        <v>-4.2119856944</v>
+        <v>-2.8079904629333332</v>
       </c>
       <c r="G18" s="1">
-        <v>-5.084723638399999</v>
+        <v>-3.3898157589333326</v>
       </c>
       <c r="H18" s="1">
-        <v>-6.3122250223718401</v>
+        <v>-4.2081500149145601</v>
       </c>
       <c r="I18" s="1">
-        <v>-6.2360883589222382</v>
+        <v>-4.1573922392814922</v>
       </c>
       <c r="J18" s="1">
-        <v>-5.8330325394620166</v>
+        <v>-3.8886883596413444</v>
       </c>
       <c r="K18" s="1">
-        <v>-6.5477660087347163</v>
+        <v>-4.3651773391564772</v>
       </c>
       <c r="L18" s="1">
-        <v>-6.8295558796247988</v>
+        <v>-4.5530372530831995</v>
       </c>
       <c r="M18" s="1">
-        <v>-8.3766009781757944</v>
+        <v>-5.5844006521171963</v>
       </c>
       <c r="N18" s="1">
-        <v>-9.6335547756255</v>
+        <v>-6.4223698504169997</v>
       </c>
       <c r="O18" s="1">
-        <v>-8.3799336370418605</v>
+        <v>-5.5866224246945739</v>
       </c>
       <c r="P18" s="1">
-        <v>-8.1100047281153476</v>
+        <v>-5.4066698187435653</v>
       </c>
       <c r="Q18" s="1">
-        <v>-7.5077449436404775</v>
+        <v>-5.005163295760318</v>
       </c>
       <c r="R18" s="1">
-        <v>-7.6013020730687053</v>
+        <v>-5.0675347153791366</v>
       </c>
       <c r="S18" s="1">
-        <v>-6.5158191626666655</v>
+        <v>-4.3438794417777773</v>
       </c>
       <c r="T18" s="1">
-        <v>-6.0355508249836802</v>
+        <v>-4.0237005499891199</v>
       </c>
       <c r="U18" s="1">
-        <v>-5.5059052208928767</v>
+        <v>-3.670603480595251</v>
       </c>
       <c r="V18" s="1">
-        <v>-3.2903833193600001</v>
+        <v>-2.1935888795733334</v>
       </c>
       <c r="W18" s="1">
-        <v>-3.8790088406579653</v>
+        <v>-2.586005893771977</v>
       </c>
       <c r="X18" s="1">
-        <v>-4.2635149938611994</v>
+        <v>-2.8423433292407996</v>
       </c>
       <c r="Y18" s="1">
-        <v>-4.0162907683151667</v>
+        <v>-2.6775271788767778</v>
       </c>
       <c r="Z18" s="1">
-        <v>-3.3209621403678717</v>
+        <v>-2.213974760245248</v>
       </c>
       <c r="AA18" s="1">
-        <v>-3.8584798586879998</v>
+        <v>-2.5723199057919999</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -72434,76 +72434,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>3.4055988388072493</v>
+        <v>2.2703992258714996</v>
       </c>
       <c r="E19" s="1">
-        <v>4.0758550155095037</v>
+        <v>2.7172366770063356</v>
       </c>
       <c r="F19" s="1">
-        <v>5.2062503910143993</v>
+        <v>3.4708335940095996</v>
       </c>
       <c r="G19" s="1">
-        <v>4.8163096512451204</v>
+        <v>3.2108731008300802</v>
       </c>
       <c r="H19" s="1">
-        <v>5.6103885751913971</v>
+        <v>3.7402590501275981</v>
       </c>
       <c r="I19" s="1">
-        <v>5.6592681025712004</v>
+        <v>3.7728454017141337</v>
       </c>
       <c r="J19" s="1">
-        <v>5.6702627351999988</v>
+        <v>3.780175156799999</v>
       </c>
       <c r="K19" s="1">
-        <v>6.3988473773279999</v>
+        <v>4.2658982515519996</v>
       </c>
       <c r="L19" s="1">
-        <v>5.5274925959246017</v>
+        <v>3.6849950639497346</v>
       </c>
       <c r="M19" s="1">
-        <v>7.1880144202852811</v>
+        <v>4.7920096135235211</v>
       </c>
       <c r="N19" s="1">
-        <v>6.6846249363907999</v>
+        <v>4.456416624260533</v>
       </c>
       <c r="O19" s="1">
-        <v>6.1211602959707205</v>
+        <v>4.0807735306471473</v>
       </c>
       <c r="P19" s="1">
-        <v>6.5349038297088002</v>
+        <v>4.3566025531391999</v>
       </c>
       <c r="Q19" s="1">
-        <v>6.2588379413792232</v>
+        <v>4.1725586275861488</v>
       </c>
       <c r="R19" s="1">
-        <v>5.8543599861331224</v>
+        <v>3.9029066574220814</v>
       </c>
       <c r="S19" s="1">
-        <v>4.922443596650977</v>
+        <v>3.2816290644339845</v>
       </c>
       <c r="T19" s="1">
-        <v>5.2747944967535982</v>
+        <v>3.5165296645023987</v>
       </c>
       <c r="U19" s="1">
-        <v>4.528901781317221</v>
+        <v>3.0192678542114808</v>
       </c>
       <c r="V19" s="1">
-        <v>3.9946412139160792</v>
+        <v>2.6630941426107193</v>
       </c>
       <c r="W19" s="1">
-        <v>4.0960160226186675</v>
+        <v>2.7306773484124451</v>
       </c>
       <c r="X19" s="1">
-        <v>4.1320632971903999</v>
+        <v>2.7547088647935998</v>
       </c>
       <c r="Y19" s="1">
-        <v>4.9195102689358094</v>
+        <v>3.279673512623873</v>
       </c>
       <c r="Z19" s="1">
-        <v>3.3009316338239993</v>
+        <v>2.2006210892159994</v>
       </c>
       <c r="AA19" s="1">
-        <v>3.610786330368001</v>
+        <v>2.4071908869120007</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -72517,76 +72517,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>1.9694279000000006</v>
+        <v>1.3129519333333337</v>
       </c>
       <c r="E20" s="1">
-        <v>2.0351235666666669</v>
+        <v>1.3567490444444446</v>
       </c>
       <c r="F20" s="1">
-        <v>1.8223337000000004</v>
+        <v>1.2148891333333336</v>
       </c>
       <c r="G20" s="1">
-        <v>1.7273153333333331</v>
+        <v>1.1515435555555553</v>
       </c>
       <c r="H20" s="1">
-        <v>1.4151807999999999</v>
+        <v>0.94345386666666664</v>
       </c>
       <c r="I20" s="1">
-        <v>1.2011090666666668</v>
+        <v>0.80073937777777793</v>
       </c>
       <c r="J20" s="1">
-        <v>1.4688589666666667</v>
+        <v>0.97923931111111118</v>
       </c>
       <c r="K20" s="1">
-        <v>0.25509146666666671</v>
+        <v>0.17006097777777782</v>
       </c>
       <c r="L20" s="1">
-        <v>0.22432666666666667</v>
+        <v>0.14955111111111111</v>
       </c>
       <c r="M20" s="1">
-        <v>0.32703623333333326</v>
+        <v>0.21802415555555552</v>
       </c>
       <c r="N20" s="1">
-        <v>0.19260046666666666</v>
+        <v>0.12840031111111111</v>
       </c>
       <c r="O20" s="1">
-        <v>0.24067046666666661</v>
+        <v>0.16044697777777775</v>
       </c>
       <c r="P20" s="1">
-        <v>0.38343836666666675</v>
+        <v>0.25562557777777783</v>
       </c>
       <c r="Q20" s="1">
-        <v>0.70646876666666669</v>
+        <v>0.47097917777777781</v>
       </c>
       <c r="R20" s="1">
-        <v>0.75373760000000001</v>
+        <v>0.5024917333333333</v>
       </c>
       <c r="S20" s="1">
-        <v>0.74123939999999988</v>
+        <v>0.49415959999999992</v>
       </c>
       <c r="T20" s="1">
-        <v>0.41580549999999999</v>
+        <v>0.27720366666666668</v>
       </c>
       <c r="U20" s="1">
-        <v>0.84699339999999979</v>
+        <v>0.56466226666666652</v>
       </c>
       <c r="V20" s="1">
-        <v>0.49704379999999998</v>
+        <v>0.33136253333333332</v>
       </c>
       <c r="W20" s="1">
-        <v>0.34946889999999992</v>
+        <v>0.2329792666666666</v>
       </c>
       <c r="X20" s="1">
-        <v>0.53069280000000008</v>
+        <v>0.35379520000000003</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.32799763333333332</v>
+        <v>0.21866508888888889</v>
       </c>
       <c r="Z20" s="1">
-        <v>1.4970600333333335</v>
+        <v>0.99804002222222232</v>
       </c>
       <c r="AA20" s="1">
-        <v>1.8047080333333332</v>
+        <v>1.2031386888888889</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -72600,76 +72600,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-4.0774140178200016</v>
+        <v>-2.7182760118800009</v>
       </c>
       <c r="E21" s="1">
-        <v>-4.8205498461120007</v>
+        <v>-3.2136998974080004</v>
       </c>
       <c r="F21" s="1">
-        <v>-4.0856261235679989</v>
+        <v>-2.7237507490453328</v>
       </c>
       <c r="G21" s="1">
-        <v>-5.186418111167999</v>
+        <v>-3.4576120741119993</v>
       </c>
       <c r="H21" s="1">
-        <v>-6.5647140232667143</v>
+        <v>-4.3764760155111428</v>
       </c>
       <c r="I21" s="1">
-        <v>-6.2360883589222382</v>
+        <v>-4.1573922392814922</v>
       </c>
       <c r="J21" s="1">
-        <v>-5.8913628648566378</v>
+        <v>-3.9275752432377584</v>
       </c>
       <c r="K21" s="1">
-        <v>-6.4822883486473692</v>
+        <v>-4.3215255657649125</v>
       </c>
       <c r="L21" s="1">
-        <v>-6.8978514384210454</v>
+        <v>-4.59856762561403</v>
       </c>
       <c r="M21" s="1">
-        <v>-8.3766009781757944</v>
+        <v>-5.5844006521171963</v>
       </c>
       <c r="N21" s="1">
-        <v>-9.5372192278692456</v>
+        <v>-6.3581461519128304</v>
       </c>
       <c r="O21" s="1">
-        <v>-8.7151309825235366</v>
+        <v>-5.8100873216823574</v>
       </c>
       <c r="P21" s="1">
-        <v>-8.1100047281153476</v>
+        <v>-5.4066698187435653</v>
       </c>
       <c r="Q21" s="1">
-        <v>-7.7329772919496911</v>
+        <v>-5.1553181946331277</v>
       </c>
       <c r="R21" s="1">
-        <v>-7.3732630108766442</v>
+        <v>-4.9155086739177625</v>
       </c>
       <c r="S21" s="1">
-        <v>-6.3855027794133319</v>
+        <v>-4.2570018529422216</v>
       </c>
       <c r="T21" s="1">
-        <v>-5.7337732837344966</v>
+        <v>-3.8225155224896645</v>
       </c>
       <c r="U21" s="1">
-        <v>-5.5059052208928767</v>
+        <v>-3.670603480595251</v>
       </c>
       <c r="V21" s="1">
-        <v>-3.3561909857471997</v>
+        <v>-2.2374606571647999</v>
       </c>
       <c r="W21" s="1">
-        <v>-3.9953791058777042</v>
+        <v>-2.663586070585136</v>
       </c>
       <c r="X21" s="1">
-        <v>-4.4340555936156472</v>
+        <v>-2.9560370624104313</v>
       </c>
       <c r="Y21" s="1">
-        <v>-3.9359649529488636</v>
+        <v>-2.6239766352992424</v>
       </c>
       <c r="Z21" s="1">
-        <v>-3.3209621403678717</v>
+        <v>-2.213974760245248</v>
       </c>
       <c r="AA21" s="1">
-        <v>-3.9742342544486391</v>
+        <v>-2.6494895029657592</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -72683,76 +72683,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>3.2353188968668873</v>
+        <v>2.1568792645779249</v>
       </c>
       <c r="E22" s="1">
-        <v>4.157372115819693</v>
+        <v>2.771581410546462</v>
       </c>
       <c r="F22" s="1">
-        <v>5.3624379027448308</v>
+        <v>3.5749586018298873</v>
       </c>
       <c r="G22" s="1">
-        <v>4.7199834582202174</v>
+        <v>3.1466556388134781</v>
       </c>
       <c r="H22" s="1">
-        <v>5.7225963466952257</v>
+        <v>3.8150642311301506</v>
       </c>
       <c r="I22" s="1">
-        <v>5.6026754215454879</v>
+        <v>3.7351169476969921</v>
       </c>
       <c r="J22" s="1">
-        <v>5.5001548531439992</v>
+        <v>3.6667699020959996</v>
       </c>
       <c r="K22" s="1">
-        <v>6.5908127986478391</v>
+        <v>4.3938751990985594</v>
       </c>
       <c r="L22" s="1">
-        <v>5.8038672257208317</v>
+        <v>3.8692448171472211</v>
       </c>
       <c r="M22" s="1">
-        <v>7.4036548528938404</v>
+        <v>4.9357699019292269</v>
       </c>
       <c r="N22" s="1">
-        <v>6.5509324376629827</v>
+        <v>4.3672882917753215</v>
       </c>
       <c r="O22" s="1">
-        <v>6.2435835018901349</v>
+        <v>4.1623890012600899</v>
       </c>
       <c r="P22" s="1">
-        <v>6.7962999828971524</v>
+        <v>4.5308666552647683</v>
       </c>
       <c r="Q22" s="1">
-        <v>6.4466030796205986</v>
+        <v>4.2977353864137324</v>
       </c>
       <c r="R22" s="1">
-        <v>5.6787291865491278</v>
+        <v>3.7858194576994184</v>
       </c>
       <c r="S22" s="1">
-        <v>4.8732191606844664</v>
+        <v>3.2488127737896444</v>
       </c>
       <c r="T22" s="1">
-        <v>5.38029038668867</v>
+        <v>3.5868602577924467</v>
       </c>
       <c r="U22" s="1">
-        <v>4.3930347278777058</v>
+        <v>2.9286898185851373</v>
       </c>
       <c r="V22" s="1">
-        <v>4.1144804503335619</v>
+        <v>2.7429869668890414</v>
       </c>
       <c r="W22" s="1">
-        <v>4.2598566635234141</v>
+        <v>2.8399044423489426</v>
       </c>
       <c r="X22" s="1">
-        <v>4.0907426642184967</v>
+        <v>2.7271617761456644</v>
       </c>
       <c r="Y22" s="1">
-        <v>4.870315166246451</v>
+        <v>3.2468767774976341</v>
       </c>
       <c r="Z22" s="1">
-        <v>3.3669502665004791</v>
+        <v>2.2446335110003193</v>
       </c>
       <c r="AA22" s="1">
-        <v>3.646894193671681</v>
+        <v>2.4312627957811208</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -72766,76 +72766,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>2.0678992950000006</v>
+        <v>1.3785995300000005</v>
       </c>
       <c r="E23" s="1">
-        <v>2.1368797449999999</v>
+        <v>1.4245864966666666</v>
       </c>
       <c r="F23" s="1">
-        <v>1.7494403519999999</v>
+        <v>1.1662935679999999</v>
       </c>
       <c r="G23" s="1">
-        <v>1.6754958733333332</v>
+        <v>1.1169972488888888</v>
       </c>
       <c r="H23" s="1">
-        <v>1.4010289919999999</v>
+        <v>0.93401932799999987</v>
       </c>
       <c r="I23" s="1">
-        <v>1.1770868853333336</v>
+        <v>0.78472459022222241</v>
       </c>
       <c r="J23" s="1">
-        <v>1.4541703769999998</v>
+        <v>0.96944691799999994</v>
       </c>
       <c r="K23" s="1">
-        <v>0.25764238133333334</v>
+        <v>0.17176158755555557</v>
       </c>
       <c r="L23" s="1">
-        <v>0.21984013333333333</v>
+        <v>0.14656008888888888</v>
       </c>
       <c r="M23" s="1">
-        <v>0.33030659566666659</v>
+        <v>0.22020439711111106</v>
       </c>
       <c r="N23" s="1">
-        <v>0.20030448533333337</v>
+        <v>0.13353632355555559</v>
       </c>
       <c r="O23" s="1">
-        <v>0.25029728533333334</v>
+        <v>0.16686485688888889</v>
       </c>
       <c r="P23" s="1">
-        <v>0.37576959933333343</v>
+        <v>0.2505130662222223</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.73472751733333341</v>
+        <v>0.48981834488888892</v>
       </c>
       <c r="R23" s="1">
-        <v>0.79142447999999987</v>
+        <v>0.52761631999999992</v>
       </c>
       <c r="S23" s="1">
-        <v>0.70417742999999999</v>
+        <v>0.46945162000000001</v>
       </c>
       <c r="T23" s="1">
-        <v>0.42827966500000003</v>
+        <v>0.28551977666666667</v>
       </c>
       <c r="U23" s="1">
-        <v>0.88087313599999983</v>
+        <v>0.58724875733333326</v>
       </c>
       <c r="V23" s="1">
-        <v>0.48710292400000005</v>
+        <v>0.32473528266666668</v>
       </c>
       <c r="W23" s="1">
-        <v>0.34597421099999992</v>
+        <v>0.23064947399999994</v>
       </c>
       <c r="X23" s="1">
-        <v>0.53069280000000008</v>
+        <v>0.35379520000000003</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.33783756233333334</v>
+        <v>0.22522504155555556</v>
       </c>
       <c r="Z23" s="1">
-        <v>1.5719130350000003</v>
+        <v>1.0479420233333336</v>
       </c>
       <c r="AA23" s="1">
-        <v>1.8408021940000001</v>
+        <v>1.2272014626666667</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -72849,76 +72849,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-4.118188157998202</v>
+        <v>-2.7454587719988015</v>
       </c>
       <c r="E24" s="1">
-        <v>-4.9651663414953608</v>
+        <v>-3.3101108943302404</v>
       </c>
       <c r="F24" s="1">
-        <v>-4.003913601096639</v>
+        <v>-2.669275734064426</v>
       </c>
       <c r="G24" s="1">
-        <v>-5.082689748944639</v>
+        <v>-3.3884598326297595</v>
       </c>
       <c r="H24" s="1">
-        <v>-6.6303611634993826</v>
+        <v>-4.4202407756662554</v>
       </c>
       <c r="I24" s="1">
-        <v>-6.0490057081545707</v>
+        <v>-4.0326704721030469</v>
       </c>
       <c r="J24" s="1">
-        <v>-5.7735356075595057</v>
+        <v>-3.8490237383730039</v>
       </c>
       <c r="K24" s="1">
-        <v>-6.6119341156203157</v>
+        <v>-4.4079560770802102</v>
       </c>
       <c r="L24" s="1">
-        <v>-7.1737654959578876</v>
+        <v>-4.7825103306385914</v>
       </c>
       <c r="M24" s="1">
-        <v>-8.6278990075210675</v>
+        <v>-5.751932671680712</v>
       </c>
       <c r="N24" s="1">
-        <v>-9.1557304587544763</v>
+        <v>-6.1038203058363178</v>
       </c>
       <c r="O24" s="1">
-        <v>-8.9765849119992431</v>
+        <v>-5.9843899413328288</v>
       </c>
       <c r="P24" s="1">
-        <v>-7.8667045862718892</v>
+        <v>-5.2444697241812595</v>
       </c>
       <c r="Q24" s="1">
-        <v>-7.5783177461106979</v>
+        <v>-5.0522118307404655</v>
       </c>
       <c r="R24" s="1">
-        <v>-7.3732630108766442</v>
+        <v>-4.9155086739177625</v>
       </c>
       <c r="S24" s="1">
-        <v>-6.1300826682367981</v>
+        <v>-4.0867217788245318</v>
       </c>
       <c r="T24" s="1">
-        <v>-5.7911110165718407</v>
+        <v>-3.8607406777145603</v>
       </c>
       <c r="U24" s="1">
-        <v>-5.2306099598482332</v>
+        <v>-3.4870733065654886</v>
       </c>
       <c r="V24" s="1">
-        <v>-3.2219433463173122</v>
+        <v>-2.1479622308782083</v>
       </c>
       <c r="W24" s="1">
-        <v>-3.9953791058777042</v>
+        <v>-2.663586070585136</v>
       </c>
       <c r="X24" s="1">
-        <v>-4.6114178173602731</v>
+        <v>-3.0742785449068486</v>
       </c>
       <c r="Y24" s="1">
-        <v>-3.8178860043603975</v>
+        <v>-2.5452573362402648</v>
       </c>
       <c r="Z24" s="1">
-        <v>-3.3873813831752297</v>
+        <v>-2.258254255450153</v>
       </c>
       <c r="AA24" s="1">
-        <v>-3.934491911904153</v>
+        <v>-2.6229946079361022</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -72932,76 +72932,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>3.2029657078982186</v>
+        <v>2.1353104719321458</v>
       </c>
       <c r="E25" s="1">
-        <v>4.157372115819693</v>
+        <v>2.771581410546462</v>
       </c>
       <c r="F25" s="1">
-        <v>5.0943160076075893</v>
+        <v>3.3962106717383929</v>
       </c>
       <c r="G25" s="1">
-        <v>4.8143831273846223</v>
+        <v>3.2095887515897483</v>
       </c>
       <c r="H25" s="1">
-        <v>5.8370482736291303</v>
+        <v>3.8913655157527534</v>
       </c>
       <c r="I25" s="1">
-        <v>5.7707556841918519</v>
+        <v>3.8471704561279014</v>
       </c>
       <c r="J25" s="1">
-        <v>5.5551564016754389</v>
+        <v>3.7034376011169594</v>
       </c>
       <c r="K25" s="1">
-        <v>6.5908127986478391</v>
+        <v>4.3938751990985594</v>
       </c>
       <c r="L25" s="1">
-        <v>5.5136738644347894</v>
+        <v>3.6757825762898597</v>
       </c>
       <c r="M25" s="1">
-        <v>7.6998010470095934</v>
+        <v>5.1332006980063953</v>
       </c>
       <c r="N25" s="1">
-        <v>6.7474604107928728</v>
+        <v>4.4983069405285816</v>
       </c>
       <c r="O25" s="1">
-        <v>6.3060193369090358</v>
+        <v>4.2040128912726908</v>
       </c>
       <c r="P25" s="1">
-        <v>6.7962999828971524</v>
+        <v>4.5308666552647683</v>
       </c>
       <c r="Q25" s="1">
-        <v>6.3821370488243936</v>
+        <v>4.2547580325495957</v>
       </c>
       <c r="R25" s="1">
-        <v>5.3947927272216711</v>
+        <v>3.5965284848144474</v>
       </c>
       <c r="S25" s="1">
-        <v>4.6295582026502426</v>
+        <v>3.0863721351001616</v>
       </c>
       <c r="T25" s="1">
-        <v>5.2188816750880092</v>
+        <v>3.4792544500586726</v>
       </c>
       <c r="U25" s="1">
-        <v>4.305174033320152</v>
+        <v>2.8701160222134345</v>
       </c>
       <c r="V25" s="1">
-        <v>4.1144804503335619</v>
+        <v>2.7429869668890414</v>
       </c>
       <c r="W25" s="1">
-        <v>4.3876523634291162</v>
+        <v>2.925101575619411</v>
       </c>
       <c r="X25" s="1">
-        <v>3.8862055310075712</v>
+        <v>2.5908036873383806</v>
       </c>
       <c r="Y25" s="1">
-        <v>5.1138309245587736</v>
+        <v>3.4092206163725156</v>
       </c>
       <c r="Z25" s="1">
-        <v>3.2996112611704693</v>
+        <v>2.1997408407803127</v>
       </c>
       <c r="AA25" s="1">
-        <v>3.7563010194818314</v>
+        <v>2.5042006796545544</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -73015,76 +73015,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>2.1299362738500007</v>
+        <v>1.4199575159000004</v>
       </c>
       <c r="E26" s="1">
-        <v>2.15824854245</v>
+        <v>1.4388323616333334</v>
       </c>
       <c r="F26" s="1">
-        <v>1.7319459484800002</v>
+        <v>1.1546306323200002</v>
       </c>
       <c r="G26" s="1">
-        <v>1.7592706669999998</v>
+        <v>1.1728471113333332</v>
       </c>
       <c r="H26" s="1">
-        <v>1.4150392819200002</v>
+        <v>0.94335952128000011</v>
       </c>
       <c r="I26" s="1">
-        <v>1.1770868853333336</v>
+        <v>0.78472459022222241</v>
       </c>
       <c r="J26" s="1">
-        <v>1.3814618581499998</v>
+        <v>0.92097457209999989</v>
       </c>
       <c r="K26" s="1">
-        <v>0.24476026226666669</v>
+        <v>0.16317350817777779</v>
       </c>
       <c r="L26" s="1">
-        <v>0.20884812666666666</v>
+        <v>0.13923208444444443</v>
       </c>
       <c r="M26" s="1">
-        <v>0.32039739779666659</v>
+        <v>0.21359826519777772</v>
       </c>
       <c r="N26" s="1">
-        <v>0.19830144048000001</v>
+        <v>0.13220096032</v>
       </c>
       <c r="O26" s="1">
-        <v>0.25530323103999997</v>
+        <v>0.17020215402666664</v>
       </c>
       <c r="P26" s="1">
-        <v>0.36825420734666675</v>
+        <v>0.24550280489777784</v>
       </c>
       <c r="Q26" s="1">
-        <v>0.77146389320000008</v>
+        <v>0.51430926213333339</v>
       </c>
       <c r="R26" s="1">
-        <v>0.83099570399999989</v>
+        <v>0.55399713599999989</v>
       </c>
       <c r="S26" s="1">
-        <v>0.73938630149999984</v>
+        <v>0.4929242009999999</v>
       </c>
       <c r="T26" s="1">
-        <v>0.43256246165000006</v>
+        <v>0.28837497443333338</v>
       </c>
       <c r="U26" s="1">
-        <v>0.88087313599999983</v>
+        <v>0.58724875733333326</v>
       </c>
       <c r="V26" s="1">
-        <v>0.48710292400000005</v>
+        <v>0.32473528266666668</v>
       </c>
       <c r="W26" s="1">
-        <v>0.33213524255999993</v>
+        <v>0.22142349503999995</v>
       </c>
       <c r="X26" s="1">
-        <v>0.51477201600000011</v>
+        <v>0.34318134400000005</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.34121593795666666</v>
+        <v>0.22747729197111111</v>
       </c>
       <c r="Z26" s="1">
-        <v>1.5247556439500001</v>
+        <v>1.0165037626333333</v>
       </c>
       <c r="AA26" s="1">
-        <v>1.8960262598199999</v>
+        <v>1.2640175065466666</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -73098,76 +73098,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-4.3240975658981116</v>
+        <v>-2.8827317105987409</v>
       </c>
       <c r="E27" s="1">
-        <v>-4.9155146780804069</v>
+        <v>-3.2770097853869378</v>
       </c>
       <c r="F27" s="1">
-        <v>-3.9638744650856732</v>
+        <v>-2.6425829767237823</v>
       </c>
       <c r="G27" s="1">
-        <v>-4.9302090564762997</v>
+        <v>-3.2868060376508663</v>
       </c>
       <c r="H27" s="1">
-        <v>-6.5640575518643898</v>
+        <v>-4.3760383679095929</v>
       </c>
       <c r="I27" s="1">
-        <v>-6.2304758793992088</v>
+        <v>-4.1536505862661395</v>
       </c>
       <c r="J27" s="1">
-        <v>-5.4848588271815295</v>
+        <v>-3.656572551454353</v>
       </c>
       <c r="K27" s="1">
-        <v>-6.5458147744641133</v>
+        <v>-4.3638765163094089</v>
       </c>
       <c r="L27" s="1">
-        <v>-6.9585525310791505</v>
+        <v>-4.639035020719434</v>
       </c>
       <c r="M27" s="1">
-        <v>-8.8867359777467012</v>
+        <v>-5.9244906518311344</v>
       </c>
       <c r="N27" s="1">
-        <v>-9.1557304587544763</v>
+        <v>-6.1038203058363178</v>
       </c>
       <c r="O27" s="1">
-        <v>-8.9765849119992431</v>
+        <v>-5.9843899413328288</v>
       </c>
       <c r="P27" s="1">
-        <v>-7.7093704945464516</v>
+        <v>-5.1395803296976341</v>
       </c>
       <c r="Q27" s="1">
-        <v>-7.5783177461106979</v>
+        <v>-5.0522118307404655</v>
       </c>
       <c r="R27" s="1">
-        <v>-7.5207282710941774</v>
+        <v>-5.0138188473961183</v>
       </c>
       <c r="S27" s="1">
-        <v>-6.2526843216015342</v>
+        <v>-4.1684562144010231</v>
       </c>
       <c r="T27" s="1">
-        <v>-5.9648443470689969</v>
+        <v>-3.9765628980459979</v>
       </c>
       <c r="U27" s="1">
-        <v>-5.2306099598482332</v>
+        <v>-3.4870733065654886</v>
       </c>
       <c r="V27" s="1">
-        <v>-3.2863822132436589</v>
+        <v>-2.1909214754957724</v>
       </c>
       <c r="W27" s="1">
-        <v>-4.1551942701128128</v>
+        <v>-2.7701295134085417</v>
       </c>
       <c r="X27" s="1">
-        <v>-4.4730752828394653</v>
+        <v>-2.9820501885596435</v>
       </c>
       <c r="Y27" s="1">
-        <v>-3.8560648644040008</v>
+        <v>-2.5707099096026673</v>
       </c>
       <c r="Z27" s="1">
-        <v>-3.2180123140164683</v>
+        <v>-2.1453415426776457</v>
       </c>
       <c r="AA27" s="1">
-        <v>-4.0131817501422367</v>
+        <v>-2.6754545000948244</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -73181,76 +73181,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>3.1068767366612722</v>
+        <v>2.0712511577741815</v>
       </c>
       <c r="E28" s="1">
-        <v>4.0326509523451035</v>
+        <v>2.6884339682300689</v>
       </c>
       <c r="F28" s="1">
-        <v>5.0943160076075893</v>
+        <v>3.3962106717383929</v>
       </c>
       <c r="G28" s="1">
-        <v>4.9588146212061597</v>
+        <v>3.3058764141374399</v>
       </c>
       <c r="H28" s="1">
-        <v>6.1289006873105869</v>
+        <v>4.0859337915403913</v>
       </c>
       <c r="I28" s="1">
-        <v>5.7130481273499329</v>
+        <v>3.808698751566622</v>
       </c>
       <c r="J28" s="1">
-        <v>5.8329142217592107</v>
+        <v>3.8886094811728071</v>
       </c>
       <c r="K28" s="1">
-        <v>6.4589965426748828</v>
+        <v>4.3059976951165888</v>
       </c>
       <c r="L28" s="1">
-        <v>5.4585371257904418</v>
+        <v>3.6390247505269611</v>
       </c>
       <c r="M28" s="1">
-        <v>8.0847910993600749</v>
+        <v>5.3898607329067163</v>
       </c>
       <c r="N28" s="1">
-        <v>7.0173588272245881</v>
+        <v>4.6782392181497254</v>
       </c>
       <c r="O28" s="1">
-        <v>6.1168387568017657</v>
+        <v>4.0778925045345105</v>
       </c>
       <c r="P28" s="1">
-        <v>6.7962999828971524</v>
+        <v>4.5308666552647683</v>
       </c>
       <c r="Q28" s="1">
-        <v>6.6374225307773678</v>
+        <v>4.4249483538515788</v>
       </c>
       <c r="R28" s="1">
-        <v>5.3947927272216711</v>
+        <v>3.5965284848144474</v>
       </c>
       <c r="S28" s="1">
-        <v>4.5369670385972372</v>
+        <v>3.0246446923981583</v>
       </c>
       <c r="T28" s="1">
-        <v>5.0623152248353689</v>
+        <v>3.3748768165569127</v>
       </c>
       <c r="U28" s="1">
-        <v>4.5204327349861595</v>
+        <v>3.0136218233241063</v>
       </c>
       <c r="V28" s="1">
-        <v>4.1144804503335619</v>
+        <v>2.7429869668890414</v>
       </c>
       <c r="W28" s="1">
-        <v>4.3437758397948256</v>
+        <v>2.8958505598632169</v>
       </c>
       <c r="X28" s="1">
-        <v>4.0416537522478739</v>
+        <v>2.694435834831916</v>
       </c>
       <c r="Y28" s="1">
-        <v>4.9604159968220101</v>
+        <v>3.3069439978813402</v>
       </c>
       <c r="Z28" s="1">
-        <v>3.3985995990055833</v>
+        <v>2.265733066003722</v>
       </c>
       <c r="AA28" s="1">
-        <v>3.6436119888973764</v>
+        <v>2.4290746592649177</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -73264,76 +73264,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>1.8709565050000003</v>
+        <v>1.247304336666667</v>
       </c>
       <c r="E29" s="1">
-        <v>1.9333673883333333</v>
+        <v>1.2889115922222223</v>
       </c>
       <c r="F29" s="1">
-        <v>1.7312170150000001</v>
+        <v>1.1541446766666668</v>
       </c>
       <c r="G29" s="1">
-        <v>1.6409495666666665</v>
+        <v>1.0939663777777777</v>
       </c>
       <c r="H29" s="1">
-        <v>1.3444217600000001</v>
+        <v>0.89628117333333346</v>
       </c>
       <c r="I29" s="1">
-        <v>1.1410536133333333</v>
+        <v>0.76070240888888885</v>
       </c>
       <c r="J29" s="1">
-        <v>1.3954160183333333</v>
+        <v>0.93027734555555552</v>
       </c>
       <c r="K29" s="1">
-        <v>0.24233689333333339</v>
+        <v>0.16155792888888892</v>
       </c>
       <c r="L29" s="1">
-        <v>0.21311033333333332</v>
+        <v>0.14207355555555554</v>
       </c>
       <c r="M29" s="1">
-        <v>0.3106844216666666</v>
+        <v>0.20712294777777773</v>
       </c>
       <c r="N29" s="1">
-        <v>0.18297044333333334</v>
+        <v>0.12198029555555556</v>
       </c>
       <c r="O29" s="1">
-        <v>0.22863694333333326</v>
+        <v>0.15242462888888883</v>
       </c>
       <c r="P29" s="1">
-        <v>0.36426644833333338</v>
+        <v>0.24284429888888892</v>
       </c>
       <c r="Q29" s="1">
-        <v>0.6711453283333334</v>
+        <v>0.44743021888888895</v>
       </c>
       <c r="R29" s="1">
-        <v>0.71605072000000003</v>
+        <v>0.47736714666666669</v>
       </c>
       <c r="S29" s="1">
-        <v>0.70417742999999977</v>
+        <v>0.46945161999999985</v>
       </c>
       <c r="T29" s="1">
-        <v>0.39501522499999991</v>
+        <v>0.26334348333333329</v>
       </c>
       <c r="U29" s="1">
-        <v>0.80464372999999989</v>
+        <v>0.5364291533333333</v>
       </c>
       <c r="V29" s="1">
-        <v>0.47219160999999993</v>
+        <v>0.31479440666666664</v>
       </c>
       <c r="W29" s="1">
-        <v>0.33199545499999994</v>
+        <v>0.22133030333333328</v>
       </c>
       <c r="X29" s="1">
-        <v>0.50415816000000002</v>
+        <v>0.33610544000000003</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.31159775166666664</v>
+        <v>0.20773183444444443</v>
       </c>
       <c r="Z29" s="1">
-        <v>1.4222070316666668</v>
+        <v>0.94813802111111123</v>
       </c>
       <c r="AA29" s="1">
-        <v>1.7144726316666665</v>
+        <v>1.1429817544444443</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -73347,76 +73347,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-4.2808565902391305</v>
+        <v>-2.8539043934927535</v>
       </c>
       <c r="E30" s="1">
-        <v>-4.9155146780804069</v>
+        <v>-3.2770097853869378</v>
       </c>
       <c r="F30" s="1">
-        <v>-3.8449582311331034</v>
+        <v>-2.5633054874220691</v>
       </c>
       <c r="G30" s="1">
-        <v>-5.1274174187353516</v>
+        <v>-3.4182782791569011</v>
       </c>
       <c r="H30" s="1">
-        <v>-6.8266198539389658</v>
+        <v>-4.5510799026259772</v>
       </c>
       <c r="I30" s="1">
-        <v>-6.4796949145751768</v>
+        <v>-4.3197966097167848</v>
       </c>
       <c r="J30" s="1">
-        <v>-5.7591017685406056</v>
+        <v>-3.8394011790270706</v>
       </c>
       <c r="K30" s="1">
-        <v>-6.807647365442679</v>
+        <v>-4.538431576961786</v>
       </c>
       <c r="L30" s="1">
-        <v>-7.1673091070115262</v>
+        <v>-4.7782060713410175</v>
       </c>
       <c r="M30" s="1">
-        <v>-9.0644706973016351</v>
+        <v>-6.0429804648677568</v>
       </c>
       <c r="N30" s="1">
-        <v>-9.2472877633420207</v>
+        <v>-6.1648585088946808</v>
       </c>
       <c r="O30" s="1">
-        <v>-9.0663507611192351</v>
+        <v>-6.0442338407461564</v>
       </c>
       <c r="P30" s="1">
-        <v>-7.4009956747645935</v>
+        <v>-4.9339971165097287</v>
       </c>
       <c r="Q30" s="1">
-        <v>-7.2751850362662696</v>
+        <v>-4.8501233575108467</v>
       </c>
       <c r="R30" s="1">
-        <v>-7.6711428365160605</v>
+        <v>-5.1140952243440401</v>
       </c>
       <c r="S30" s="1">
-        <v>-6.3152111648175504</v>
+        <v>-4.2101407765450336</v>
       </c>
       <c r="T30" s="1">
-        <v>-6.0244927905396866</v>
+        <v>-4.0163285270264577</v>
       </c>
       <c r="U30" s="1">
-        <v>-5.3875282586436795</v>
+        <v>-3.5916855057624528</v>
       </c>
       <c r="V30" s="1">
-        <v>-3.1220631025814751</v>
+        <v>-2.0813754017209836</v>
       </c>
       <c r="W30" s="1">
-        <v>-4.1967462128139408</v>
+        <v>-2.7978308085426273</v>
       </c>
       <c r="X30" s="1">
-        <v>-4.2941522715258866</v>
+        <v>-2.8627681810172576</v>
       </c>
       <c r="Y30" s="1">
-        <v>-3.9717468103361209</v>
+        <v>-2.6478312068907472</v>
       </c>
       <c r="Z30" s="1">
-        <v>-3.2823725602967979</v>
+        <v>-2.1882483735311986</v>
       </c>
       <c r="AA30" s="1">
-        <v>-4.2138408376493484</v>
+        <v>-2.8092272250995656</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -73430,76 +73430,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>3.2311518061277229</v>
+        <v>2.1541012040851486</v>
       </c>
       <c r="E31" s="1">
-        <v>4.0729774618685539</v>
+        <v>2.7153183079123693</v>
       </c>
       <c r="F31" s="1">
-        <v>5.2980886479118929</v>
+        <v>3.5320590986079288</v>
       </c>
       <c r="G31" s="1">
-        <v>5.0579909136302827</v>
+        <v>3.3719939424201884</v>
       </c>
       <c r="H31" s="1">
-        <v>6.312767707929904</v>
+        <v>4.2085118052866024</v>
       </c>
       <c r="I31" s="1">
-        <v>5.5987871648029355</v>
+        <v>3.7325247765352905</v>
       </c>
       <c r="J31" s="1">
-        <v>5.5412685106712489</v>
+        <v>3.6941790071141658</v>
       </c>
       <c r="K31" s="1">
-        <v>6.4589965426748828</v>
+        <v>4.3059976951165888</v>
       </c>
       <c r="L31" s="1">
-        <v>5.5677078683062513</v>
+        <v>3.711805245537501</v>
       </c>
       <c r="M31" s="1">
-        <v>8.4890306543280776</v>
+        <v>5.6593537695520517</v>
       </c>
       <c r="N31" s="1">
-        <v>6.8770116506800969</v>
+        <v>4.5846744337867316</v>
       </c>
       <c r="O31" s="1">
-        <v>6.1168387568017657</v>
+        <v>4.0778925045345105</v>
       </c>
       <c r="P31" s="1">
-        <v>7.0681519822130374</v>
+        <v>4.712101321475358</v>
       </c>
       <c r="Q31" s="1">
-        <v>6.305551404238499</v>
+        <v>4.2037009361589996</v>
       </c>
       <c r="R31" s="1">
-        <v>5.3947927272216711</v>
+        <v>3.5965284848144474</v>
       </c>
       <c r="S31" s="1">
-        <v>4.7638153905270988</v>
+        <v>3.175876927018066</v>
       </c>
       <c r="T31" s="1">
-        <v>5.0116920725870155</v>
+        <v>3.3411280483913437</v>
       </c>
       <c r="U31" s="1">
-        <v>4.4300240802864357</v>
+        <v>2.9533493868576239</v>
       </c>
       <c r="V31" s="1">
-        <v>4.1967700593402339</v>
+        <v>2.7978467062268226</v>
       </c>
       <c r="W31" s="1">
-        <v>4.4740891149886695</v>
+        <v>2.9827260766591128</v>
       </c>
       <c r="X31" s="1">
-        <v>4.1224868272928319</v>
+        <v>2.7483245515285546</v>
       </c>
       <c r="Y31" s="1">
-        <v>4.8116035169173497</v>
+        <v>3.2077356779448998</v>
       </c>
       <c r="Z31" s="1">
-        <v>3.4325855949956394</v>
+        <v>2.2883903966637598</v>
       </c>
       <c r="AA31" s="1">
-        <v>3.6800481087863499</v>
+        <v>2.4533654058575665</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -73513,76 +73513,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>1.8522469399500003</v>
+        <v>1.2348312933000003</v>
       </c>
       <c r="E32" s="1">
-        <v>2.0300357577500003</v>
+        <v>1.3533571718333335</v>
       </c>
       <c r="F32" s="1">
-        <v>1.7312170150000001</v>
+        <v>1.1541446766666668</v>
       </c>
       <c r="G32" s="1">
-        <v>1.5589020883333331</v>
+        <v>1.0392680588888887</v>
       </c>
       <c r="H32" s="1">
-        <v>1.3309775424000001</v>
+        <v>0.88731836160000011</v>
       </c>
       <c r="I32" s="1">
-        <v>1.0840009326666669</v>
+        <v>0.72266728844444461</v>
       </c>
       <c r="J32" s="1">
-        <v>1.3395993775999999</v>
+        <v>0.89306625173333332</v>
       </c>
       <c r="K32" s="1">
-        <v>0.2496070001333334</v>
+        <v>0.1664046667555556</v>
       </c>
       <c r="L32" s="1">
-        <v>0.21311033333333332</v>
+        <v>0.14207355555555554</v>
       </c>
       <c r="M32" s="1">
-        <v>0.30447073323333324</v>
+        <v>0.20298048882222217</v>
       </c>
       <c r="N32" s="1">
-        <v>0.18114073890000001</v>
+        <v>0.12076049260000001</v>
       </c>
       <c r="O32" s="1">
-        <v>0.23092331276666658</v>
+        <v>0.15394887517777772</v>
       </c>
       <c r="P32" s="1">
-        <v>0.3606237838500001</v>
+        <v>0.24041585590000006</v>
       </c>
       <c r="Q32" s="1">
-        <v>0.66443387504999996</v>
+        <v>0.44295591669999995</v>
       </c>
       <c r="R32" s="1">
-        <v>0.72321122719999986</v>
+        <v>0.48214081813333326</v>
       </c>
       <c r="S32" s="1">
-        <v>0.67601033279999989</v>
+        <v>0.45067355519999991</v>
       </c>
       <c r="T32" s="1">
-        <v>0.39501522499999991</v>
+        <v>0.26334348333333329</v>
       </c>
       <c r="U32" s="1">
-        <v>0.84487591649999982</v>
+        <v>0.56325061099999985</v>
       </c>
       <c r="V32" s="1">
-        <v>0.45330394560000004</v>
+        <v>0.30220263040000001</v>
       </c>
       <c r="W32" s="1">
-        <v>0.33863536409999989</v>
+        <v>0.22575690939999993</v>
       </c>
       <c r="X32" s="1">
-        <v>0.48399183360000003</v>
+        <v>0.3226612224</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.29913384159999995</v>
+        <v>0.19942256106666664</v>
       </c>
       <c r="Z32" s="1">
-        <v>1.4079849613500002</v>
+        <v>0.93865664090000012</v>
       </c>
       <c r="AA32" s="1">
-        <v>1.7144726316666665</v>
+        <v>1.1429817544444443</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -73596,76 +73596,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-4.1952394584343473</v>
+        <v>-2.7968263056228984</v>
       </c>
       <c r="E33" s="1">
-        <v>-4.8172043845187993</v>
+        <v>-3.2114695896791994</v>
       </c>
       <c r="F33" s="1">
-        <v>-3.7680590665104408</v>
+        <v>-2.5120393776736272</v>
       </c>
       <c r="G33" s="1">
-        <v>-4.9735948961732896</v>
+        <v>-3.3157299307821932</v>
       </c>
       <c r="H33" s="1">
-        <v>-7.1679508466359136</v>
+        <v>-4.7786338977572758</v>
       </c>
       <c r="I33" s="1">
-        <v>-6.2853040671379219</v>
+        <v>-4.1902027114252816</v>
       </c>
       <c r="J33" s="1">
-        <v>-5.8742838039114176</v>
+        <v>-3.9161892026076117</v>
       </c>
       <c r="K33" s="1">
-        <v>-6.7395708917882517</v>
+        <v>-4.4930472611921681</v>
       </c>
       <c r="L33" s="1">
-        <v>-6.9522898338011805</v>
+        <v>-4.6348598892007873</v>
       </c>
       <c r="M33" s="1">
-        <v>-8.7925365763825862</v>
+        <v>-5.8616910509217242</v>
       </c>
       <c r="N33" s="1">
-        <v>-8.7849233751749178</v>
+        <v>-5.8566155834499449</v>
       </c>
       <c r="O33" s="1">
-        <v>-9.5196682991751977</v>
+        <v>-6.3464455327834655</v>
       </c>
       <c r="P33" s="1">
-        <v>-7.6230255450075317</v>
+        <v>-5.0820170300050211</v>
       </c>
       <c r="Q33" s="1">
-        <v>-7.4206887369915941</v>
+        <v>-4.9471258246610628</v>
       </c>
       <c r="R33" s="1">
-        <v>-7.977988549976704</v>
+        <v>-5.318659033317803</v>
       </c>
       <c r="S33" s="1">
-        <v>-6.5678196114102514</v>
+        <v>-4.3785464076068346</v>
       </c>
       <c r="T33" s="1">
-        <v>-5.9642478626342905</v>
+        <v>-3.9761652417561937</v>
       </c>
       <c r="U33" s="1">
-        <v>-5.3336529760572438</v>
+        <v>-3.5557686507048292</v>
       </c>
       <c r="V33" s="1">
-        <v>-3.1532837336072901</v>
+        <v>-2.1021891557381935</v>
       </c>
       <c r="W33" s="1">
-        <v>-4.1967462128139408</v>
+        <v>-2.7978308085426273</v>
       </c>
       <c r="X33" s="1">
-        <v>-4.3800353169564046</v>
+        <v>-2.9200235446376031</v>
       </c>
       <c r="Y33" s="1">
-        <v>-4.170334150852927</v>
+        <v>-2.7802227672352848</v>
       </c>
       <c r="Z33" s="1">
-        <v>-3.4464911883116378</v>
+        <v>-2.2976607922077585</v>
       </c>
       <c r="AA33" s="1">
-        <v>-4.0452872041433752</v>
+        <v>-2.6968581360955834</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -73679,76 +73679,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>3.0695942158213367</v>
+        <v>2.0463961438808913</v>
       </c>
       <c r="E34" s="1">
-        <v>4.1951667857246102</v>
+        <v>2.7967778571497401</v>
       </c>
       <c r="F34" s="1">
-        <v>5.0331842155162985</v>
+        <v>3.3554561436775323</v>
       </c>
       <c r="G34" s="1">
-        <v>4.8556712770850723</v>
+        <v>3.2371141847233815</v>
       </c>
       <c r="H34" s="1">
-        <v>5.9971293225334099</v>
+        <v>3.9980862150222731</v>
       </c>
       <c r="I34" s="1">
-        <v>5.7667507797470234</v>
+        <v>3.8445005198313491</v>
       </c>
       <c r="J34" s="1">
-        <v>5.319617770244399</v>
+        <v>3.5464118468295993</v>
       </c>
       <c r="K34" s="1">
-        <v>6.1360467155411387</v>
+        <v>4.0906978103607594</v>
       </c>
       <c r="L34" s="1">
-        <v>5.7904161830385013</v>
+        <v>3.8602774553590007</v>
       </c>
       <c r="M34" s="1">
-        <v>8.0645791216116738</v>
+        <v>5.3763860810744495</v>
       </c>
       <c r="N34" s="1">
-        <v>6.5331610681460921</v>
+        <v>4.355440712097395</v>
       </c>
       <c r="O34" s="1">
-        <v>6.422680694641854</v>
+        <v>4.281787129761236</v>
       </c>
       <c r="P34" s="1">
-        <v>7.209515021857297</v>
+        <v>4.8063433479048649</v>
       </c>
       <c r="Q34" s="1">
-        <v>6.431662432323269</v>
+        <v>4.2877749548821793</v>
       </c>
       <c r="R34" s="1">
-        <v>5.5026885817661055</v>
+        <v>3.6684590545107372</v>
       </c>
       <c r="S34" s="1">
-        <v>4.7638153905270988</v>
+        <v>3.175876927018066</v>
       </c>
       <c r="T34" s="1">
-        <v>5.0618089933128854</v>
+        <v>3.3745393288752568</v>
       </c>
       <c r="U34" s="1">
-        <v>4.2971233578778429</v>
+        <v>2.8647489052518953</v>
       </c>
       <c r="V34" s="1">
-        <v>4.3226731611204405</v>
+        <v>2.8817821074136272</v>
       </c>
       <c r="W34" s="1">
-        <v>4.563570897288443</v>
+        <v>3.0423805981922953</v>
       </c>
       <c r="X34" s="1">
-        <v>3.91636248592819</v>
+        <v>2.6109083239521267</v>
       </c>
       <c r="Y34" s="1">
-        <v>4.763487481748176</v>
+        <v>3.1756583211654505</v>
       </c>
       <c r="Z34" s="1">
-        <v>3.2609563152458576</v>
+        <v>2.1739708768305719</v>
       </c>
       <c r="AA34" s="1">
-        <v>3.7904495520499402</v>
+        <v>2.5269663680332934</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -73762,76 +73762,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>1.8522469399500003</v>
+        <v>1.2348312933000003</v>
       </c>
       <c r="E35" s="1">
-        <v>2.1112371880600005</v>
+        <v>1.4074914587066669</v>
       </c>
       <c r="F35" s="1">
-        <v>1.7312170150000001</v>
+        <v>1.1541446766666668</v>
       </c>
       <c r="G35" s="1">
-        <v>1.5277240465666664</v>
+        <v>1.018482697711111</v>
       </c>
       <c r="H35" s="1">
-        <v>1.2644286652800003</v>
+        <v>0.84295244352000021</v>
       </c>
       <c r="I35" s="1">
-        <v>1.0623209140133334</v>
+        <v>0.7082139426755556</v>
       </c>
       <c r="J35" s="1">
-        <v>1.27261940872</v>
+        <v>0.84841293914666671</v>
       </c>
       <c r="K35" s="1">
-        <v>0.24461486013066677</v>
+        <v>0.16307657342044451</v>
       </c>
       <c r="L35" s="1">
-        <v>0.21311033333333332</v>
+        <v>0.14207355555555554</v>
       </c>
       <c r="M35" s="1">
-        <v>0.3075154405656666</v>
+        <v>0.20501029371044441</v>
       </c>
       <c r="N35" s="1">
-        <v>0.190197775845</v>
+        <v>0.12679851722999999</v>
       </c>
       <c r="O35" s="1">
-        <v>0.22861407963899993</v>
+        <v>0.15240938642599997</v>
       </c>
       <c r="P35" s="1">
-        <v>0.37865497304250012</v>
+        <v>0.2524366486950001</v>
       </c>
       <c r="Q35" s="1">
-        <v>0.67772255255099989</v>
+        <v>0.45181503503399995</v>
       </c>
       <c r="R35" s="1">
-        <v>0.73767545174399984</v>
+        <v>0.49178363449599988</v>
       </c>
       <c r="S35" s="1">
-        <v>0.6557300228159999</v>
+        <v>0.43715334854399995</v>
       </c>
       <c r="T35" s="1">
-        <v>0.40686568174999999</v>
+        <v>0.27124378783333331</v>
       </c>
       <c r="U35" s="1">
-        <v>0.81952963900499975</v>
+        <v>0.54635309266999987</v>
       </c>
       <c r="V35" s="1">
-        <v>0.471436103424</v>
+        <v>0.31429073561600002</v>
       </c>
       <c r="W35" s="1">
-        <v>0.32847630317699988</v>
+        <v>0.21898420211799993</v>
       </c>
       <c r="X35" s="1">
-        <v>0.45979224192000001</v>
+        <v>0.30652816127999999</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.29614250318399998</v>
+        <v>0.197428335456</v>
       </c>
       <c r="Z35" s="1">
-        <v>1.4361446605770001</v>
+        <v>0.95742977371800009</v>
       </c>
       <c r="AA35" s="1">
-        <v>1.6973279053500001</v>
+        <v>1.1315519369</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -73845,76 +73845,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-4.405001431356065</v>
+        <v>-2.9366676209040432</v>
       </c>
       <c r="E36" s="1">
-        <v>-5.0580646037447394</v>
+        <v>-3.3720430691631598</v>
       </c>
       <c r="F36" s="1">
-        <v>-3.8811008385057537</v>
+        <v>-2.5874005590038358</v>
       </c>
       <c r="G36" s="1">
-        <v>-5.0730667940967562</v>
+        <v>-3.3820445293978376</v>
       </c>
       <c r="H36" s="1">
-        <v>-7.3113098635686322</v>
+        <v>-4.8742065757124218</v>
       </c>
       <c r="I36" s="1">
-        <v>-6.5995692704948183</v>
+        <v>-4.3997128469965459</v>
       </c>
       <c r="J36" s="1">
-        <v>-5.6980552897940742</v>
+        <v>-3.7987035265293829</v>
       </c>
       <c r="K36" s="1">
-        <v>-6.8743623096240176</v>
+        <v>-4.582908206416012</v>
       </c>
       <c r="L36" s="1">
-        <v>-6.8827669354631693</v>
+        <v>-4.5885112903087792</v>
       </c>
       <c r="M36" s="1">
-        <v>-8.52876047909111</v>
+        <v>-5.6858403193940736</v>
       </c>
       <c r="N36" s="1">
-        <v>-8.3456772064161751</v>
+        <v>-5.56378480427745</v>
       </c>
       <c r="O36" s="1">
-        <v>-9.3292749331916927</v>
+        <v>-6.2195166221277951</v>
       </c>
       <c r="P36" s="1">
-        <v>-7.2418742677571544</v>
+        <v>-4.8279161785047693</v>
       </c>
       <c r="Q36" s="1">
-        <v>-7.3464818496216786</v>
+        <v>-4.8976545664144524</v>
       </c>
       <c r="R36" s="1">
-        <v>-8.3768879774755387</v>
+        <v>-5.5845919849836925</v>
       </c>
       <c r="S36" s="1">
-        <v>-6.76485419975256</v>
+        <v>-4.5099027998350403</v>
       </c>
       <c r="T36" s="1">
-        <v>-5.6660354695025745</v>
+        <v>-3.777356979668383</v>
       </c>
       <c r="U36" s="1">
-        <v>-5.6003356248601044</v>
+        <v>-3.7335570832400697</v>
       </c>
       <c r="V36" s="1">
-        <v>-3.1848165709433629</v>
+        <v>-2.1232110472955754</v>
       </c>
       <c r="W36" s="1">
-        <v>-4.2806811370702187</v>
+        <v>-2.8537874247134791</v>
       </c>
       <c r="X36" s="1">
-        <v>-4.2486342574477112</v>
+        <v>-2.832422838298474</v>
       </c>
       <c r="Y36" s="1">
-        <v>-4.0035207848188099</v>
+        <v>-2.6690138565458734</v>
       </c>
       <c r="Z36" s="1">
-        <v>-3.5843508358441034</v>
+        <v>-2.3895672238960688</v>
       </c>
       <c r="AA36" s="1">
-        <v>-3.964381460060507</v>
+        <v>-2.6429209733736712</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -73928,76 +73928,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>3.0695942158213367</v>
+        <v>2.0463961438808913</v>
       </c>
       <c r="E37" s="1">
-        <v>4.1112634500101182</v>
+        <v>2.7408423000067454</v>
       </c>
       <c r="F37" s="1">
-        <v>5.0331842155162985</v>
+        <v>3.3554561436775323</v>
       </c>
       <c r="G37" s="1">
-        <v>4.6128877132308181</v>
+        <v>3.0752584754872121</v>
       </c>
       <c r="H37" s="1">
-        <v>6.1770432022094122</v>
+        <v>4.1180288014729411</v>
       </c>
       <c r="I37" s="1">
-        <v>6.0550883187343745</v>
+        <v>4.0367255458229163</v>
       </c>
       <c r="J37" s="1">
-        <v>5.5324024810541745</v>
+        <v>3.6882683207027829</v>
       </c>
       <c r="K37" s="1">
-        <v>6.2587676498519604</v>
+        <v>4.1725117665679736</v>
       </c>
       <c r="L37" s="1">
-        <v>5.7904161830385013</v>
+        <v>3.8602774553590007</v>
       </c>
       <c r="M37" s="1">
-        <v>8.2258707040439045</v>
+        <v>5.4839138026959366</v>
       </c>
       <c r="N37" s="1">
-        <v>6.794487510871936</v>
+        <v>4.5296583405812907</v>
       </c>
       <c r="O37" s="1">
-        <v>6.6153611154811083</v>
+        <v>4.4102407436540725</v>
       </c>
       <c r="P37" s="1">
-        <v>6.8490392707644334</v>
+        <v>4.5660261805096223</v>
       </c>
       <c r="Q37" s="1">
-        <v>6.1100793107071061</v>
+        <v>4.0733862071380704</v>
       </c>
       <c r="R37" s="1">
-        <v>5.6127423534014271</v>
+        <v>3.7418282356009516</v>
       </c>
       <c r="S37" s="1">
-        <v>4.6685390827165572</v>
+        <v>3.1123593884777048</v>
       </c>
       <c r="T37" s="1">
-        <v>5.1630451731791434</v>
+        <v>3.4420301154527624</v>
       </c>
       <c r="U37" s="1">
-        <v>4.1682096571415084</v>
+        <v>2.7788064380943389</v>
       </c>
       <c r="V37" s="1">
-        <v>4.4955800875652576</v>
+        <v>2.9970533917101716</v>
       </c>
       <c r="W37" s="1">
-        <v>4.4722994793426736</v>
+        <v>2.9815329862284492</v>
       </c>
       <c r="X37" s="1">
-        <v>3.8771988610689081</v>
+        <v>2.5847992407126053</v>
       </c>
       <c r="Y37" s="1">
-        <v>4.763487481748176</v>
+        <v>3.1756583211654505</v>
       </c>
       <c r="Z37" s="1">
-        <v>3.1305180626360229</v>
+        <v>2.0870120417573488</v>
       </c>
       <c r="AA37" s="1">
-        <v>3.7904495520499402</v>
+        <v>2.5269663680332934</v>
       </c>
     </row>
   </sheetData>

--- a/data/OP2/case18_2_2/case18_operational_data.xlsx
+++ b/data/OP2/case18_2_2/case18_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case18_2_1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case18_2_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3080FAF5-C96D-8B4A-88FE-8BA4CB4590F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0BF939-BA87-414D-889A-B03BF0F4CA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -454,12 +454,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*3.5</f>
-        <v>0.70000000000000007</v>
+        <f>E2*3</f>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*2</f>
-        <v>0.24</v>
+        <f>F2*2.5</f>
+        <v>0.3</v>
       </c>
       <c r="D2" s="2">
         <f>$B2/SUM($B$2:$B$1048576)</f>
@@ -477,12 +477,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B31" si="0">E3*3.5</f>
-        <v>1.4000000000000001</v>
+        <f t="shared" ref="B3:B31" si="0">E3*3</f>
+        <v>1.2000000000000002</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C31" si="1">F3*2</f>
-        <v>0.5</v>
+        <f t="shared" ref="C3:C31" si="1">F3*2.5</f>
+        <v>0.625</v>
       </c>
       <c r="D3" s="2">
         <f t="shared" ref="D3:D31" si="2">$B3/SUM($B$2:$B$1048576)</f>
@@ -501,15 +501,15 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>1.86</v>
+        <v>2.3250000000000002</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="2"/>
-        <v>6.4655172413793108E-2</v>
+        <v>6.4655172413793094E-2</v>
       </c>
       <c r="E4" s="1">
         <v>1.5</v>
@@ -524,15 +524,15 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>4.5199999999999996</v>
+        <v>5.6499999999999995</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="2"/>
-        <v>0.12931034482758622</v>
+        <v>0.12931034482758619</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -547,11 +547,11 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="2"/>
@@ -570,11 +570,11 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="2"/>
@@ -593,11 +593,11 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="2"/>
@@ -616,11 +616,11 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>0.62</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="2"/>
@@ -639,11 +639,11 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="2"/>
@@ -662,15 +662,15 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>0.38</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="D11" s="2">
         <f t="shared" si="2"/>
-        <v>1.2931034482758621E-2</v>
+        <v>1.2931034482758617E-2</v>
       </c>
       <c r="E11" s="1">
         <v>0.3</v>
@@ -685,11 +685,11 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" si="2"/>
@@ -708,11 +708,11 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D13" s="2">
         <f t="shared" si="2"/>
@@ -731,11 +731,11 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>0.62</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="2"/>
@@ -754,11 +754,11 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="2"/>
@@ -777,11 +777,11 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" si="2"/>
@@ -800,11 +800,11 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D17" s="2">
         <f>$B17/SUM($B$2:$B$1048576)</f>
@@ -823,11 +823,11 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="D18" s="2">
         <f t="shared" si="2"/>
@@ -846,15 +846,15 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>1.86</v>
+        <v>2.3250000000000002</v>
       </c>
       <c r="D19" s="2">
         <f t="shared" si="2"/>
-        <v>6.4655172413793108E-2</v>
+        <v>6.4655172413793094E-2</v>
       </c>
       <c r="E19" s="1">
         <v>1.5</v>
@@ -869,15 +869,15 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>4.5199999999999996</v>
+        <v>5.6499999999999995</v>
       </c>
       <c r="D20" s="2">
         <f t="shared" si="2"/>
-        <v>0.12931034482758622</v>
+        <v>0.12931034482758619</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -892,11 +892,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D21" s="2">
         <f t="shared" si="2"/>
@@ -915,11 +915,11 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D22" s="2">
         <f t="shared" si="2"/>
@@ -938,11 +938,11 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="D23" s="2">
         <f t="shared" si="2"/>
@@ -961,11 +961,11 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
-        <v>0.62</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="D24" s="2">
         <f t="shared" si="2"/>
@@ -984,11 +984,11 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="D25" s="2">
         <f t="shared" si="2"/>
@@ -1007,15 +1007,15 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>1.05</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>0.38</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="2"/>
-        <v>1.2931034482758621E-2</v>
+        <v>1.2931034482758617E-2</v>
       </c>
       <c r="E26" s="1">
         <v>0.3</v>
@@ -1030,11 +1030,11 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D27" s="2">
         <f t="shared" si="2"/>
@@ -1053,11 +1053,11 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>2.8000000000000003</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D28" s="2">
         <f t="shared" si="2"/>
@@ -1076,11 +1076,11 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>0.62</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="D29" s="2">
         <f t="shared" si="2"/>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="1"/>
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" si="2"/>
@@ -1122,11 +1122,11 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000007</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D31" s="2">
         <f t="shared" si="2"/>

--- a/data/OP2/case18_2_2/case18_operational_data.xlsx
+++ b/data/OP2/case18_2_2/case18_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/case18_2_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0BF939-BA87-414D-889A-B03BF0F4CA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF27D327-057D-8F48-85F2-035A32B03775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -71023,76 +71023,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>1.8846200000000002</v>
+        <v>3.2980850000000004</v>
       </c>
       <c r="E2" s="1">
-        <v>1.947486666666667</v>
+        <v>3.4081016666666675</v>
       </c>
       <c r="F2" s="1">
-        <v>1.7438599999999997</v>
+        <v>3.0517549999999996</v>
       </c>
       <c r="G2" s="1">
-        <v>1.6529333333333331</v>
+        <v>2.8926333333333329</v>
       </c>
       <c r="H2" s="1">
-        <v>1.3542400000000001</v>
+        <v>2.36992</v>
       </c>
       <c r="I2" s="1">
-        <v>1.1493866666666668</v>
+        <v>2.0114266666666669</v>
       </c>
       <c r="J2" s="1">
-        <v>1.4056066666666667</v>
+        <v>2.4598116666666665</v>
       </c>
       <c r="K2" s="1">
-        <v>0.24410666666666667</v>
+        <v>0.42718666666666666</v>
       </c>
       <c r="L2" s="1">
-        <v>0.21466666666666667</v>
+        <v>0.3756666666666667</v>
       </c>
       <c r="M2" s="1">
-        <v>0.31295333333333325</v>
+        <v>0.5476683333333332</v>
       </c>
       <c r="N2" s="1">
-        <v>0.1843066666666667</v>
+        <v>0.32253666666666675</v>
       </c>
       <c r="O2" s="1">
-        <v>0.23030666666666666</v>
+        <v>0.40303666666666665</v>
       </c>
       <c r="P2" s="1">
-        <v>0.36692666666666679</v>
+        <v>0.64212166666666692</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.67604666666666668</v>
+        <v>1.1830816666666668</v>
       </c>
       <c r="R2" s="1">
-        <v>0.72127999999999981</v>
+        <v>1.2622399999999996</v>
       </c>
       <c r="S2" s="1">
-        <v>0.70931999999999995</v>
+        <v>1.2413099999999999</v>
       </c>
       <c r="T2" s="1">
-        <v>0.39789999999999998</v>
+        <v>0.69632499999999997</v>
       </c>
       <c r="U2" s="1">
-        <v>0.81051999999999991</v>
+        <v>1.4184099999999997</v>
       </c>
       <c r="V2" s="1">
-        <v>0.47564000000000001</v>
+        <v>0.83237000000000005</v>
       </c>
       <c r="W2" s="1">
-        <v>0.33441999999999994</v>
+        <v>0.58523499999999995</v>
       </c>
       <c r="X2" s="1">
-        <v>0.50784000000000007</v>
+        <v>0.88872000000000018</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.31387333333333334</v>
+        <v>0.54927833333333331</v>
       </c>
       <c r="Z2" s="1">
-        <v>1.4325933333333334</v>
+        <v>2.5070383333333335</v>
       </c>
       <c r="AA2" s="1">
-        <v>1.7269933333333334</v>
+        <v>3.0222383333333336</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -71106,76 +71106,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-4.2549999999999999</v>
+        <v>-7.44625</v>
       </c>
       <c r="E3" s="1">
-        <v>-4.5500133333333332</v>
+        <v>-7.9625233333333334</v>
       </c>
       <c r="F3" s="1">
-        <v>-5.1173466666666672</v>
+        <v>-8.9553566666666669</v>
       </c>
       <c r="G3" s="1">
-        <v>-5.520153333333333</v>
+        <v>-9.6602683333333328</v>
       </c>
       <c r="H3" s="1">
-        <v>-5.900266666666667</v>
+        <v>-10.325466666666667</v>
       </c>
       <c r="I3" s="1">
-        <v>-6.439233333333334</v>
+        <v>-11.268658333333335</v>
       </c>
       <c r="J3" s="1">
-        <v>-6.1442199999999998</v>
+        <v>-10.752385</v>
       </c>
       <c r="K3" s="1">
-        <v>-6.8922413333333319</v>
+        <v>-12.061422333333331</v>
       </c>
       <c r="L3" s="1">
-        <v>-6.2511546666666646</v>
+        <v>-10.939520666666663</v>
       </c>
       <c r="M3" s="1">
-        <v>-9.1819219999999984</v>
+        <v>-16.068363499999997</v>
       </c>
       <c r="N3" s="1">
-        <v>-9.0878213333333342</v>
+        <v>-15.903687333333334</v>
       </c>
       <c r="O3" s="1">
-        <v>-8.3076613333333338</v>
+        <v>-14.538407333333334</v>
       </c>
       <c r="P3" s="1">
-        <v>-7.963581333333333</v>
+        <v>-13.936267333333333</v>
       </c>
       <c r="Q3" s="1">
-        <v>-7.6887006666666666</v>
+        <v>-13.455226166666666</v>
       </c>
       <c r="R3" s="1">
-        <v>-7.247177333333334</v>
+        <v>-12.682560333333335</v>
       </c>
       <c r="S3" s="1">
-        <v>-6.594958666666666</v>
+        <v>-11.541177666666666</v>
       </c>
       <c r="T3" s="1">
-        <v>-6.1666680000000005</v>
+        <v>-10.791669000000001</v>
       </c>
       <c r="U3" s="1">
-        <v>-5.5185586666666673</v>
+        <v>-9.6574776666666686</v>
       </c>
       <c r="V3" s="1">
-        <v>-3.5027926666666662</v>
+        <v>-6.1298871666666663</v>
       </c>
       <c r="W3" s="1">
-        <v>-3.9201506666666659</v>
+        <v>-6.8602636666666656</v>
       </c>
       <c r="X3" s="1">
-        <v>-4.1437719999999993</v>
+        <v>-7.2516009999999991</v>
       </c>
       <c r="Y3" s="1">
-        <v>-4.4487366666666661</v>
+        <v>-7.7852891666666659</v>
       </c>
       <c r="Z3" s="1">
-        <v>-3.5344866666666666</v>
+        <v>-6.1853516666666666</v>
       </c>
       <c r="AA3" s="1">
-        <v>-3.755746666666667</v>
+        <v>-6.5725566666666673</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -71189,76 +71189,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>4.0991979999999995</v>
+        <v>7.1735964999999986</v>
       </c>
       <c r="E4" s="1">
-        <v>4.3854559999999987</v>
+        <v>7.6745479999999979</v>
       </c>
       <c r="F4" s="1">
-        <v>4.9171086666666666</v>
+        <v>8.6049401666666672</v>
       </c>
       <c r="G4" s="1">
-        <v>5.2909353333333344</v>
+        <v>9.2591368333333346</v>
       </c>
       <c r="H4" s="1">
-        <v>5.6317033333333315</v>
+        <v>9.8554808333333295</v>
       </c>
       <c r="I4" s="1">
-        <v>6.1494333333333335</v>
+        <v>10.761508333333333</v>
       </c>
       <c r="J4" s="1">
-        <v>5.8626999999999994</v>
+        <v>10.259725</v>
       </c>
       <c r="K4" s="1">
-        <v>6.6160113333333328</v>
+        <v>11.578019833333332</v>
       </c>
       <c r="L4" s="1">
-        <v>6.0601780000000005</v>
+        <v>10.605311500000001</v>
       </c>
       <c r="M4" s="1">
-        <v>6.9151186666666655</v>
+        <v>12.101457666666665</v>
       </c>
       <c r="N4" s="1">
-        <v>6.969567333333333</v>
+        <v>12.196742833333333</v>
       </c>
       <c r="O4" s="1">
-        <v>6.5241953333333322</v>
+        <v>11.417341833333332</v>
       </c>
       <c r="P4" s="1">
-        <v>6.3043000000000005</v>
+        <v>11.032525000000001</v>
       </c>
       <c r="Q4" s="1">
-        <v>6.1422573333333332</v>
+        <v>10.748950333333333</v>
       </c>
       <c r="R4" s="1">
-        <v>5.7562560000000005</v>
+        <v>10.073448000000001</v>
       </c>
       <c r="S4" s="1">
-        <v>5.2407340000000007</v>
+        <v>9.1712845000000005</v>
       </c>
       <c r="T4" s="1">
-        <v>4.8821486666666649</v>
+        <v>8.5437601666666634</v>
       </c>
       <c r="U4" s="1">
-        <v>4.3634373333333327</v>
+        <v>7.636015333333332</v>
       </c>
       <c r="V4" s="1">
-        <v>3.4152546666666663</v>
+        <v>5.9766956666666662</v>
       </c>
       <c r="W4" s="1">
-        <v>3.822661333333333</v>
+        <v>6.6896573333333329</v>
       </c>
       <c r="X4" s="1">
-        <v>4.0620146666666672</v>
+        <v>7.1085256666666679</v>
       </c>
       <c r="Y4" s="1">
-        <v>4.3755813333333338</v>
+        <v>7.6572673333333343</v>
       </c>
       <c r="Z4" s="1">
-        <v>3.4047666666666667</v>
+        <v>5.9583416666666666</v>
       </c>
       <c r="AA4" s="1">
-        <v>3.6205066666666674</v>
+        <v>6.335886666666668</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -71272,76 +71272,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>1.8657738000000006</v>
+        <v>3.2651041500000009</v>
       </c>
       <c r="E5" s="1">
-        <v>1.947486666666667</v>
+        <v>3.4081016666666675</v>
       </c>
       <c r="F5" s="1">
-        <v>1.8136143999999998</v>
+        <v>3.1738251999999996</v>
       </c>
       <c r="G5" s="1">
-        <v>1.6859919999999997</v>
+        <v>2.9504859999999997</v>
       </c>
       <c r="H5" s="1">
-        <v>1.3271552</v>
+        <v>2.3225216</v>
       </c>
       <c r="I5" s="1">
-        <v>1.1034112000000003</v>
+        <v>1.9309696000000005</v>
       </c>
       <c r="J5" s="1">
-        <v>1.4196627333333334</v>
+        <v>2.4844097833333336</v>
       </c>
       <c r="K5" s="1">
-        <v>0.23922453333333335</v>
+        <v>0.41864293333333336</v>
       </c>
       <c r="L5" s="1">
-        <v>0.22325333333333339</v>
+        <v>0.39069333333333345</v>
       </c>
       <c r="M5" s="1">
-        <v>0.32860099999999998</v>
+        <v>0.57505174999999997</v>
       </c>
       <c r="N5" s="1">
-        <v>0.18062053333333336</v>
+        <v>0.3160859333333334</v>
       </c>
       <c r="O5" s="1">
-        <v>0.23260973333333332</v>
+        <v>0.40706703333333333</v>
       </c>
       <c r="P5" s="1">
-        <v>0.36692666666666679</v>
+        <v>0.64212166666666692</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.70984900000000006</v>
+        <v>1.2422357500000001</v>
       </c>
       <c r="R5" s="1">
-        <v>0.72127999999999981</v>
+        <v>1.2622399999999996</v>
       </c>
       <c r="S5" s="1">
-        <v>0.72350639999999988</v>
+        <v>1.2661361999999998</v>
       </c>
       <c r="T5" s="1">
-        <v>0.37800499999999998</v>
+        <v>0.66150874999999998</v>
       </c>
       <c r="U5" s="1">
-        <v>0.85104599999999975</v>
+        <v>1.4893304999999994</v>
       </c>
       <c r="V5" s="1">
-        <v>0.4803964</v>
+        <v>0.84069369999999999</v>
       </c>
       <c r="W5" s="1">
-        <v>0.34445259999999989</v>
+        <v>0.6027920499999998</v>
       </c>
       <c r="X5" s="1">
-        <v>0.51291840000000011</v>
+        <v>0.89760720000000016</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.29817966666666668</v>
+        <v>0.52181441666666672</v>
       </c>
       <c r="Z5" s="1">
-        <v>1.4612452000000002</v>
+        <v>2.5571791000000004</v>
       </c>
       <c r="AA5" s="1">
-        <v>1.7269933333333334</v>
+        <v>3.0222383333333336</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -71355,76 +71355,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-4.2549999999999999</v>
+        <v>-7.44625</v>
       </c>
       <c r="E6" s="1">
-        <v>-4.5045131999999999</v>
+        <v>-7.8828981000000002</v>
       </c>
       <c r="F6" s="1">
-        <v>-5.1173466666666672</v>
+        <v>-8.9553566666666669</v>
       </c>
       <c r="G6" s="1">
-        <v>-5.2441456666666664</v>
+        <v>-9.1772549166666657</v>
       </c>
       <c r="H6" s="1">
-        <v>-5.7232586666666663</v>
+        <v>-10.015702666666666</v>
       </c>
       <c r="I6" s="1">
-        <v>-6.1816640000000005</v>
+        <v>-10.817912000000002</v>
       </c>
       <c r="J6" s="1">
-        <v>-6.2056621999999999</v>
+        <v>-10.85990885</v>
       </c>
       <c r="K6" s="1">
-        <v>-6.8922413333333319</v>
+        <v>-12.061422333333331</v>
       </c>
       <c r="L6" s="1">
-        <v>-6.2511546666666646</v>
+        <v>-10.939520666666663</v>
       </c>
       <c r="M6" s="1">
-        <v>-9.0901027799999987</v>
+        <v>-15.907679864999999</v>
       </c>
       <c r="N6" s="1">
-        <v>-9.2695777600000024</v>
+        <v>-16.221761080000004</v>
       </c>
       <c r="O6" s="1">
-        <v>-8.1415081066666666</v>
+        <v>-14.247639186666667</v>
       </c>
       <c r="P6" s="1">
-        <v>-8.2821245866666668</v>
+        <v>-14.493718026666667</v>
       </c>
       <c r="Q6" s="1">
-        <v>-7.6118136599999993</v>
+        <v>-13.320673905</v>
       </c>
       <c r="R6" s="1">
-        <v>-7.5370644266666682</v>
+        <v>-13.18986274666667</v>
       </c>
       <c r="S6" s="1">
-        <v>-6.594958666666666</v>
+        <v>-11.541177666666666</v>
       </c>
       <c r="T6" s="1">
-        <v>-6.0433346400000003</v>
+        <v>-10.575835620000001</v>
       </c>
       <c r="U6" s="1">
-        <v>-5.2978163199999999</v>
+        <v>-9.2711785599999992</v>
       </c>
       <c r="V6" s="1">
-        <v>-3.5027926666666662</v>
+        <v>-6.1298871666666663</v>
       </c>
       <c r="W6" s="1">
-        <v>-3.8809491599999988</v>
+        <v>-6.7916610299999975</v>
       </c>
       <c r="X6" s="1">
-        <v>-4.0608965599999989</v>
+        <v>-7.1065689799999978</v>
       </c>
       <c r="Y6" s="1">
-        <v>-4.3152745666666661</v>
+        <v>-7.5517304916666657</v>
       </c>
       <c r="Z6" s="1">
-        <v>-3.6758661333333333</v>
+        <v>-6.4327657333333335</v>
       </c>
       <c r="AA6" s="1">
-        <v>-3.6055168000000002</v>
+        <v>-6.3096544000000003</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -71438,76 +71438,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>3.8942380999999995</v>
+        <v>6.8149166749999992</v>
       </c>
       <c r="E7" s="1">
-        <v>4.5170196799999989</v>
+        <v>7.9047844399999985</v>
       </c>
       <c r="F7" s="1">
-        <v>4.7204243199999993</v>
+        <v>8.2607425599999988</v>
       </c>
       <c r="G7" s="1">
-        <v>5.0263885666666672</v>
+        <v>8.7961799916666674</v>
       </c>
       <c r="H7" s="1">
-        <v>5.4627522333333323</v>
+        <v>9.5598164083333312</v>
       </c>
       <c r="I7" s="1">
-        <v>6.3339163333333346</v>
+        <v>11.084353583333336</v>
       </c>
       <c r="J7" s="1">
-        <v>5.6281919999999994</v>
+        <v>9.8493359999999992</v>
       </c>
       <c r="K7" s="1">
-        <v>6.3513708800000011</v>
+        <v>11.114899040000001</v>
       </c>
       <c r="L7" s="1">
-        <v>6.1207797800000003</v>
+        <v>10.711364615000001</v>
       </c>
       <c r="M7" s="1">
-        <v>6.7076651066666662</v>
+        <v>11.738413936666666</v>
       </c>
       <c r="N7" s="1">
-        <v>6.969567333333333</v>
+        <v>12.196742833333333</v>
       </c>
       <c r="O7" s="1">
-        <v>6.6546792399999992</v>
+        <v>11.645688669999998</v>
       </c>
       <c r="P7" s="1">
-        <v>6.0521280000000006</v>
+        <v>10.591224</v>
       </c>
       <c r="Q7" s="1">
-        <v>6.2651024799999986</v>
+        <v>10.963929339999998</v>
       </c>
       <c r="R7" s="1">
-        <v>6.0440688000000016</v>
+        <v>10.577120400000002</v>
       </c>
       <c r="S7" s="1">
-        <v>5.3979560200000014</v>
+        <v>9.4464230350000022</v>
       </c>
       <c r="T7" s="1">
-        <v>4.7356842066666651</v>
+        <v>8.2874473616666648</v>
       </c>
       <c r="U7" s="1">
-        <v>4.537974826666666</v>
+        <v>7.9414559466666654</v>
       </c>
       <c r="V7" s="1">
-        <v>3.5860173999999994</v>
+        <v>6.2755304499999989</v>
       </c>
       <c r="W7" s="1">
-        <v>3.822661333333333</v>
+        <v>6.6896573333333329</v>
       </c>
       <c r="X7" s="1">
-        <v>3.8589139333333335</v>
+        <v>6.7530993833333337</v>
       </c>
       <c r="Y7" s="1">
-        <v>4.5943604000000002</v>
+        <v>8.0401307000000006</v>
       </c>
       <c r="Z7" s="1">
-        <v>3.3707189999999994</v>
+        <v>5.8987582499999984</v>
       </c>
       <c r="AA7" s="1">
-        <v>3.6205066666666674</v>
+        <v>6.335886666666668</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -71521,76 +71521,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>1.8284583240000003</v>
+        <v>3.1998020670000007</v>
       </c>
       <c r="E8" s="1">
-        <v>1.9864363999999999</v>
+        <v>3.4762636999999996</v>
       </c>
       <c r="F8" s="1">
-        <v>1.8317505439999999</v>
+        <v>3.2055634519999998</v>
       </c>
       <c r="G8" s="1">
-        <v>1.6185523199999998</v>
+        <v>2.8324665599999999</v>
       </c>
       <c r="H8" s="1">
-        <v>1.2607974399999999</v>
+        <v>2.2063955200000001</v>
       </c>
       <c r="I8" s="1">
-        <v>1.1144453120000002</v>
+        <v>1.9502792960000004</v>
       </c>
       <c r="J8" s="1">
-        <v>1.4054661060000002</v>
+        <v>2.4595656855000003</v>
       </c>
       <c r="K8" s="1">
-        <v>0.24879351466666666</v>
+        <v>0.43538865066666665</v>
       </c>
       <c r="L8" s="1">
-        <v>0.22325333333333339</v>
+        <v>0.39069333333333345</v>
       </c>
       <c r="M8" s="1">
-        <v>0.31217095</v>
+        <v>0.54629916249999999</v>
       </c>
       <c r="N8" s="1">
-        <v>0.18242673866666667</v>
+        <v>0.31924679266666667</v>
       </c>
       <c r="O8" s="1">
-        <v>0.23260973333333332</v>
+        <v>0.40706703333333333</v>
       </c>
       <c r="P8" s="1">
-        <v>0.36325740000000012</v>
+        <v>0.63570045000000019</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.67435655000000005</v>
+        <v>1.1801239625000002</v>
       </c>
       <c r="R8" s="1">
-        <v>0.69964159999999997</v>
+        <v>1.2243728</v>
       </c>
       <c r="S8" s="1">
-        <v>0.7018012079999999</v>
+        <v>1.2281521139999998</v>
       </c>
       <c r="T8" s="1">
-        <v>0.37800499999999998</v>
+        <v>0.66150874999999998</v>
       </c>
       <c r="U8" s="1">
-        <v>0.82551461999999975</v>
+        <v>1.4446505849999995</v>
       </c>
       <c r="V8" s="1">
-        <v>0.47078847199999996</v>
+        <v>0.82387982599999998</v>
       </c>
       <c r="W8" s="1">
-        <v>0.3616752299999999</v>
+        <v>0.63293165249999983</v>
       </c>
       <c r="X8" s="1">
-        <v>0.51291840000000011</v>
+        <v>0.89760720000000016</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.31010685333333332</v>
+        <v>0.54268699333333337</v>
       </c>
       <c r="Z8" s="1">
-        <v>1.4320202960000001</v>
+        <v>2.506035518</v>
       </c>
       <c r="AA8" s="1">
-        <v>1.6579135999999999</v>
+        <v>2.9013487999999996</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -71604,76 +71604,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-4.0422500000000001</v>
+        <v>-7.0739375000000004</v>
       </c>
       <c r="E9" s="1">
-        <v>-4.5045131999999999</v>
+        <v>-7.8828981000000002</v>
       </c>
       <c r="F9" s="1">
-        <v>-4.8614793333333344</v>
+        <v>-8.5075888333333349</v>
       </c>
       <c r="G9" s="1">
-        <v>-5.2441456666666664</v>
+        <v>-9.1772549166666657</v>
       </c>
       <c r="H9" s="1">
-        <v>-5.9521890133333342</v>
+        <v>-10.416330773333335</v>
       </c>
       <c r="I9" s="1">
-        <v>-6.0580307200000005</v>
+        <v>-10.601553760000002</v>
       </c>
       <c r="J9" s="1">
-        <v>-6.3918320660000001</v>
+        <v>-11.1857061155</v>
       </c>
       <c r="K9" s="1">
-        <v>-6.7543965066666658</v>
+        <v>-11.820193886666665</v>
       </c>
       <c r="L9" s="1">
-        <v>-6.5637123999999973</v>
+        <v>-11.486496699999995</v>
       </c>
       <c r="M9" s="1">
-        <v>-9.181003807799998</v>
+        <v>-16.066756663649997</v>
       </c>
       <c r="N9" s="1">
-        <v>-8.9914904272000022</v>
+        <v>-15.735108247600003</v>
       </c>
       <c r="O9" s="1">
-        <v>-8.3857533498666665</v>
+        <v>-14.675068362266666</v>
       </c>
       <c r="P9" s="1">
-        <v>-8.199303340800002</v>
+        <v>-14.348780846400004</v>
       </c>
       <c r="Q9" s="1">
-        <v>-7.9924043429999996</v>
+        <v>-13.98670760025</v>
       </c>
       <c r="R9" s="1">
-        <v>-7.4616937824000011</v>
+        <v>-13.057964119200001</v>
       </c>
       <c r="S9" s="1">
-        <v>-6.594958666666666</v>
+        <v>-11.541177666666666</v>
       </c>
       <c r="T9" s="1">
-        <v>-5.9829012936000003</v>
+        <v>-10.4700772638</v>
       </c>
       <c r="U9" s="1">
-        <v>-5.5097289728000005</v>
+        <v>-9.6420257024000016</v>
       </c>
       <c r="V9" s="1">
-        <v>-3.6078764466666668</v>
+        <v>-6.3137837816666673</v>
       </c>
       <c r="W9" s="1">
-        <v>-3.8421396683999984</v>
+        <v>-6.7237444196999974</v>
       </c>
       <c r="X9" s="1">
-        <v>-4.0608965599999989</v>
+        <v>-7.1065689799999978</v>
       </c>
       <c r="Y9" s="1">
-        <v>-4.099510838333333</v>
+        <v>-7.1741439670833325</v>
       </c>
       <c r="Z9" s="1">
-        <v>-3.6391074719999996</v>
+        <v>-6.3684380759999994</v>
       </c>
       <c r="AA9" s="1">
-        <v>-3.7857926399999999</v>
+        <v>-6.6251371199999998</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -71687,76 +71687,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>3.9721228619999995</v>
+        <v>6.9512150084999993</v>
       </c>
       <c r="E10" s="1">
-        <v>4.2911686959999988</v>
+        <v>7.5095452179999977</v>
       </c>
       <c r="F10" s="1">
-        <v>4.7204243199999993</v>
+        <v>8.2607425599999988</v>
       </c>
       <c r="G10" s="1">
-        <v>4.8755969096666671</v>
+        <v>8.5322945919166671</v>
       </c>
       <c r="H10" s="1">
-        <v>5.1896146216666645</v>
+        <v>9.0818255879166632</v>
       </c>
       <c r="I10" s="1">
-        <v>6.0172205166666677</v>
+        <v>10.530135904166668</v>
       </c>
       <c r="J10" s="1">
-        <v>5.3467823999999986</v>
+        <v>9.3568691999999984</v>
       </c>
       <c r="K10" s="1">
-        <v>6.0338023360000008</v>
+        <v>10.559154088000001</v>
       </c>
       <c r="L10" s="1">
-        <v>5.9983641844000006</v>
+        <v>10.4971373227</v>
       </c>
       <c r="M10" s="1">
-        <v>6.8418184088000009</v>
+        <v>11.973182215400001</v>
       </c>
       <c r="N10" s="1">
-        <v>7.1089586799999998</v>
+        <v>12.440677689999999</v>
       </c>
       <c r="O10" s="1">
-        <v>6.3219452780000003</v>
+        <v>11.0634042365</v>
       </c>
       <c r="P10" s="1">
-        <v>6.2942131200000011</v>
+        <v>11.014872960000002</v>
       </c>
       <c r="Q10" s="1">
-        <v>6.3277535047999995</v>
+        <v>11.073568633399999</v>
       </c>
       <c r="R10" s="1">
-        <v>6.1649501760000014</v>
+        <v>10.788662808000002</v>
       </c>
       <c r="S10" s="1">
-        <v>5.1820377792000007</v>
+        <v>9.0685661136000011</v>
       </c>
       <c r="T10" s="1">
-        <v>4.9251115749333314</v>
+        <v>8.6189452561333297</v>
       </c>
       <c r="U10" s="1">
-        <v>4.3564558335999992</v>
+        <v>7.6237977087999989</v>
       </c>
       <c r="V10" s="1">
-        <v>3.7653182699999994</v>
+        <v>6.5893069724999993</v>
       </c>
       <c r="W10" s="1">
-        <v>3.8608879466666668</v>
+        <v>6.7565539066666673</v>
       </c>
       <c r="X10" s="1">
-        <v>4.0132704906666667</v>
+        <v>7.0232233586666668</v>
       </c>
       <c r="Y10" s="1">
-        <v>4.7321912120000009</v>
+        <v>8.281334621000001</v>
       </c>
       <c r="Z10" s="1">
-        <v>3.4044261899999992</v>
+        <v>5.9577458324999988</v>
       </c>
       <c r="AA10" s="1">
-        <v>3.8015320000000012</v>
+        <v>6.6526810000000021</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -71770,76 +71770,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>1.7903890000000002</v>
+        <v>3.1331807500000002</v>
       </c>
       <c r="E11" s="1">
-        <v>1.8501123333333334</v>
+        <v>3.2376965833333333</v>
       </c>
       <c r="F11" s="1">
-        <v>1.6566669999999999</v>
+        <v>2.8991672499999996</v>
       </c>
       <c r="G11" s="1">
-        <v>1.5702866666666662</v>
+        <v>2.7480016666666658</v>
       </c>
       <c r="H11" s="1">
-        <v>1.2865279999999999</v>
+        <v>2.2514239999999996</v>
       </c>
       <c r="I11" s="1">
-        <v>1.0919173333333334</v>
+        <v>1.9108553333333336</v>
       </c>
       <c r="J11" s="1">
-        <v>1.3353263333333334</v>
+        <v>2.3368210833333336</v>
       </c>
       <c r="K11" s="1">
-        <v>0.23190133333333332</v>
+        <v>0.40582733333333332</v>
       </c>
       <c r="L11" s="1">
-        <v>0.20393333333333333</v>
+        <v>0.35688333333333333</v>
       </c>
       <c r="M11" s="1">
-        <v>0.29730566666666658</v>
+        <v>0.52028491666666654</v>
       </c>
       <c r="N11" s="1">
-        <v>0.17509133333333335</v>
+        <v>0.30640983333333338</v>
       </c>
       <c r="O11" s="1">
-        <v>0.21879133333333331</v>
+        <v>0.38288483333333329</v>
       </c>
       <c r="P11" s="1">
-        <v>0.34858033333333344</v>
+        <v>0.6100155833333335</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.64224433333333331</v>
+        <v>1.1239275833333333</v>
       </c>
       <c r="R11" s="1">
-        <v>0.68521599999999994</v>
+        <v>1.199128</v>
       </c>
       <c r="S11" s="1">
-        <v>0.67385399999999984</v>
+        <v>1.1792444999999998</v>
       </c>
       <c r="T11" s="1">
-        <v>0.37800499999999998</v>
+        <v>0.66150874999999998</v>
       </c>
       <c r="U11" s="1">
-        <v>0.76999399999999973</v>
+        <v>1.3474894999999996</v>
       </c>
       <c r="V11" s="1">
-        <v>0.45185799999999993</v>
+        <v>0.79075149999999983</v>
       </c>
       <c r="W11" s="1">
-        <v>0.3176989999999999</v>
+        <v>0.55597324999999986</v>
       </c>
       <c r="X11" s="1">
-        <v>0.48244799999999999</v>
+        <v>0.84428400000000003</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.29817966666666668</v>
+        <v>0.52181441666666672</v>
       </c>
       <c r="Z11" s="1">
-        <v>1.3609636666666667</v>
+        <v>2.3816864166666667</v>
       </c>
       <c r="AA11" s="1">
-        <v>1.6406436666666666</v>
+        <v>2.8711264166666668</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -71853,76 +71853,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-4.2039400000000002</v>
+        <v>-7.3568950000000006</v>
       </c>
       <c r="E12" s="1">
-        <v>-4.5045131999999999</v>
+        <v>-7.8828981000000002</v>
       </c>
       <c r="F12" s="1">
-        <v>-4.6184053666666669</v>
+        <v>-8.0822093916666677</v>
       </c>
       <c r="G12" s="1">
-        <v>-5.2441456666666664</v>
+        <v>-9.1772549166666657</v>
       </c>
       <c r="H12" s="1">
-        <v>-5.8926671231999999</v>
+        <v>-10.3121674656</v>
       </c>
       <c r="I12" s="1">
-        <v>-6.3003519487999995</v>
+        <v>-11.025615910399999</v>
       </c>
       <c r="J12" s="1">
-        <v>-6.2000771040200009</v>
+        <v>-10.850134932035001</v>
       </c>
       <c r="K12" s="1">
-        <v>-6.6868525415999978</v>
+        <v>-11.701991947799996</v>
       </c>
       <c r="L12" s="1">
-        <v>-6.6949866479999978</v>
+        <v>-11.716226633999996</v>
       </c>
       <c r="M12" s="1">
-        <v>-8.8137636554879979</v>
+        <v>-15.424086397103997</v>
       </c>
       <c r="N12" s="1">
-        <v>-9.0814053314720038</v>
+        <v>-15.892459330076006</v>
       </c>
       <c r="O12" s="1">
-        <v>-8.6373259503626674</v>
+        <v>-15.115320413134668</v>
       </c>
       <c r="P12" s="1">
-        <v>-7.9533242405759994</v>
+        <v>-13.918317421007998</v>
       </c>
       <c r="Q12" s="1">
-        <v>-7.5927841258499988</v>
+        <v>-13.287372220237497</v>
       </c>
       <c r="R12" s="1">
-        <v>-7.3870768445760016</v>
+        <v>-12.927384478008003</v>
       </c>
       <c r="S12" s="1">
-        <v>-6.594958666666666</v>
+        <v>-11.541177666666666</v>
       </c>
       <c r="T12" s="1">
-        <v>-6.2222173453440002</v>
+        <v>-10.888880354352001</v>
       </c>
       <c r="U12" s="1">
-        <v>-5.3995343933439992</v>
+        <v>-9.4491851883519988</v>
       </c>
       <c r="V12" s="1">
-        <v>-3.4635613888000001</v>
+        <v>-6.0612324304000005</v>
       </c>
       <c r="W12" s="1">
-        <v>-3.8805610650839988</v>
+        <v>-6.7909818638969979</v>
       </c>
       <c r="X12" s="1">
-        <v>-4.2639413879999992</v>
+        <v>-7.4618974289999986</v>
       </c>
       <c r="Y12" s="1">
-        <v>-4.099510838333333</v>
+        <v>-7.1741439670833325</v>
       </c>
       <c r="Z12" s="1">
-        <v>-3.52993424784</v>
+        <v>-6.17738493372</v>
       </c>
       <c r="AA12" s="1">
-        <v>-3.7100767871999998</v>
+        <v>-6.4926343776</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -71936,76 +71936,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>3.7735167188999998</v>
+        <v>6.6036542580750002</v>
       </c>
       <c r="E13" s="1">
-        <v>4.1624336351200002</v>
+        <v>7.2842588614600006</v>
       </c>
       <c r="F13" s="1">
-        <v>4.7676285631999988</v>
+        <v>8.343349985599998</v>
       </c>
       <c r="G13" s="1">
-        <v>4.7780849714733344</v>
+        <v>8.3616487000783355</v>
       </c>
       <c r="H13" s="1">
-        <v>5.137718475449998</v>
+        <v>8.9910073320374959</v>
       </c>
       <c r="I13" s="1">
-        <v>6.0773927218333341</v>
+        <v>10.635437263208335</v>
       </c>
       <c r="J13" s="1">
-        <v>5.3467823999999986</v>
+        <v>9.3568691999999984</v>
       </c>
       <c r="K13" s="1">
-        <v>6.0941403593599999</v>
+        <v>10.66474562888</v>
       </c>
       <c r="L13" s="1">
-        <v>5.9983641844000006</v>
+        <v>10.4971373227</v>
       </c>
       <c r="M13" s="1">
-        <v>7.0470729610640008</v>
+        <v>12.332377681862001</v>
       </c>
       <c r="N13" s="1">
-        <v>6.7535107459999999</v>
+        <v>11.818643805499999</v>
       </c>
       <c r="O13" s="1">
-        <v>6.0058480140999997</v>
+        <v>10.510234024675</v>
       </c>
       <c r="P13" s="1">
-        <v>6.4830395136000005</v>
+        <v>11.345319148800002</v>
       </c>
       <c r="Q13" s="1">
-        <v>6.2644759697519996</v>
+        <v>10.962832947066</v>
       </c>
       <c r="R13" s="1">
-        <v>6.0416511724800017</v>
+        <v>10.572889551840003</v>
       </c>
       <c r="S13" s="1">
-        <v>4.9229358902400007</v>
+        <v>8.6151378079200018</v>
       </c>
       <c r="T13" s="1">
-        <v>5.1713671536799986</v>
+        <v>9.0498925189399984</v>
       </c>
       <c r="U13" s="1">
-        <v>4.5307140669439994</v>
+        <v>7.9287496171519987</v>
       </c>
       <c r="V13" s="1">
-        <v>3.8029714526999996</v>
+        <v>6.6552000422249993</v>
       </c>
       <c r="W13" s="1">
-        <v>3.976714585066667</v>
+        <v>6.9592505238666673</v>
       </c>
       <c r="X13" s="1">
-        <v>3.9731377857600005</v>
+        <v>6.9529911250800005</v>
       </c>
       <c r="Y13" s="1">
-        <v>4.9214788604800015</v>
+        <v>8.6125880058400028</v>
       </c>
       <c r="Z13" s="1">
-        <v>3.4044261899999992</v>
+        <v>5.9577458324999988</v>
       </c>
       <c r="AA13" s="1">
-        <v>3.8775626400000012</v>
+        <v>6.7857346200000022</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -72019,76 +72019,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>1.8620045600000001</v>
+        <v>3.2585079800000001</v>
       </c>
       <c r="E14" s="1">
-        <v>1.8686134566666668</v>
+        <v>3.2700735491666668</v>
       </c>
       <c r="F14" s="1">
-        <v>1.6566669999999999</v>
+        <v>2.8991672499999996</v>
       </c>
       <c r="G14" s="1">
-        <v>1.6016923999999992</v>
+        <v>2.8029616999999987</v>
       </c>
       <c r="H14" s="1">
-        <v>1.2993932799999999</v>
+        <v>2.2739382399999997</v>
       </c>
       <c r="I14" s="1">
-        <v>1.0591598133333333</v>
+        <v>1.8535296733333333</v>
       </c>
       <c r="J14" s="1">
-        <v>1.3887393866666666</v>
+        <v>2.4302939266666668</v>
       </c>
       <c r="K14" s="1">
-        <v>0.22958232000000001</v>
+        <v>0.40176906000000001</v>
       </c>
       <c r="L14" s="1">
-        <v>0.21005133333333337</v>
+        <v>0.36758983333333339</v>
       </c>
       <c r="M14" s="1">
-        <v>0.29433260999999994</v>
+        <v>0.51508206749999985</v>
       </c>
       <c r="N14" s="1">
-        <v>0.18034407333333333</v>
+        <v>0.31560212833333334</v>
       </c>
       <c r="O14" s="1">
-        <v>0.20785176666666663</v>
+        <v>0.36374059166666661</v>
       </c>
       <c r="P14" s="1">
-        <v>0.34858033333333344</v>
+        <v>0.6100155833333335</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.66151166333333333</v>
+        <v>1.1576454108333334</v>
       </c>
       <c r="R14" s="1">
-        <v>0.67151167999999994</v>
+        <v>1.1751454399999999</v>
       </c>
       <c r="S14" s="1">
-        <v>0.68733107999999976</v>
+        <v>1.2028293899999996</v>
       </c>
       <c r="T14" s="1">
-        <v>0.36288479999999995</v>
+        <v>0.63504839999999996</v>
       </c>
       <c r="U14" s="1">
-        <v>0.73919423999999978</v>
+        <v>1.2935899199999996</v>
       </c>
       <c r="V14" s="1">
-        <v>0.43378367999999995</v>
+        <v>0.75912143999999993</v>
       </c>
       <c r="W14" s="1">
-        <v>0.33358394999999991</v>
+        <v>0.58377191249999982</v>
       </c>
       <c r="X14" s="1">
-        <v>0.46797456000000004</v>
+        <v>0.81895548000000007</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.30712505666666662</v>
+        <v>0.5374688491666666</v>
       </c>
       <c r="Z14" s="1">
-        <v>1.3745733033333334</v>
+        <v>2.4055032808333334</v>
       </c>
       <c r="AA14" s="1">
-        <v>1.6078307933333333</v>
+        <v>2.8137038883333334</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -72102,76 +72102,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-4.2459794000000004</v>
+        <v>-7.4304639500000009</v>
       </c>
       <c r="E15" s="1">
-        <v>-4.4144229360000002</v>
+        <v>-7.7252401380000002</v>
       </c>
       <c r="F15" s="1">
-        <v>-4.4336691520000002</v>
+        <v>-7.7589210160000004</v>
       </c>
       <c r="G15" s="1">
-        <v>-5.0343798399999988</v>
+        <v>-8.8101647199999977</v>
       </c>
       <c r="H15" s="1">
-        <v>-6.1283738081280008</v>
+        <v>-10.724654164224001</v>
       </c>
       <c r="I15" s="1">
-        <v>-6.1743449098239997</v>
+        <v>-10.805103592191999</v>
       </c>
       <c r="J15" s="1">
-        <v>-6.0760755619396001</v>
+        <v>-10.633132233394299</v>
       </c>
       <c r="K15" s="1">
-        <v>-6.419378439935997</v>
+        <v>-11.233912269887995</v>
       </c>
       <c r="L15" s="1">
-        <v>-6.7619365144799986</v>
+        <v>-11.833388900339997</v>
       </c>
       <c r="M15" s="1">
-        <v>-8.7256260189331183</v>
+        <v>-15.269845533132957</v>
       </c>
       <c r="N15" s="1">
-        <v>-9.4446615447308826</v>
+        <v>-16.528157703279046</v>
       </c>
       <c r="O15" s="1">
-        <v>-8.4645794313554159</v>
+        <v>-14.813014004871977</v>
       </c>
       <c r="P15" s="1">
-        <v>-7.8737909981702403</v>
+        <v>-13.77913424679792</v>
       </c>
       <c r="Q15" s="1">
-        <v>-7.2890727608159978</v>
+        <v>-12.755877331427996</v>
       </c>
       <c r="R15" s="1">
-        <v>-7.2393353076844811</v>
+        <v>-12.668836788447841</v>
       </c>
       <c r="S15" s="1">
-        <v>-6.2652107333333324</v>
+        <v>-10.964118783333332</v>
       </c>
       <c r="T15" s="1">
-        <v>-6.2222173453440002</v>
+        <v>-10.888880354352001</v>
       </c>
       <c r="U15" s="1">
-        <v>-5.3455390494105588</v>
+        <v>-9.3546933364684772</v>
       </c>
       <c r="V15" s="1">
-        <v>-3.4635613888000001</v>
+        <v>-6.0612324304000005</v>
       </c>
       <c r="W15" s="1">
-        <v>-3.958172286385679</v>
+        <v>-6.9268015011749382</v>
       </c>
       <c r="X15" s="1">
-        <v>-4.3065808018799991</v>
+        <v>-7.5365164032899985</v>
       </c>
       <c r="Y15" s="1">
-        <v>-4.1405059467166661</v>
+        <v>-7.2458854067541658</v>
       </c>
       <c r="Z15" s="1">
-        <v>-3.3887368779263998</v>
+        <v>-5.9302895363712</v>
       </c>
       <c r="AA15" s="1">
-        <v>-3.8584798586879998</v>
+        <v>-6.7523397527039997</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -72185,76 +72185,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>3.5848408829549996</v>
+        <v>6.2734715451712493</v>
       </c>
       <c r="E16" s="1">
-        <v>3.9959362897151998</v>
+        <v>6.9928885070015996</v>
       </c>
       <c r="F16" s="1">
-        <v>5.0060099913599991</v>
+        <v>8.7605174848799976</v>
       </c>
       <c r="G16" s="1">
-        <v>4.5869615726144</v>
+        <v>8.0271827520752002</v>
       </c>
       <c r="H16" s="1">
-        <v>5.3946043992224979</v>
+        <v>9.4405576986393704</v>
       </c>
       <c r="I16" s="1">
-        <v>5.8342970129600005</v>
+        <v>10.210019772680001</v>
       </c>
       <c r="J16" s="1">
-        <v>5.4002502239999997</v>
+        <v>9.4504378920000001</v>
       </c>
       <c r="K16" s="1">
-        <v>6.0941403593599999</v>
+        <v>10.66474562888</v>
       </c>
       <c r="L16" s="1">
-        <v>5.6984459751800012</v>
+        <v>9.9722804565650023</v>
       </c>
       <c r="M16" s="1">
-        <v>7.1880144202852811</v>
+        <v>12.579025235499241</v>
       </c>
       <c r="N16" s="1">
-        <v>6.6184405310800001</v>
+        <v>11.582270929390001</v>
       </c>
       <c r="O16" s="1">
-        <v>6.2460819346639989</v>
+        <v>10.930643385661998</v>
       </c>
       <c r="P16" s="1">
-        <v>6.2237179330560002</v>
+        <v>10.891506382848</v>
       </c>
       <c r="Q16" s="1">
-        <v>6.4524102488445587</v>
+        <v>11.291717935477978</v>
       </c>
       <c r="R16" s="1">
-        <v>6.1624841959296015</v>
+        <v>10.784347342876803</v>
       </c>
       <c r="S16" s="1">
-        <v>4.9721652491424004</v>
+        <v>8.701289185999201</v>
       </c>
       <c r="T16" s="1">
-        <v>5.2747944967535982</v>
+        <v>9.2308903693187965</v>
       </c>
       <c r="U16" s="1">
-        <v>4.4400997856051196</v>
+        <v>7.7701746248089592</v>
       </c>
       <c r="V16" s="1">
-        <v>3.8410011672269992</v>
+        <v>6.7217520426472488</v>
       </c>
       <c r="W16" s="1">
-        <v>3.976714585066667</v>
+        <v>6.9592505238666673</v>
       </c>
       <c r="X16" s="1">
-        <v>4.1320632971903999</v>
+        <v>7.2311107700832</v>
       </c>
       <c r="Y16" s="1">
-        <v>5.0199084376896019</v>
+        <v>8.7848397659568036</v>
       </c>
       <c r="Z16" s="1">
-        <v>3.4384704518999993</v>
+        <v>6.0173232908249989</v>
       </c>
       <c r="AA16" s="1">
-        <v>3.7224601344000017</v>
+        <v>6.5143052352000028</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -72268,76 +72268,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>1.7689043320000002</v>
+        <v>3.0955825810000004</v>
       </c>
       <c r="E17" s="1">
-        <v>1.9433579949333335</v>
+        <v>3.4008764911333338</v>
       </c>
       <c r="F17" s="1">
-        <v>1.6401003299999999</v>
+        <v>2.8701755775</v>
       </c>
       <c r="G17" s="1">
-        <v>1.6817770199999993</v>
+        <v>2.943109784999999</v>
       </c>
       <c r="H17" s="1">
-        <v>1.3123872127999998</v>
+        <v>2.2966776223999998</v>
       </c>
       <c r="I17" s="1">
-        <v>1.0485682152000002</v>
+        <v>1.8349943766000003</v>
       </c>
       <c r="J17" s="1">
-        <v>1.3470772050666664</v>
+        <v>2.3573851088666662</v>
       </c>
       <c r="K17" s="1">
-        <v>0.2318781432</v>
+        <v>0.40578675060000002</v>
       </c>
       <c r="L17" s="1">
-        <v>0.21005133333333337</v>
+        <v>0.36758983333333339</v>
       </c>
       <c r="M17" s="1">
-        <v>0.28550263169999995</v>
+        <v>0.4996296054749999</v>
       </c>
       <c r="N17" s="1">
-        <v>0.1785406326</v>
+        <v>0.31244610704999998</v>
       </c>
       <c r="O17" s="1">
-        <v>0.20577324899999996</v>
+        <v>0.36010318574999994</v>
       </c>
       <c r="P17" s="1">
-        <v>0.34858033333333344</v>
+        <v>0.6100155833333335</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.6681267799666667</v>
+        <v>1.1692218649416668</v>
       </c>
       <c r="R17" s="1">
-        <v>0.70508726399999988</v>
+        <v>1.2339027119999999</v>
       </c>
       <c r="S17" s="1">
-        <v>0.65296452599999966</v>
+        <v>1.1426879204999993</v>
       </c>
       <c r="T17" s="1">
-        <v>0.35199825599999995</v>
+        <v>0.61599694799999993</v>
       </c>
       <c r="U17" s="1">
-        <v>0.73180229759999982</v>
+        <v>1.2806540207999997</v>
       </c>
       <c r="V17" s="1">
-        <v>0.44245935359999988</v>
+        <v>0.77430386879999979</v>
       </c>
       <c r="W17" s="1">
-        <v>0.33358394999999991</v>
+        <v>0.58377191249999982</v>
       </c>
       <c r="X17" s="1">
-        <v>0.45861506880000008</v>
+        <v>0.80257637040000018</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.30712505666666662</v>
+        <v>0.5374688491666666</v>
       </c>
       <c r="Z17" s="1">
-        <v>1.3195903712000001</v>
+        <v>2.3092831496000001</v>
       </c>
       <c r="AA17" s="1">
-        <v>1.5756741774666665</v>
+        <v>2.7574298105666664</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -72351,76 +72351,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-4.2035196060000013</v>
+        <v>-7.3561593105000025</v>
       </c>
       <c r="E18" s="1">
-        <v>-4.5909998534400005</v>
+        <v>-8.0342497435200002</v>
       </c>
       <c r="F18" s="1">
-        <v>-4.2119856944</v>
+        <v>-7.3709749652000003</v>
       </c>
       <c r="G18" s="1">
-        <v>-5.084723638399999</v>
+        <v>-8.898266367199998</v>
       </c>
       <c r="H18" s="1">
-        <v>-6.3122250223718401</v>
+        <v>-11.04639378915072</v>
       </c>
       <c r="I18" s="1">
-        <v>-6.2360883589222382</v>
+        <v>-10.913154628113917</v>
       </c>
       <c r="J18" s="1">
-        <v>-5.8330325394620166</v>
+        <v>-10.207806944058529</v>
       </c>
       <c r="K18" s="1">
-        <v>-6.5477660087347163</v>
+        <v>-11.458590515285753</v>
       </c>
       <c r="L18" s="1">
-        <v>-6.8295558796247988</v>
+        <v>-11.951722789343398</v>
       </c>
       <c r="M18" s="1">
-        <v>-8.3766009781757944</v>
+        <v>-14.65905171180764</v>
       </c>
       <c r="N18" s="1">
-        <v>-9.6335547756255</v>
+        <v>-16.858720857344625</v>
       </c>
       <c r="O18" s="1">
-        <v>-8.3799336370418605</v>
+        <v>-14.664883864823256</v>
       </c>
       <c r="P18" s="1">
-        <v>-8.1100047281153476</v>
+        <v>-14.192508274201858</v>
       </c>
       <c r="Q18" s="1">
-        <v>-7.5077449436404775</v>
+        <v>-13.138553651370836</v>
       </c>
       <c r="R18" s="1">
-        <v>-7.6013020730687053</v>
+        <v>-13.302278627870233</v>
       </c>
       <c r="S18" s="1">
-        <v>-6.5158191626666655</v>
+        <v>-11.402683534666664</v>
       </c>
       <c r="T18" s="1">
-        <v>-6.0355508249836802</v>
+        <v>-10.56221394372144</v>
       </c>
       <c r="U18" s="1">
-        <v>-5.5059052208928767</v>
+        <v>-9.635334136562534</v>
       </c>
       <c r="V18" s="1">
-        <v>-3.2903833193600001</v>
+        <v>-5.7581708088800001</v>
       </c>
       <c r="W18" s="1">
-        <v>-3.8790088406579653</v>
+        <v>-6.7882654711514387</v>
       </c>
       <c r="X18" s="1">
-        <v>-4.2635149938611994</v>
+        <v>-7.4611512392570987</v>
       </c>
       <c r="Y18" s="1">
-        <v>-4.0162907683151667</v>
+        <v>-7.028508844551542</v>
       </c>
       <c r="Z18" s="1">
-        <v>-3.3209621403678717</v>
+        <v>-5.8116837456437755</v>
       </c>
       <c r="AA18" s="1">
-        <v>-3.8584798586879998</v>
+        <v>-6.7523397527039997</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -72434,76 +72434,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>3.4055988388072493</v>
+        <v>5.959797967912686</v>
       </c>
       <c r="E19" s="1">
-        <v>4.0758550155095037</v>
+        <v>7.1327462771416315</v>
       </c>
       <c r="F19" s="1">
-        <v>5.2062503910143993</v>
+        <v>9.1109381842751986</v>
       </c>
       <c r="G19" s="1">
-        <v>4.8163096512451204</v>
+        <v>8.4285418896789608</v>
       </c>
       <c r="H19" s="1">
-        <v>5.6103885751913971</v>
+        <v>9.8181800065849458</v>
       </c>
       <c r="I19" s="1">
-        <v>5.6592681025712004</v>
+        <v>9.9037191794995998</v>
       </c>
       <c r="J19" s="1">
-        <v>5.6702627351999988</v>
+        <v>9.9229597865999981</v>
       </c>
       <c r="K19" s="1">
-        <v>6.3988473773279999</v>
+        <v>11.197982910324001</v>
       </c>
       <c r="L19" s="1">
-        <v>5.5274925959246017</v>
+        <v>9.6731120428680537</v>
       </c>
       <c r="M19" s="1">
-        <v>7.1880144202852811</v>
+        <v>12.579025235499241</v>
       </c>
       <c r="N19" s="1">
-        <v>6.6846249363907999</v>
+        <v>11.698093638683901</v>
       </c>
       <c r="O19" s="1">
-        <v>6.1211602959707205</v>
+        <v>10.712030517948762</v>
       </c>
       <c r="P19" s="1">
-        <v>6.5349038297088002</v>
+        <v>11.4360817019904</v>
       </c>
       <c r="Q19" s="1">
-        <v>6.2588379413792232</v>
+        <v>10.95296639741364</v>
       </c>
       <c r="R19" s="1">
-        <v>5.8543599861331224</v>
+        <v>10.245129975732965</v>
       </c>
       <c r="S19" s="1">
-        <v>4.922443596650977</v>
+        <v>8.6142762941392093</v>
       </c>
       <c r="T19" s="1">
-        <v>5.2747944967535982</v>
+        <v>9.2308903693187965</v>
       </c>
       <c r="U19" s="1">
-        <v>4.528901781317221</v>
+        <v>7.9255781173051369</v>
       </c>
       <c r="V19" s="1">
-        <v>3.9946412139160792</v>
+        <v>6.9906221243531386</v>
       </c>
       <c r="W19" s="1">
-        <v>4.0960160226186675</v>
+        <v>7.1680280395826683</v>
       </c>
       <c r="X19" s="1">
-        <v>4.1320632971903999</v>
+        <v>7.2311107700832</v>
       </c>
       <c r="Y19" s="1">
-        <v>4.9195102689358094</v>
+        <v>8.6091429706376665</v>
       </c>
       <c r="Z19" s="1">
-        <v>3.3009316338239993</v>
+        <v>5.7766303591919987</v>
       </c>
       <c r="AA19" s="1">
-        <v>3.610786330368001</v>
+        <v>6.3188760781440019</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -72517,76 +72517,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>1.9694279000000006</v>
+        <v>3.4464988250000008</v>
       </c>
       <c r="E20" s="1">
-        <v>2.0351235666666669</v>
+        <v>3.5614662416666674</v>
       </c>
       <c r="F20" s="1">
-        <v>1.8223337000000004</v>
+        <v>3.1890839750000008</v>
       </c>
       <c r="G20" s="1">
-        <v>1.7273153333333331</v>
+        <v>3.0228018333333329</v>
       </c>
       <c r="H20" s="1">
-        <v>1.4151807999999999</v>
+        <v>2.4765663999999998</v>
       </c>
       <c r="I20" s="1">
-        <v>1.2011090666666668</v>
+        <v>2.1019408666666668</v>
       </c>
       <c r="J20" s="1">
-        <v>1.4688589666666667</v>
+        <v>2.570503191666667</v>
       </c>
       <c r="K20" s="1">
-        <v>0.25509146666666671</v>
+        <v>0.44641006666666672</v>
       </c>
       <c r="L20" s="1">
-        <v>0.22432666666666667</v>
+        <v>0.39257166666666665</v>
       </c>
       <c r="M20" s="1">
-        <v>0.32703623333333326</v>
+        <v>0.57231340833333322</v>
       </c>
       <c r="N20" s="1">
-        <v>0.19260046666666666</v>
+        <v>0.33705081666666664</v>
       </c>
       <c r="O20" s="1">
-        <v>0.24067046666666661</v>
+        <v>0.42117331666666658</v>
       </c>
       <c r="P20" s="1">
-        <v>0.38343836666666675</v>
+        <v>0.67101714166666682</v>
       </c>
       <c r="Q20" s="1">
-        <v>0.70646876666666669</v>
+        <v>1.2363203416666666</v>
       </c>
       <c r="R20" s="1">
-        <v>0.75373760000000001</v>
+        <v>1.3190408</v>
       </c>
       <c r="S20" s="1">
-        <v>0.74123939999999988</v>
+        <v>1.2971689499999999</v>
       </c>
       <c r="T20" s="1">
-        <v>0.41580549999999999</v>
+        <v>0.72765962500000003</v>
       </c>
       <c r="U20" s="1">
-        <v>0.84699339999999979</v>
+        <v>1.4822384499999997</v>
       </c>
       <c r="V20" s="1">
-        <v>0.49704379999999998</v>
+        <v>0.86982664999999992</v>
       </c>
       <c r="W20" s="1">
-        <v>0.34946889999999992</v>
+        <v>0.61157057499999989</v>
       </c>
       <c r="X20" s="1">
-        <v>0.53069280000000008</v>
+        <v>0.9287124000000001</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.32799763333333332</v>
+        <v>0.57399585833333333</v>
       </c>
       <c r="Z20" s="1">
-        <v>1.4970600333333335</v>
+        <v>2.6198550583333335</v>
       </c>
       <c r="AA20" s="1">
-        <v>1.8047080333333332</v>
+        <v>3.1582390583333328</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -72600,76 +72600,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-4.0774140178200016</v>
+        <v>-7.135474531185003</v>
       </c>
       <c r="E21" s="1">
-        <v>-4.8205498461120007</v>
+        <v>-8.4359622306960009</v>
       </c>
       <c r="F21" s="1">
-        <v>-4.0856261235679989</v>
+        <v>-7.1498457162439983</v>
       </c>
       <c r="G21" s="1">
-        <v>-5.186418111167999</v>
+        <v>-9.0762316945439991</v>
       </c>
       <c r="H21" s="1">
-        <v>-6.5647140232667143</v>
+        <v>-11.488249540716749</v>
       </c>
       <c r="I21" s="1">
-        <v>-6.2360883589222382</v>
+        <v>-10.913154628113917</v>
       </c>
       <c r="J21" s="1">
-        <v>-5.8913628648566378</v>
+        <v>-10.309885013499116</v>
       </c>
       <c r="K21" s="1">
-        <v>-6.4822883486473692</v>
+        <v>-11.344004610132895</v>
       </c>
       <c r="L21" s="1">
-        <v>-6.8978514384210454</v>
+        <v>-12.07124001723683</v>
       </c>
       <c r="M21" s="1">
-        <v>-8.3766009781757944</v>
+        <v>-14.65905171180764</v>
       </c>
       <c r="N21" s="1">
-        <v>-9.5372192278692456</v>
+        <v>-16.69013364877118</v>
       </c>
       <c r="O21" s="1">
-        <v>-8.7151309825235366</v>
+        <v>-15.25147921941619</v>
       </c>
       <c r="P21" s="1">
-        <v>-8.1100047281153476</v>
+        <v>-14.192508274201858</v>
       </c>
       <c r="Q21" s="1">
-        <v>-7.7329772919496911</v>
+        <v>-13.532710260911958</v>
       </c>
       <c r="R21" s="1">
-        <v>-7.3732630108766442</v>
+        <v>-12.903210269034128</v>
       </c>
       <c r="S21" s="1">
-        <v>-6.3855027794133319</v>
+        <v>-11.174629863973331</v>
       </c>
       <c r="T21" s="1">
-        <v>-5.7337732837344966</v>
+        <v>-10.03410324653537</v>
       </c>
       <c r="U21" s="1">
-        <v>-5.5059052208928767</v>
+        <v>-9.635334136562534</v>
       </c>
       <c r="V21" s="1">
-        <v>-3.3561909857471997</v>
+        <v>-5.8733342250575991</v>
       </c>
       <c r="W21" s="1">
-        <v>-3.9953791058777042</v>
+        <v>-6.9919134352859826</v>
       </c>
       <c r="X21" s="1">
-        <v>-4.4340555936156472</v>
+        <v>-7.7595972888273828</v>
       </c>
       <c r="Y21" s="1">
-        <v>-3.9359649529488636</v>
+        <v>-6.887938667660511</v>
       </c>
       <c r="Z21" s="1">
-        <v>-3.3209621403678717</v>
+        <v>-5.8116837456437755</v>
       </c>
       <c r="AA21" s="1">
-        <v>-3.9742342544486391</v>
+        <v>-6.9549099452851184</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -72683,76 +72683,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>3.2353188968668873</v>
+        <v>5.6618080695170532</v>
       </c>
       <c r="E22" s="1">
-        <v>4.157372115819693</v>
+        <v>7.2754012026844626</v>
       </c>
       <c r="F22" s="1">
-        <v>5.3624379027448308</v>
+        <v>9.3842663298034541</v>
       </c>
       <c r="G22" s="1">
-        <v>4.7199834582202174</v>
+        <v>8.2599710518853797</v>
       </c>
       <c r="H22" s="1">
-        <v>5.7225963466952257</v>
+        <v>10.014543606716645</v>
       </c>
       <c r="I22" s="1">
-        <v>5.6026754215454879</v>
+        <v>9.8046819877046048</v>
       </c>
       <c r="J22" s="1">
-        <v>5.5001548531439992</v>
+        <v>9.6252709930019993</v>
       </c>
       <c r="K22" s="1">
-        <v>6.5908127986478391</v>
+        <v>11.533922397633718</v>
       </c>
       <c r="L22" s="1">
-        <v>5.8038672257208317</v>
+        <v>10.156767645011456</v>
       </c>
       <c r="M22" s="1">
-        <v>7.4036548528938404</v>
+        <v>12.956395992564222</v>
       </c>
       <c r="N22" s="1">
-        <v>6.5509324376629827</v>
+        <v>11.464131765910221</v>
       </c>
       <c r="O22" s="1">
-        <v>6.2435835018901349</v>
+        <v>10.926271128307736</v>
       </c>
       <c r="P22" s="1">
-        <v>6.7962999828971524</v>
+        <v>11.893524970070017</v>
       </c>
       <c r="Q22" s="1">
-        <v>6.4466030796205986</v>
+        <v>11.281555389336047</v>
       </c>
       <c r="R22" s="1">
-        <v>5.6787291865491278</v>
+        <v>9.9377760764609739</v>
       </c>
       <c r="S22" s="1">
-        <v>4.8732191606844664</v>
+        <v>8.5281335311978168</v>
       </c>
       <c r="T22" s="1">
-        <v>5.38029038668867</v>
+        <v>9.4155081767051723</v>
       </c>
       <c r="U22" s="1">
-        <v>4.3930347278777058</v>
+        <v>7.6878107737859853</v>
       </c>
       <c r="V22" s="1">
-        <v>4.1144804503335619</v>
+        <v>7.2003407880837331</v>
       </c>
       <c r="W22" s="1">
-        <v>4.2598566635234141</v>
+        <v>7.4547491611659744</v>
       </c>
       <c r="X22" s="1">
-        <v>4.0907426642184967</v>
+        <v>7.1587996623823695</v>
       </c>
       <c r="Y22" s="1">
-        <v>4.870315166246451</v>
+        <v>8.5230515409312897</v>
       </c>
       <c r="Z22" s="1">
-        <v>3.3669502665004791</v>
+        <v>5.8921629663758388</v>
       </c>
       <c r="AA22" s="1">
-        <v>3.646894193671681</v>
+        <v>6.3820648389254417</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -72766,76 +72766,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>2.0678992950000006</v>
+        <v>3.6188237662500011</v>
       </c>
       <c r="E23" s="1">
-        <v>2.1368797449999999</v>
+        <v>3.7395395537499998</v>
       </c>
       <c r="F23" s="1">
-        <v>1.7494403519999999</v>
+        <v>3.0615206159999997</v>
       </c>
       <c r="G23" s="1">
-        <v>1.6754958733333332</v>
+        <v>2.9321177783333332</v>
       </c>
       <c r="H23" s="1">
-        <v>1.4010289919999999</v>
+        <v>2.4518007359999996</v>
       </c>
       <c r="I23" s="1">
-        <v>1.1770868853333336</v>
+        <v>2.059902049333334</v>
       </c>
       <c r="J23" s="1">
-        <v>1.4541703769999998</v>
+        <v>2.5447981597499996</v>
       </c>
       <c r="K23" s="1">
-        <v>0.25764238133333334</v>
+        <v>0.45087416733333335</v>
       </c>
       <c r="L23" s="1">
-        <v>0.21984013333333333</v>
+        <v>0.38472023333333333</v>
       </c>
       <c r="M23" s="1">
-        <v>0.33030659566666659</v>
+        <v>0.57803654241666658</v>
       </c>
       <c r="N23" s="1">
-        <v>0.20030448533333337</v>
+        <v>0.3505328493333334</v>
       </c>
       <c r="O23" s="1">
-        <v>0.25029728533333334</v>
+        <v>0.43802024933333333</v>
       </c>
       <c r="P23" s="1">
-        <v>0.37576959933333343</v>
+        <v>0.65759679883333355</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.73472751733333341</v>
+        <v>1.2857731553333336</v>
       </c>
       <c r="R23" s="1">
-        <v>0.79142447999999987</v>
+        <v>1.3849928399999998</v>
       </c>
       <c r="S23" s="1">
-        <v>0.70417742999999999</v>
+        <v>1.2323105025000001</v>
       </c>
       <c r="T23" s="1">
-        <v>0.42827966500000003</v>
+        <v>0.74948941375000011</v>
       </c>
       <c r="U23" s="1">
-        <v>0.88087313599999983</v>
+        <v>1.5415279879999997</v>
       </c>
       <c r="V23" s="1">
-        <v>0.48710292400000005</v>
+        <v>0.85243011700000004</v>
       </c>
       <c r="W23" s="1">
-        <v>0.34597421099999992</v>
+        <v>0.60545486924999992</v>
       </c>
       <c r="X23" s="1">
-        <v>0.53069280000000008</v>
+        <v>0.9287124000000001</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.33783756233333334</v>
+        <v>0.59121573408333339</v>
       </c>
       <c r="Z23" s="1">
-        <v>1.5719130350000003</v>
+        <v>2.7508478112500008</v>
       </c>
       <c r="AA23" s="1">
-        <v>1.8408021940000001</v>
+        <v>3.2214038395000002</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -72849,76 +72849,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-4.118188157998202</v>
+        <v>-7.2068292764968538</v>
       </c>
       <c r="E24" s="1">
-        <v>-4.9651663414953608</v>
+        <v>-8.6890410976168813</v>
       </c>
       <c r="F24" s="1">
-        <v>-4.003913601096639</v>
+        <v>-7.0068488019191184</v>
       </c>
       <c r="G24" s="1">
-        <v>-5.082689748944639</v>
+        <v>-8.8947070606531184</v>
       </c>
       <c r="H24" s="1">
-        <v>-6.6303611634993826</v>
+        <v>-11.60313203612392</v>
       </c>
       <c r="I24" s="1">
-        <v>-6.0490057081545707</v>
+        <v>-10.5857599892705</v>
       </c>
       <c r="J24" s="1">
-        <v>-5.7735356075595057</v>
+        <v>-10.103687313229134</v>
       </c>
       <c r="K24" s="1">
-        <v>-6.6119341156203157</v>
+        <v>-11.570884702335553</v>
       </c>
       <c r="L24" s="1">
-        <v>-7.1737654959578876</v>
+        <v>-12.554089617926303</v>
       </c>
       <c r="M24" s="1">
-        <v>-8.6278990075210675</v>
+        <v>-15.098823263161869</v>
       </c>
       <c r="N24" s="1">
-        <v>-9.1557304587544763</v>
+        <v>-16.022528302820334</v>
       </c>
       <c r="O24" s="1">
-        <v>-8.9765849119992431</v>
+        <v>-15.709023595998676</v>
       </c>
       <c r="P24" s="1">
-        <v>-7.8667045862718892</v>
+        <v>-13.766733025975807</v>
       </c>
       <c r="Q24" s="1">
-        <v>-7.5783177461106979</v>
+        <v>-13.262056055693721</v>
       </c>
       <c r="R24" s="1">
-        <v>-7.3732630108766442</v>
+        <v>-12.903210269034128</v>
       </c>
       <c r="S24" s="1">
-        <v>-6.1300826682367981</v>
+        <v>-10.727644669414397</v>
       </c>
       <c r="T24" s="1">
-        <v>-5.7911110165718407</v>
+        <v>-10.134444279000721</v>
       </c>
       <c r="U24" s="1">
-        <v>-5.2306099598482332</v>
+        <v>-9.1535674297344087</v>
       </c>
       <c r="V24" s="1">
-        <v>-3.2219433463173122</v>
+        <v>-5.6384008560552967</v>
       </c>
       <c r="W24" s="1">
-        <v>-3.9953791058777042</v>
+        <v>-6.9919134352859826</v>
       </c>
       <c r="X24" s="1">
-        <v>-4.6114178173602731</v>
+        <v>-8.0699811803804771</v>
       </c>
       <c r="Y24" s="1">
-        <v>-3.8178860043603975</v>
+        <v>-6.6813005076306959</v>
       </c>
       <c r="Z24" s="1">
-        <v>-3.3873813831752297</v>
+        <v>-5.9279174205566516</v>
       </c>
       <c r="AA24" s="1">
-        <v>-3.934491911904153</v>
+        <v>-6.8853608458322677</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -72932,76 +72932,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>3.2029657078982186</v>
+        <v>5.6051899888218824</v>
       </c>
       <c r="E25" s="1">
-        <v>4.157372115819693</v>
+        <v>7.2754012026844626</v>
       </c>
       <c r="F25" s="1">
-        <v>5.0943160076075893</v>
+        <v>8.9150530133132815</v>
       </c>
       <c r="G25" s="1">
-        <v>4.8143831273846223</v>
+        <v>8.4251704729230887</v>
       </c>
       <c r="H25" s="1">
-        <v>5.8370482736291303</v>
+        <v>10.214834478850978</v>
       </c>
       <c r="I25" s="1">
-        <v>5.7707556841918519</v>
+        <v>10.09882244733574</v>
       </c>
       <c r="J25" s="1">
-        <v>5.5551564016754389</v>
+        <v>9.7215237029320178</v>
       </c>
       <c r="K25" s="1">
-        <v>6.5908127986478391</v>
+        <v>11.533922397633718</v>
       </c>
       <c r="L25" s="1">
-        <v>5.5136738644347894</v>
+        <v>9.6489292627608805</v>
       </c>
       <c r="M25" s="1">
-        <v>7.6998010470095934</v>
+        <v>13.474651832266789</v>
       </c>
       <c r="N25" s="1">
-        <v>6.7474604107928728</v>
+        <v>11.808055718887527</v>
       </c>
       <c r="O25" s="1">
-        <v>6.3060193369090358</v>
+        <v>11.035533839590812</v>
       </c>
       <c r="P25" s="1">
-        <v>6.7962999828971524</v>
+        <v>11.893524970070017</v>
       </c>
       <c r="Q25" s="1">
-        <v>6.3821370488243936</v>
+        <v>11.16873983544269</v>
       </c>
       <c r="R25" s="1">
-        <v>5.3947927272216711</v>
+        <v>9.4408872726379247</v>
       </c>
       <c r="S25" s="1">
-        <v>4.6295582026502426</v>
+        <v>8.1017268546379242</v>
       </c>
       <c r="T25" s="1">
-        <v>5.2188816750880092</v>
+        <v>9.1330429314040167</v>
       </c>
       <c r="U25" s="1">
-        <v>4.305174033320152</v>
+        <v>7.5340545583102658</v>
       </c>
       <c r="V25" s="1">
-        <v>4.1144804503335619</v>
+        <v>7.2003407880837331</v>
       </c>
       <c r="W25" s="1">
-        <v>4.3876523634291162</v>
+        <v>7.6783916360009536</v>
       </c>
       <c r="X25" s="1">
-        <v>3.8862055310075712</v>
+        <v>6.8008596792632492</v>
       </c>
       <c r="Y25" s="1">
-        <v>5.1138309245587736</v>
+        <v>8.9492041179778532</v>
       </c>
       <c r="Z25" s="1">
-        <v>3.2996112611704693</v>
+        <v>5.7743197070483214</v>
       </c>
       <c r="AA25" s="1">
-        <v>3.7563010194818314</v>
+        <v>6.5735267840932048</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -73015,76 +73015,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>2.1299362738500007</v>
+        <v>3.7273884792375012</v>
       </c>
       <c r="E26" s="1">
-        <v>2.15824854245</v>
+        <v>3.7769349492875</v>
       </c>
       <c r="F26" s="1">
-        <v>1.7319459484800002</v>
+        <v>3.0309054098400003</v>
       </c>
       <c r="G26" s="1">
-        <v>1.7592706669999998</v>
+        <v>3.0787236672499998</v>
       </c>
       <c r="H26" s="1">
-        <v>1.4150392819200002</v>
+        <v>2.4763187433600002</v>
       </c>
       <c r="I26" s="1">
-        <v>1.1770868853333336</v>
+        <v>2.059902049333334</v>
       </c>
       <c r="J26" s="1">
-        <v>1.3814618581499998</v>
+        <v>2.4175582517624994</v>
       </c>
       <c r="K26" s="1">
-        <v>0.24476026226666669</v>
+        <v>0.42833045896666672</v>
       </c>
       <c r="L26" s="1">
-        <v>0.20884812666666666</v>
+        <v>0.36548422166666666</v>
       </c>
       <c r="M26" s="1">
-        <v>0.32039739779666659</v>
+        <v>0.56069544614416655</v>
       </c>
       <c r="N26" s="1">
-        <v>0.19830144048000001</v>
+        <v>0.34702752083999999</v>
       </c>
       <c r="O26" s="1">
-        <v>0.25530323103999997</v>
+        <v>0.44678065431999991</v>
       </c>
       <c r="P26" s="1">
-        <v>0.36825420734666675</v>
+        <v>0.6444448628566668</v>
       </c>
       <c r="Q26" s="1">
-        <v>0.77146389320000008</v>
+        <v>1.3500618131000002</v>
       </c>
       <c r="R26" s="1">
-        <v>0.83099570399999989</v>
+        <v>1.4542424819999997</v>
       </c>
       <c r="S26" s="1">
-        <v>0.73938630149999984</v>
+        <v>1.2939260276249998</v>
       </c>
       <c r="T26" s="1">
-        <v>0.43256246165000006</v>
+        <v>0.75698430788750015</v>
       </c>
       <c r="U26" s="1">
-        <v>0.88087313599999983</v>
+        <v>1.5415279879999997</v>
       </c>
       <c r="V26" s="1">
-        <v>0.48710292400000005</v>
+        <v>0.85243011700000004</v>
       </c>
       <c r="W26" s="1">
-        <v>0.33213524255999993</v>
+        <v>0.58123667447999994</v>
       </c>
       <c r="X26" s="1">
-        <v>0.51477201600000011</v>
+        <v>0.90085102800000016</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.34121593795666666</v>
+        <v>0.59712789142416667</v>
       </c>
       <c r="Z26" s="1">
-        <v>1.5247556439500001</v>
+        <v>2.6683223769125002</v>
       </c>
       <c r="AA26" s="1">
-        <v>1.8960262598199999</v>
+        <v>3.3180459546850001</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -73098,76 +73098,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-4.3240975658981116</v>
+        <v>-7.5671707403216955</v>
       </c>
       <c r="E27" s="1">
-        <v>-4.9155146780804069</v>
+        <v>-8.6021506866407123</v>
       </c>
       <c r="F27" s="1">
-        <v>-3.9638744650856732</v>
+        <v>-6.936780313899928</v>
       </c>
       <c r="G27" s="1">
-        <v>-4.9302090564762997</v>
+        <v>-8.6278658488335243</v>
       </c>
       <c r="H27" s="1">
-        <v>-6.5640575518643898</v>
+        <v>-11.487100715762683</v>
       </c>
       <c r="I27" s="1">
-        <v>-6.2304758793992088</v>
+        <v>-10.903332788948616</v>
       </c>
       <c r="J27" s="1">
-        <v>-5.4848588271815295</v>
+        <v>-9.5985029475676775</v>
       </c>
       <c r="K27" s="1">
-        <v>-6.5458147744641133</v>
+        <v>-11.455175855312199</v>
       </c>
       <c r="L27" s="1">
-        <v>-6.9585525310791505</v>
+        <v>-12.177466929388514</v>
       </c>
       <c r="M27" s="1">
-        <v>-8.8867359777467012</v>
+        <v>-15.551787961056727</v>
       </c>
       <c r="N27" s="1">
-        <v>-9.1557304587544763</v>
+        <v>-16.022528302820334</v>
       </c>
       <c r="O27" s="1">
-        <v>-8.9765849119992431</v>
+        <v>-15.709023595998676</v>
       </c>
       <c r="P27" s="1">
-        <v>-7.7093704945464516</v>
+        <v>-13.491398365456291</v>
       </c>
       <c r="Q27" s="1">
-        <v>-7.5783177461106979</v>
+        <v>-13.262056055693721</v>
       </c>
       <c r="R27" s="1">
-        <v>-7.5207282710941774</v>
+        <v>-13.16127447441481</v>
       </c>
       <c r="S27" s="1">
-        <v>-6.2526843216015342</v>
+        <v>-10.942197562802685</v>
       </c>
       <c r="T27" s="1">
-        <v>-5.9648443470689969</v>
+        <v>-10.438477607370745</v>
       </c>
       <c r="U27" s="1">
-        <v>-5.2306099598482332</v>
+        <v>-9.1535674297344087</v>
       </c>
       <c r="V27" s="1">
-        <v>-3.2863822132436589</v>
+        <v>-5.751168873176403</v>
       </c>
       <c r="W27" s="1">
-        <v>-4.1551942701128128</v>
+        <v>-7.2715899726974227</v>
       </c>
       <c r="X27" s="1">
-        <v>-4.4730752828394653</v>
+        <v>-7.8278817449690639</v>
       </c>
       <c r="Y27" s="1">
-        <v>-3.8560648644040008</v>
+        <v>-6.7481135127070013</v>
       </c>
       <c r="Z27" s="1">
-        <v>-3.2180123140164683</v>
+        <v>-5.6315215495288191</v>
       </c>
       <c r="AA27" s="1">
-        <v>-4.0131817501422367</v>
+        <v>-7.0230680627489139</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -73181,76 +73181,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>3.1068767366612722</v>
+        <v>5.4370342891572268</v>
       </c>
       <c r="E28" s="1">
-        <v>4.0326509523451035</v>
+        <v>7.0571391666039309</v>
       </c>
       <c r="F28" s="1">
-        <v>5.0943160076075893</v>
+        <v>8.9150530133132815</v>
       </c>
       <c r="G28" s="1">
-        <v>4.9588146212061597</v>
+        <v>8.6779255871107797</v>
       </c>
       <c r="H28" s="1">
-        <v>6.1289006873105869</v>
+        <v>10.725576202793526</v>
       </c>
       <c r="I28" s="1">
-        <v>5.7130481273499329</v>
+        <v>9.997834222862382</v>
       </c>
       <c r="J28" s="1">
-        <v>5.8329142217592107</v>
+        <v>10.207599888078619</v>
       </c>
       <c r="K28" s="1">
-        <v>6.4589965426748828</v>
+        <v>11.303243949681045</v>
       </c>
       <c r="L28" s="1">
-        <v>5.4585371257904418</v>
+        <v>9.552439970133273</v>
       </c>
       <c r="M28" s="1">
-        <v>8.0847910993600749</v>
+        <v>14.148384423880131</v>
       </c>
       <c r="N28" s="1">
-        <v>7.0173588272245881</v>
+        <v>12.280377947643029</v>
       </c>
       <c r="O28" s="1">
-        <v>6.1168387568017657</v>
+        <v>10.704467824403089</v>
       </c>
       <c r="P28" s="1">
-        <v>6.7962999828971524</v>
+        <v>11.893524970070017</v>
       </c>
       <c r="Q28" s="1">
-        <v>6.6374225307773678</v>
+        <v>11.615489428860393</v>
       </c>
       <c r="R28" s="1">
-        <v>5.3947927272216711</v>
+        <v>9.4408872726379247</v>
       </c>
       <c r="S28" s="1">
-        <v>4.5369670385972372</v>
+        <v>7.9396923175451652</v>
       </c>
       <c r="T28" s="1">
-        <v>5.0623152248353689</v>
+        <v>8.8590516434618962</v>
       </c>
       <c r="U28" s="1">
-        <v>4.5204327349861595</v>
+        <v>7.9107572862257793</v>
       </c>
       <c r="V28" s="1">
-        <v>4.1144804503335619</v>
+        <v>7.2003407880837331</v>
       </c>
       <c r="W28" s="1">
-        <v>4.3437758397948256</v>
+        <v>7.6016077196409446</v>
       </c>
       <c r="X28" s="1">
-        <v>4.0416537522478739</v>
+        <v>7.0728940664337792</v>
       </c>
       <c r="Y28" s="1">
-        <v>4.9604159968220101</v>
+        <v>8.6807279944385183</v>
       </c>
       <c r="Z28" s="1">
-        <v>3.3985995990055833</v>
+        <v>5.9475492982597711</v>
       </c>
       <c r="AA28" s="1">
-        <v>3.6436119888973764</v>
+        <v>6.3763209805704086</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -73264,76 +73264,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>1.8709565050000003</v>
+        <v>3.2741738837500005</v>
       </c>
       <c r="E29" s="1">
-        <v>1.9333673883333333</v>
+        <v>3.3833929295833332</v>
       </c>
       <c r="F29" s="1">
-        <v>1.7312170150000001</v>
+        <v>3.0296297762500002</v>
       </c>
       <c r="G29" s="1">
-        <v>1.6409495666666665</v>
+        <v>2.8716617416666663</v>
       </c>
       <c r="H29" s="1">
-        <v>1.3444217600000001</v>
+        <v>2.3527380800000004</v>
       </c>
       <c r="I29" s="1">
-        <v>1.1410536133333333</v>
+        <v>1.9968438233333332</v>
       </c>
       <c r="J29" s="1">
-        <v>1.3954160183333333</v>
+        <v>2.4419780320833331</v>
       </c>
       <c r="K29" s="1">
-        <v>0.24233689333333339</v>
+        <v>0.42408956333333342</v>
       </c>
       <c r="L29" s="1">
-        <v>0.21311033333333332</v>
+        <v>0.37294308333333331</v>
       </c>
       <c r="M29" s="1">
-        <v>0.3106844216666666</v>
+        <v>0.54369773791666653</v>
       </c>
       <c r="N29" s="1">
-        <v>0.18297044333333334</v>
+        <v>0.32019827583333338</v>
       </c>
       <c r="O29" s="1">
-        <v>0.22863694333333326</v>
+        <v>0.4001146508333332</v>
       </c>
       <c r="P29" s="1">
-        <v>0.36426644833333338</v>
+        <v>0.63746628458333343</v>
       </c>
       <c r="Q29" s="1">
-        <v>0.6711453283333334</v>
+        <v>1.1745043245833335</v>
       </c>
       <c r="R29" s="1">
-        <v>0.71605072000000003</v>
+        <v>1.25308876</v>
       </c>
       <c r="S29" s="1">
-        <v>0.70417742999999977</v>
+        <v>1.2323105024999996</v>
       </c>
       <c r="T29" s="1">
-        <v>0.39501522499999991</v>
+        <v>0.69127664374999986</v>
       </c>
       <c r="U29" s="1">
-        <v>0.80464372999999989</v>
+        <v>1.4081265274999999</v>
       </c>
       <c r="V29" s="1">
-        <v>0.47219160999999993</v>
+        <v>0.82633531749999989</v>
       </c>
       <c r="W29" s="1">
-        <v>0.33199545499999994</v>
+        <v>0.58099204624999989</v>
       </c>
       <c r="X29" s="1">
-        <v>0.50415816000000002</v>
+        <v>0.88227677999999998</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.31159775166666664</v>
+        <v>0.54529606541666664</v>
       </c>
       <c r="Z29" s="1">
-        <v>1.4222070316666668</v>
+        <v>2.4888623054166672</v>
       </c>
       <c r="AA29" s="1">
-        <v>1.7144726316666665</v>
+        <v>3.0003271054166665</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -73347,76 +73347,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-4.2808565902391305</v>
+        <v>-7.4914990329184779</v>
       </c>
       <c r="E30" s="1">
-        <v>-4.9155146780804069</v>
+        <v>-8.6021506866407123</v>
       </c>
       <c r="F30" s="1">
-        <v>-3.8449582311331034</v>
+        <v>-6.7286769044829313</v>
       </c>
       <c r="G30" s="1">
-        <v>-5.1274174187353516</v>
+        <v>-8.9729804827868662</v>
       </c>
       <c r="H30" s="1">
-        <v>-6.8266198539389658</v>
+        <v>-11.94658474439319</v>
       </c>
       <c r="I30" s="1">
-        <v>-6.4796949145751768</v>
+        <v>-11.339466100506559</v>
       </c>
       <c r="J30" s="1">
-        <v>-5.7591017685406056</v>
+        <v>-10.078428094946061</v>
       </c>
       <c r="K30" s="1">
-        <v>-6.807647365442679</v>
+        <v>-11.913382889524689</v>
       </c>
       <c r="L30" s="1">
-        <v>-7.1673091070115262</v>
+        <v>-12.542790937270171</v>
       </c>
       <c r="M30" s="1">
-        <v>-9.0644706973016351</v>
+        <v>-15.862823720277861</v>
       </c>
       <c r="N30" s="1">
-        <v>-9.2472877633420207</v>
+        <v>-16.182753585848538</v>
       </c>
       <c r="O30" s="1">
-        <v>-9.0663507611192351</v>
+        <v>-15.866113831958661</v>
       </c>
       <c r="P30" s="1">
-        <v>-7.4009956747645935</v>
+        <v>-12.951742430838038</v>
       </c>
       <c r="Q30" s="1">
-        <v>-7.2751850362662696</v>
+        <v>-12.731573813465971</v>
       </c>
       <c r="R30" s="1">
-        <v>-7.6711428365160605</v>
+        <v>-13.424499963903106</v>
       </c>
       <c r="S30" s="1">
-        <v>-6.3152111648175504</v>
+        <v>-11.051619538430714</v>
       </c>
       <c r="T30" s="1">
-        <v>-6.0244927905396866</v>
+        <v>-10.542862383444451</v>
       </c>
       <c r="U30" s="1">
-        <v>-5.3875282586436795</v>
+        <v>-9.4281744526264397</v>
       </c>
       <c r="V30" s="1">
-        <v>-3.1220631025814751</v>
+        <v>-5.4636104295175816</v>
       </c>
       <c r="W30" s="1">
-        <v>-4.1967462128139408</v>
+        <v>-7.3443058724243961</v>
       </c>
       <c r="X30" s="1">
-        <v>-4.2941522715258866</v>
+        <v>-7.5147664751703012</v>
       </c>
       <c r="Y30" s="1">
-        <v>-3.9717468103361209</v>
+        <v>-6.9505569180882114</v>
       </c>
       <c r="Z30" s="1">
-        <v>-3.2823725602967979</v>
+        <v>-5.7441519805193959</v>
       </c>
       <c r="AA30" s="1">
-        <v>-4.2138408376493484</v>
+        <v>-7.3742214658863592</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -73430,76 +73430,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>3.2311518061277229</v>
+        <v>5.654515660723515</v>
       </c>
       <c r="E31" s="1">
-        <v>4.0729774618685539</v>
+        <v>7.1277105582699694</v>
       </c>
       <c r="F31" s="1">
-        <v>5.2980886479118929</v>
+        <v>9.2716551338458117</v>
       </c>
       <c r="G31" s="1">
-        <v>5.0579909136302827</v>
+        <v>8.8514840988529944</v>
       </c>
       <c r="H31" s="1">
-        <v>6.312767707929904</v>
+        <v>11.047343488877331</v>
       </c>
       <c r="I31" s="1">
-        <v>5.5987871648029355</v>
+        <v>9.7978775384051371</v>
       </c>
       <c r="J31" s="1">
-        <v>5.5412685106712489</v>
+        <v>9.697219893674685</v>
       </c>
       <c r="K31" s="1">
-        <v>6.4589965426748828</v>
+        <v>11.303243949681045</v>
       </c>
       <c r="L31" s="1">
-        <v>5.5677078683062513</v>
+        <v>9.74348876953594</v>
       </c>
       <c r="M31" s="1">
-        <v>8.4890306543280776</v>
+        <v>14.855803645074136</v>
       </c>
       <c r="N31" s="1">
-        <v>6.8770116506800969</v>
+        <v>12.03477038869017</v>
       </c>
       <c r="O31" s="1">
-        <v>6.1168387568017657</v>
+        <v>10.704467824403089</v>
       </c>
       <c r="P31" s="1">
-        <v>7.0681519822130374</v>
+        <v>12.369265968872815</v>
       </c>
       <c r="Q31" s="1">
-        <v>6.305551404238499</v>
+        <v>11.034714957417373</v>
       </c>
       <c r="R31" s="1">
-        <v>5.3947927272216711</v>
+        <v>9.4408872726379247</v>
       </c>
       <c r="S31" s="1">
-        <v>4.7638153905270988</v>
+        <v>8.3366769334224227</v>
       </c>
       <c r="T31" s="1">
-        <v>5.0116920725870155</v>
+        <v>8.7704611270272768</v>
       </c>
       <c r="U31" s="1">
-        <v>4.4300240802864357</v>
+        <v>7.7525421405012622</v>
       </c>
       <c r="V31" s="1">
-        <v>4.1967700593402339</v>
+        <v>7.3443476038454092</v>
       </c>
       <c r="W31" s="1">
-        <v>4.4740891149886695</v>
+        <v>7.8296559512301718</v>
       </c>
       <c r="X31" s="1">
-        <v>4.1224868272928319</v>
+        <v>7.2143519477624558</v>
       </c>
       <c r="Y31" s="1">
-        <v>4.8116035169173497</v>
+        <v>8.4203061546053615</v>
       </c>
       <c r="Z31" s="1">
-        <v>3.4325855949956394</v>
+        <v>6.0070247912423689</v>
       </c>
       <c r="AA31" s="1">
-        <v>3.6800481087863499</v>
+        <v>6.4400841903761119</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -73513,76 +73513,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>1.8522469399500003</v>
+        <v>3.2414321449125008</v>
       </c>
       <c r="E32" s="1">
-        <v>2.0300357577500003</v>
+        <v>3.5525625760625008</v>
       </c>
       <c r="F32" s="1">
-        <v>1.7312170150000001</v>
+        <v>3.0296297762500002</v>
       </c>
       <c r="G32" s="1">
-        <v>1.5589020883333331</v>
+        <v>2.7280786545833329</v>
       </c>
       <c r="H32" s="1">
-        <v>1.3309775424000001</v>
+        <v>2.3292106992000003</v>
       </c>
       <c r="I32" s="1">
-        <v>1.0840009326666669</v>
+        <v>1.897001632166667</v>
       </c>
       <c r="J32" s="1">
-        <v>1.3395993775999999</v>
+        <v>2.3442989108000001</v>
       </c>
       <c r="K32" s="1">
-        <v>0.2496070001333334</v>
+        <v>0.43681225023333342</v>
       </c>
       <c r="L32" s="1">
-        <v>0.21311033333333332</v>
+        <v>0.37294308333333331</v>
       </c>
       <c r="M32" s="1">
-        <v>0.30447073323333324</v>
+        <v>0.53282378315833312</v>
       </c>
       <c r="N32" s="1">
-        <v>0.18114073890000001</v>
+        <v>0.31699629307500005</v>
       </c>
       <c r="O32" s="1">
-        <v>0.23092331276666658</v>
+        <v>0.40411579734166653</v>
       </c>
       <c r="P32" s="1">
-        <v>0.3606237838500001</v>
+        <v>0.63109162173750022</v>
       </c>
       <c r="Q32" s="1">
-        <v>0.66443387504999996</v>
+        <v>1.1627592813374998</v>
       </c>
       <c r="R32" s="1">
-        <v>0.72321122719999986</v>
+        <v>1.2656196475999997</v>
       </c>
       <c r="S32" s="1">
-        <v>0.67601033279999989</v>
+        <v>1.1830180823999998</v>
       </c>
       <c r="T32" s="1">
-        <v>0.39501522499999991</v>
+        <v>0.69127664374999986</v>
       </c>
       <c r="U32" s="1">
-        <v>0.84487591649999982</v>
+        <v>1.4785328538749998</v>
       </c>
       <c r="V32" s="1">
-        <v>0.45330394560000004</v>
+        <v>0.79328190480000005</v>
       </c>
       <c r="W32" s="1">
-        <v>0.33863536409999989</v>
+        <v>0.5926118871749998</v>
       </c>
       <c r="X32" s="1">
-        <v>0.48399183360000003</v>
+        <v>0.84698570880000001</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.29913384159999995</v>
+        <v>0.52348422279999995</v>
       </c>
       <c r="Z32" s="1">
-        <v>1.4079849613500002</v>
+        <v>2.4639736823625005</v>
       </c>
       <c r="AA32" s="1">
-        <v>1.7144726316666665</v>
+        <v>3.0003271054166665</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -73596,76 +73596,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-4.1952394584343473</v>
+        <v>-7.3416690522601078</v>
       </c>
       <c r="E33" s="1">
-        <v>-4.8172043845187993</v>
+        <v>-8.4301076729078979</v>
       </c>
       <c r="F33" s="1">
-        <v>-3.7680590665104408</v>
+        <v>-6.5941033663932718</v>
       </c>
       <c r="G33" s="1">
-        <v>-4.9735948961732896</v>
+        <v>-8.7037910683032571</v>
       </c>
       <c r="H33" s="1">
-        <v>-7.1679508466359136</v>
+        <v>-12.54391398161285</v>
       </c>
       <c r="I33" s="1">
-        <v>-6.2853040671379219</v>
+        <v>-10.999282117491363</v>
       </c>
       <c r="J33" s="1">
-        <v>-5.8742838039114176</v>
+        <v>-10.279996656844981</v>
       </c>
       <c r="K33" s="1">
-        <v>-6.7395708917882517</v>
+        <v>-11.79424906062944</v>
       </c>
       <c r="L33" s="1">
-        <v>-6.9522898338011805</v>
+        <v>-12.166507209152066</v>
       </c>
       <c r="M33" s="1">
-        <v>-8.7925365763825862</v>
+        <v>-15.386939008669525</v>
       </c>
       <c r="N33" s="1">
-        <v>-8.7849233751749178</v>
+        <v>-15.373615906556106</v>
       </c>
       <c r="O33" s="1">
-        <v>-9.5196682991751977</v>
+        <v>-16.659419523556597</v>
       </c>
       <c r="P33" s="1">
-        <v>-7.6230255450075317</v>
+        <v>-13.340294703763181</v>
       </c>
       <c r="Q33" s="1">
-        <v>-7.4206887369915941</v>
+        <v>-12.98620528973529</v>
       </c>
       <c r="R33" s="1">
-        <v>-7.977988549976704</v>
+        <v>-13.961479962459233</v>
       </c>
       <c r="S33" s="1">
-        <v>-6.5678196114102514</v>
+        <v>-11.49368431996794</v>
       </c>
       <c r="T33" s="1">
-        <v>-5.9642478626342905</v>
+        <v>-10.437433759610009</v>
       </c>
       <c r="U33" s="1">
-        <v>-5.3336529760572438</v>
+        <v>-9.3338927081001763</v>
       </c>
       <c r="V33" s="1">
-        <v>-3.1532837336072901</v>
+        <v>-5.518246533812758</v>
       </c>
       <c r="W33" s="1">
-        <v>-4.1967462128139408</v>
+        <v>-7.3443058724243961</v>
       </c>
       <c r="X33" s="1">
-        <v>-4.3800353169564046</v>
+        <v>-7.6650618046737078</v>
       </c>
       <c r="Y33" s="1">
-        <v>-4.170334150852927</v>
+        <v>-7.2980847639926223</v>
       </c>
       <c r="Z33" s="1">
-        <v>-3.4464911883116378</v>
+        <v>-6.0313595795453665</v>
       </c>
       <c r="AA33" s="1">
-        <v>-4.0452872041433752</v>
+        <v>-7.0792526072509068</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -73679,76 +73679,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>3.0695942158213367</v>
+        <v>5.3717898776873394</v>
       </c>
       <c r="E34" s="1">
-        <v>4.1951667857246102</v>
+        <v>7.3415418750180681</v>
       </c>
       <c r="F34" s="1">
-        <v>5.0331842155162985</v>
+        <v>8.8080723771535219</v>
       </c>
       <c r="G34" s="1">
-        <v>4.8556712770850723</v>
+        <v>8.4974247348988765</v>
       </c>
       <c r="H34" s="1">
-        <v>5.9971293225334099</v>
+        <v>10.494976314433467</v>
       </c>
       <c r="I34" s="1">
-        <v>5.7667507797470234</v>
+        <v>10.091813864557292</v>
       </c>
       <c r="J34" s="1">
-        <v>5.319617770244399</v>
+        <v>9.3093310979276982</v>
       </c>
       <c r="K34" s="1">
-        <v>6.1360467155411387</v>
+        <v>10.738081752196992</v>
       </c>
       <c r="L34" s="1">
-        <v>5.7904161830385013</v>
+        <v>10.133228320317377</v>
       </c>
       <c r="M34" s="1">
-        <v>8.0645791216116738</v>
+        <v>14.11301346282043</v>
       </c>
       <c r="N34" s="1">
-        <v>6.5331610681460921</v>
+        <v>11.433031869255661</v>
       </c>
       <c r="O34" s="1">
-        <v>6.422680694641854</v>
+        <v>11.239691215623244</v>
       </c>
       <c r="P34" s="1">
-        <v>7.209515021857297</v>
+        <v>12.616651288250269</v>
       </c>
       <c r="Q34" s="1">
-        <v>6.431662432323269</v>
+        <v>11.25540925656572</v>
       </c>
       <c r="R34" s="1">
-        <v>5.5026885817661055</v>
+        <v>9.629705018090684</v>
       </c>
       <c r="S34" s="1">
-        <v>4.7638153905270988</v>
+        <v>8.3366769334224227</v>
       </c>
       <c r="T34" s="1">
-        <v>5.0618089933128854</v>
+        <v>8.8581657382975489</v>
       </c>
       <c r="U34" s="1">
-        <v>4.2971233578778429</v>
+        <v>7.5199658762862249</v>
       </c>
       <c r="V34" s="1">
-        <v>4.3226731611204405</v>
+        <v>7.5646780319607707</v>
       </c>
       <c r="W34" s="1">
-        <v>4.563570897288443</v>
+        <v>7.9862490702547753</v>
       </c>
       <c r="X34" s="1">
-        <v>3.91636248592819</v>
+        <v>6.8536343503743327</v>
       </c>
       <c r="Y34" s="1">
-        <v>4.763487481748176</v>
+        <v>8.3361030930593074</v>
       </c>
       <c r="Z34" s="1">
-        <v>3.2609563152458576</v>
+        <v>5.7066735516802511</v>
       </c>
       <c r="AA34" s="1">
-        <v>3.7904495520499402</v>
+        <v>6.6332867160873956</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -73762,76 +73762,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>1.8522469399500003</v>
+        <v>3.2414321449125008</v>
       </c>
       <c r="E35" s="1">
-        <v>2.1112371880600005</v>
+        <v>3.6946650791050009</v>
       </c>
       <c r="F35" s="1">
-        <v>1.7312170150000001</v>
+        <v>3.0296297762500002</v>
       </c>
       <c r="G35" s="1">
-        <v>1.5277240465666664</v>
+        <v>2.6735170814916662</v>
       </c>
       <c r="H35" s="1">
-        <v>1.2644286652800003</v>
+        <v>2.2127501642400005</v>
       </c>
       <c r="I35" s="1">
-        <v>1.0623209140133334</v>
+        <v>1.8590615995233335</v>
       </c>
       <c r="J35" s="1">
-        <v>1.27261940872</v>
+        <v>2.2270839652599999</v>
       </c>
       <c r="K35" s="1">
-        <v>0.24461486013066677</v>
+        <v>0.42807600522866684</v>
       </c>
       <c r="L35" s="1">
-        <v>0.21311033333333332</v>
+        <v>0.37294308333333331</v>
       </c>
       <c r="M35" s="1">
-        <v>0.3075154405656666</v>
+        <v>0.53815202098991655</v>
       </c>
       <c r="N35" s="1">
-        <v>0.190197775845</v>
+        <v>0.33284610772875001</v>
       </c>
       <c r="O35" s="1">
-        <v>0.22861407963899993</v>
+        <v>0.40007463936824988</v>
       </c>
       <c r="P35" s="1">
-        <v>0.37865497304250012</v>
+        <v>0.66264620282437525</v>
       </c>
       <c r="Q35" s="1">
-        <v>0.67772255255099989</v>
+        <v>1.1860144669642498</v>
       </c>
       <c r="R35" s="1">
-        <v>0.73767545174399984</v>
+        <v>1.2909320405519997</v>
       </c>
       <c r="S35" s="1">
-        <v>0.6557300228159999</v>
+        <v>1.1475275399279998</v>
       </c>
       <c r="T35" s="1">
-        <v>0.40686568174999999</v>
+        <v>0.71201494306250002</v>
       </c>
       <c r="U35" s="1">
-        <v>0.81952963900499975</v>
+        <v>1.4341768682587497</v>
       </c>
       <c r="V35" s="1">
-        <v>0.471436103424</v>
+        <v>0.82501318099200005</v>
       </c>
       <c r="W35" s="1">
-        <v>0.32847630317699988</v>
+        <v>0.57483353055974984</v>
       </c>
       <c r="X35" s="1">
-        <v>0.45979224192000001</v>
+        <v>0.80463642336000007</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.29614250318399998</v>
+        <v>0.51824938057199998</v>
       </c>
       <c r="Z35" s="1">
-        <v>1.4361446605770001</v>
+        <v>2.5132531560097502</v>
       </c>
       <c r="AA35" s="1">
-        <v>1.6973279053500001</v>
+        <v>2.9703238343625</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -73845,76 +73845,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-4.405001431356065</v>
+        <v>-7.7087525048731136</v>
       </c>
       <c r="E36" s="1">
-        <v>-5.0580646037447394</v>
+        <v>-8.851613056553294</v>
       </c>
       <c r="F36" s="1">
-        <v>-3.8811008385057537</v>
+        <v>-6.7919264673850694</v>
       </c>
       <c r="G36" s="1">
-        <v>-5.0730667940967562</v>
+        <v>-8.877866889669324</v>
       </c>
       <c r="H36" s="1">
-        <v>-7.3113098635686322</v>
+        <v>-12.794792261245107</v>
       </c>
       <c r="I36" s="1">
-        <v>-6.5995692704948183</v>
+        <v>-11.549246223365932</v>
       </c>
       <c r="J36" s="1">
-        <v>-5.6980552897940742</v>
+        <v>-9.9715967571396291</v>
       </c>
       <c r="K36" s="1">
-        <v>-6.8743623096240176</v>
+        <v>-12.030134041842031</v>
       </c>
       <c r="L36" s="1">
-        <v>-6.8827669354631693</v>
+        <v>-12.044842137060547</v>
       </c>
       <c r="M36" s="1">
-        <v>-8.52876047909111</v>
+        <v>-14.925330838409442</v>
       </c>
       <c r="N36" s="1">
-        <v>-8.3456772064161751</v>
+        <v>-14.604935111228306</v>
       </c>
       <c r="O36" s="1">
-        <v>-9.3292749331916927</v>
+        <v>-16.326231133085461</v>
       </c>
       <c r="P36" s="1">
-        <v>-7.2418742677571544</v>
+        <v>-12.67327996857502</v>
       </c>
       <c r="Q36" s="1">
-        <v>-7.3464818496216786</v>
+        <v>-12.856343236837937</v>
       </c>
       <c r="R36" s="1">
-        <v>-8.3768879774755387</v>
+        <v>-14.659553960582192</v>
       </c>
       <c r="S36" s="1">
-        <v>-6.76485419975256</v>
+        <v>-11.838494849566979</v>
       </c>
       <c r="T36" s="1">
-        <v>-5.6660354695025745</v>
+        <v>-9.9155620716295054</v>
       </c>
       <c r="U36" s="1">
-        <v>-5.6003356248601044</v>
+        <v>-9.8005873435051818</v>
       </c>
       <c r="V36" s="1">
-        <v>-3.1848165709433629</v>
+        <v>-5.5734289991508854</v>
       </c>
       <c r="W36" s="1">
-        <v>-4.2806811370702187</v>
+        <v>-7.4911919898728829</v>
       </c>
       <c r="X36" s="1">
-        <v>-4.2486342574477112</v>
+        <v>-7.4351099505334943</v>
       </c>
       <c r="Y36" s="1">
-        <v>-4.0035207848188099</v>
+        <v>-7.0061613734329171</v>
       </c>
       <c r="Z36" s="1">
-        <v>-3.5843508358441034</v>
+        <v>-6.2726139627271813</v>
       </c>
       <c r="AA36" s="1">
-        <v>-3.964381460060507</v>
+        <v>-6.9376675551058868</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -73928,76 +73928,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>3.0695942158213367</v>
+        <v>5.3717898776873394</v>
       </c>
       <c r="E37" s="1">
-        <v>4.1112634500101182</v>
+        <v>7.194711037517707</v>
       </c>
       <c r="F37" s="1">
-        <v>5.0331842155162985</v>
+        <v>8.8080723771535219</v>
       </c>
       <c r="G37" s="1">
-        <v>4.6128877132308181</v>
+        <v>8.0725534981539315</v>
       </c>
       <c r="H37" s="1">
-        <v>6.1770432022094122</v>
+        <v>10.809825603866472</v>
       </c>
       <c r="I37" s="1">
-        <v>6.0550883187343745</v>
+        <v>10.596404557785155</v>
       </c>
       <c r="J37" s="1">
-        <v>5.5324024810541745</v>
+        <v>9.6817043418448048</v>
       </c>
       <c r="K37" s="1">
-        <v>6.2587676498519604</v>
+        <v>10.952843387240931</v>
       </c>
       <c r="L37" s="1">
-        <v>5.7904161830385013</v>
+        <v>10.133228320317377</v>
       </c>
       <c r="M37" s="1">
-        <v>8.2258707040439045</v>
+        <v>14.395273732076832</v>
       </c>
       <c r="N37" s="1">
-        <v>6.794487510871936</v>
+        <v>11.890353144025887</v>
       </c>
       <c r="O37" s="1">
-        <v>6.6153611154811083</v>
+        <v>11.57688195209194</v>
       </c>
       <c r="P37" s="1">
-        <v>6.8490392707644334</v>
+        <v>11.985818723837758</v>
       </c>
       <c r="Q37" s="1">
-        <v>6.1100793107071061</v>
+        <v>10.692638793737435</v>
       </c>
       <c r="R37" s="1">
-        <v>5.6127423534014271</v>
+        <v>9.8222991184524968</v>
       </c>
       <c r="S37" s="1">
-        <v>4.6685390827165572</v>
+        <v>8.1699433947539752</v>
       </c>
       <c r="T37" s="1">
-        <v>5.1630451731791434</v>
+        <v>9.0353290530635011</v>
       </c>
       <c r="U37" s="1">
-        <v>4.1682096571415084</v>
+        <v>7.2943668999976392</v>
       </c>
       <c r="V37" s="1">
-        <v>4.4955800875652576</v>
+        <v>7.8672651532392006</v>
       </c>
       <c r="W37" s="1">
-        <v>4.4722994793426736</v>
+        <v>7.8265240888496788</v>
       </c>
       <c r="X37" s="1">
-        <v>3.8771988610689081</v>
+        <v>6.7850980068705891</v>
       </c>
       <c r="Y37" s="1">
-        <v>4.763487481748176</v>
+        <v>8.3361030930593074</v>
       </c>
       <c r="Z37" s="1">
-        <v>3.1305180626360229</v>
+        <v>5.4784066096130406</v>
       </c>
       <c r="AA37" s="1">
-        <v>3.7904495520499402</v>
+        <v>6.6332867160873956</v>
       </c>
     </row>
   </sheetData>
